--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -21,16 +21,16 @@
     <definedName name="countryoftravel">'cv_sample'!$K$1:$K$273</definedName>
     <definedName name="environmentalsample">'cv_sample'!$U$1:$U$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$X$1:$X$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$X$1:$X$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$AE$1:$AE$14</definedName>
     <definedName name="hostsex">'cv_sample'!$AF$1:$AF$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AJ$1:$AJ$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
     <definedName name="travelrelation">'cv_sample'!$I$1:$I$3</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="691">
   <si>
     <t>alias</t>
   </si>
@@ -455,6 +455,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -545,6 +548,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1772,13 +1778,13 @@
     <t>subject exposure duration</t>
   </si>
   <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>No</t>
@@ -1823,7 +1829,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1835,12 +1841,21 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2096,7 +2111,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -2623,10 +2638,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2667,10 +2682,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2697,7 +2712,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2714,7 +2729,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2731,7 +2746,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2748,7 +2763,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2765,7 +2780,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2782,7 +2797,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2799,7 +2814,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2816,7 +2831,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2833,7 +2848,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2850,7 +2865,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2864,7 +2879,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2878,7 +2893,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2892,7 +2907,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2906,7 +2921,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2920,7 +2935,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2934,7 +2949,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2948,7 +2963,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2962,7 +2977,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2972,8 +2987,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2984,7 +3002,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2995,7 +3013,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3006,7 +3024,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3017,7 +3035,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3028,7 +3046,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3039,7 +3057,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3050,7 +3068,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3061,7 +3079,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3072,7 +3090,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3083,7 +3101,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3094,7 +3112,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3105,7 +3123,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3116,7 +3134,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3124,7 +3142,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3132,7 +3150,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3140,7 +3158,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3148,7 +3166,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3156,7 +3174,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3164,7 +3182,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3172,7 +3190,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3180,7 +3198,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3188,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3196,236 +3214,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3447,27 +3470,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3487,122 +3510,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3626,312 +3649,312 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:52" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -3970,258 +3993,258 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I1:AJ289"/>
+  <dimension ref="I1:AJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="9:36">
       <c r="I1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="X1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AE1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AF1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="AJ1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="9:36">
       <c r="I2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="U2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z2" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AE2" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="AF2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="AJ2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="9:36">
       <c r="I3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="X3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AE3" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AF3" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="9:36">
       <c r="K4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="X4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AE4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AF4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="9:36">
       <c r="K5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="X5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AE5" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AF5" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="9:36">
       <c r="K6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="X6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AE6" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AF6" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" spans="9:36">
       <c r="K7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="X7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AE7" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AF7" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="9:36">
       <c r="K8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AE8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AF8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="9:36">
       <c r="K9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="X9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AE9" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AF9" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="9:36">
       <c r="K10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="X10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AE10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AF10" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="9:36">
       <c r="K11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="X11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AE11" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AF11" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="9:36">
       <c r="K12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="X12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AE12" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AF12" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="9:36">
       <c r="K13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="X13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AE13" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="AF13" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="9:36">
       <c r="K14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AE14" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AF14" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15" spans="9:36">
       <c r="K15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="X15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AF15" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="16" spans="9:36">
       <c r="K16" t="s">
+        <v>304</v>
+      </c>
+      <c r="X16" t="s">
         <v>302</v>
-      </c>
-      <c r="X16" t="s">
-        <v>300</v>
       </c>
       <c r="AF16" t="s">
         <v>116</v>
@@ -4229,1562 +4252,1562 @@
     </row>
     <row r="17" spans="11:32">
       <c r="K17" t="s">
+        <v>305</v>
+      </c>
+      <c r="X17" t="s">
         <v>303</v>
       </c>
-      <c r="X17" t="s">
-        <v>301</v>
-      </c>
       <c r="AF17" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" spans="11:32">
       <c r="K18" t="s">
+        <v>306</v>
+      </c>
+      <c r="X18" t="s">
         <v>304</v>
-      </c>
-      <c r="X18" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="19" spans="11:32">
       <c r="K19" t="s">
+        <v>307</v>
+      </c>
+      <c r="X19" t="s">
         <v>305</v>
-      </c>
-      <c r="X19" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="20" spans="11:32">
       <c r="K20" t="s">
+        <v>308</v>
+      </c>
+      <c r="X20" t="s">
         <v>306</v>
-      </c>
-      <c r="X20" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="21" spans="11:32">
       <c r="K21" t="s">
+        <v>309</v>
+      </c>
+      <c r="X21" t="s">
         <v>307</v>
-      </c>
-      <c r="X21" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="22" spans="11:32">
       <c r="K22" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="X22" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="23" spans="11:32">
       <c r="K23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="X23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="11:32">
       <c r="K24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="X24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="11:32">
       <c r="K25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="11:32">
       <c r="K26" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="11:32">
       <c r="K27" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="X27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="11:32">
       <c r="K28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="X28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="11:32">
       <c r="K29" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X29" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="11:32">
       <c r="K30" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="11:32">
       <c r="K31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="11:32">
       <c r="K32" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X32" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="11:24">
       <c r="K33" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="34" spans="11:24">
       <c r="K34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="X34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" spans="11:24">
       <c r="K35" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="X35" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="11:24">
       <c r="K36" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="X36" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="11:24">
       <c r="K37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="X37" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="11:24">
       <c r="K38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="X38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="11:24">
       <c r="K39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="X39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="11:24">
       <c r="K40" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="X40" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="11:24">
       <c r="K41" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="X41" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="11:24">
       <c r="K42" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="X42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="11:24">
       <c r="K43" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="X43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="11:24">
       <c r="K44" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="X44" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="11:24">
       <c r="K45" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="X45" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="11:24">
       <c r="K46" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="X46" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="11:24">
       <c r="K47" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="X47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="11:24">
       <c r="K48" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="X48" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" spans="11:24">
       <c r="K49" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="X49" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="11:24">
       <c r="K50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="X50" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="11:24">
       <c r="K51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="X51" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="11:24">
       <c r="K52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="X52" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="11:24">
       <c r="K53" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="X53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="11:24">
       <c r="K54" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="X54" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="11:24">
       <c r="K55" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="X55" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="11:24">
       <c r="K56" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X56" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="11:24">
       <c r="K57" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="X57" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="11:24">
       <c r="K58" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X58" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="11:24">
       <c r="K59" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="X59" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="11:24">
       <c r="K60" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="X60" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="11:24">
       <c r="K61" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="X61" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="11:24">
       <c r="K62" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X62" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="11:24">
       <c r="K63" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X63" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="64" spans="11:24">
       <c r="K64" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X64" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="11:24">
       <c r="K65" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X65" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="11:24">
       <c r="K66" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="X66" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="11:24">
       <c r="K67" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="X67" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="11:24">
       <c r="K68" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="X68" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="11:24">
       <c r="K69" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="X69" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="11:24">
       <c r="K70" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="X70" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="11:24">
       <c r="K71" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="X71" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="72" spans="11:24">
       <c r="K72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="X72" t="s">
-        <v>594</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="11:24">
       <c r="K73" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="X73" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="74" spans="11:24">
       <c r="K74" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="X74" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="75" spans="11:24">
       <c r="K75" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="X75" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" spans="11:24">
       <c r="K76" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="X76" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="11:24">
       <c r="K77" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="X77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78" spans="11:24">
       <c r="K78" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="X78" t="s">
-        <v>359</v>
+        <v>596</v>
       </c>
     </row>
     <row r="79" spans="11:24">
       <c r="K79" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="X79" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="80" spans="11:24">
       <c r="K80" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="X80" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="11:24">
       <c r="K81" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="X81" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="82" spans="11:24">
       <c r="K82" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="X82" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="83" spans="11:24">
       <c r="K83" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="X83" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="11:24">
       <c r="K84" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="X84" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" spans="11:24">
       <c r="K85" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="X85" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="86" spans="11:24">
       <c r="K86" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="X86" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="11:24">
       <c r="K87" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="X87" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="88" spans="11:24">
       <c r="K88" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="X88" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="11:24">
       <c r="K89" t="s">
+        <v>377</v>
+      </c>
+      <c r="X89" t="s">
         <v>375</v>
-      </c>
-      <c r="X89" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="90" spans="11:24">
       <c r="K90" t="s">
+        <v>378</v>
+      </c>
+      <c r="X90" t="s">
         <v>376</v>
-      </c>
-      <c r="X90" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="91" spans="11:24">
       <c r="K91" t="s">
+        <v>379</v>
+      </c>
+      <c r="X91" t="s">
         <v>377</v>
-      </c>
-      <c r="X91" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="92" spans="11:24">
       <c r="K92" t="s">
+        <v>380</v>
+      </c>
+      <c r="X92" t="s">
         <v>378</v>
-      </c>
-      <c r="X92" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="93" spans="11:24">
       <c r="K93" t="s">
+        <v>381</v>
+      </c>
+      <c r="X93" t="s">
         <v>379</v>
-      </c>
-      <c r="X93" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="94" spans="11:24">
       <c r="K94" t="s">
+        <v>382</v>
+      </c>
+      <c r="X94" t="s">
         <v>380</v>
-      </c>
-      <c r="X94" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="95" spans="11:24">
       <c r="K95" t="s">
+        <v>383</v>
+      </c>
+      <c r="X95" t="s">
         <v>381</v>
-      </c>
-      <c r="X95" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="96" spans="11:24">
       <c r="K96" t="s">
+        <v>384</v>
+      </c>
+      <c r="X96" t="s">
         <v>382</v>
-      </c>
-      <c r="X96" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="97" spans="11:24">
       <c r="K97" t="s">
+        <v>385</v>
+      </c>
+      <c r="X97" t="s">
         <v>383</v>
-      </c>
-      <c r="X97" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="98" spans="11:24">
       <c r="K98" t="s">
+        <v>386</v>
+      </c>
+      <c r="X98" t="s">
         <v>384</v>
-      </c>
-      <c r="X98" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="99" spans="11:24">
       <c r="K99" t="s">
+        <v>387</v>
+      </c>
+      <c r="X99" t="s">
         <v>385</v>
-      </c>
-      <c r="X99" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="100" spans="11:24">
       <c r="K100" t="s">
+        <v>388</v>
+      </c>
+      <c r="X100" t="s">
         <v>386</v>
-      </c>
-      <c r="X100" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="101" spans="11:24">
       <c r="K101" t="s">
+        <v>389</v>
+      </c>
+      <c r="X101" t="s">
         <v>387</v>
-      </c>
-      <c r="X101" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="102" spans="11:24">
       <c r="K102" t="s">
+        <v>390</v>
+      </c>
+      <c r="X102" t="s">
         <v>388</v>
-      </c>
-      <c r="X102" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="103" spans="11:24">
       <c r="K103" t="s">
+        <v>391</v>
+      </c>
+      <c r="X103" t="s">
         <v>389</v>
-      </c>
-      <c r="X103" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="104" spans="11:24">
       <c r="K104" t="s">
+        <v>392</v>
+      </c>
+      <c r="X104" t="s">
         <v>390</v>
-      </c>
-      <c r="X104" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="105" spans="11:24">
       <c r="K105" t="s">
+        <v>393</v>
+      </c>
+      <c r="X105" t="s">
         <v>391</v>
-      </c>
-      <c r="X105" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="106" spans="11:24">
       <c r="K106" t="s">
+        <v>394</v>
+      </c>
+      <c r="X106" t="s">
         <v>392</v>
-      </c>
-      <c r="X106" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="107" spans="11:24">
       <c r="K107" t="s">
+        <v>395</v>
+      </c>
+      <c r="X107" t="s">
         <v>393</v>
-      </c>
-      <c r="X107" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="108" spans="11:24">
       <c r="K108" t="s">
+        <v>396</v>
+      </c>
+      <c r="X108" t="s">
         <v>394</v>
-      </c>
-      <c r="X108" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="109" spans="11:24">
       <c r="K109" t="s">
+        <v>397</v>
+      </c>
+      <c r="X109" t="s">
         <v>395</v>
-      </c>
-      <c r="X109" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="110" spans="11:24">
       <c r="K110" t="s">
+        <v>398</v>
+      </c>
+      <c r="X110" t="s">
         <v>396</v>
-      </c>
-      <c r="X110" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="111" spans="11:24">
       <c r="K111" t="s">
+        <v>399</v>
+      </c>
+      <c r="X111" t="s">
         <v>397</v>
-      </c>
-      <c r="X111" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="112" spans="11:24">
       <c r="K112" t="s">
+        <v>400</v>
+      </c>
+      <c r="X112" t="s">
         <v>398</v>
-      </c>
-      <c r="X112" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="113" spans="11:24">
       <c r="K113" t="s">
+        <v>401</v>
+      </c>
+      <c r="X113" t="s">
         <v>399</v>
-      </c>
-      <c r="X113" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="114" spans="11:24">
       <c r="K114" t="s">
+        <v>402</v>
+      </c>
+      <c r="X114" t="s">
         <v>400</v>
-      </c>
-      <c r="X114" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="115" spans="11:24">
       <c r="K115" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="X115" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="116" spans="11:24">
       <c r="K116" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="X116" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="11:24">
       <c r="K117" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="X117" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="11:24">
       <c r="K118" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="X118" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="11:24">
       <c r="K119" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="X119" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="120" spans="11:24">
       <c r="K120" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="X120" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" spans="11:24">
       <c r="K121" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="X121" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="122" spans="11:24">
       <c r="K122" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="X122" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="123" spans="11:24">
       <c r="K123" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="X123" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="124" spans="11:24">
       <c r="K124" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="X124" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="125" spans="11:24">
       <c r="K125" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="X125" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="126" spans="11:24">
       <c r="K126" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="X126" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="127" spans="11:24">
       <c r="K127" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="X127" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="128" spans="11:24">
       <c r="K128" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="X128" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="129" spans="11:24">
       <c r="K129" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="X129" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="11:24">
       <c r="K130" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="X130" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="131" spans="11:24">
       <c r="K131" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="X131" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="132" spans="11:24">
       <c r="K132" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="X132" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="133" spans="11:24">
       <c r="K133" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="X133" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="134" spans="11:24">
       <c r="K134" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="X134" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="135" spans="11:24">
       <c r="K135" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="X135" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="136" spans="11:24">
       <c r="K136" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="X136" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="137" spans="11:24">
       <c r="K137" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="X137" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="11:24">
       <c r="K138" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="X138" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="139" spans="11:24">
       <c r="K139" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="X139" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="140" spans="11:24">
       <c r="K140" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="X140" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="141" spans="11:24">
       <c r="K141" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="X141" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="142" spans="11:24">
       <c r="K142" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="X142" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="143" spans="11:24">
       <c r="K143" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="X143" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="144" spans="11:24">
       <c r="K144" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="X144" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="145" spans="11:24">
       <c r="K145" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="X145" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="146" spans="11:24">
       <c r="K146" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="X146" t="s">
-        <v>429</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147" spans="11:24">
       <c r="K147" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="X147" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="148" spans="11:24">
       <c r="K148" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="X148" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="149" spans="11:24">
       <c r="K149" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="X149" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="150" spans="11:24">
       <c r="K150" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="X150" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="151" spans="11:24">
       <c r="K151" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="X151" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="152" spans="11:24">
       <c r="K152" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="X152" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="153" spans="11:24">
       <c r="K153" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="X153" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="154" spans="11:24">
       <c r="K154" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="X154" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="155" spans="11:24">
       <c r="K155" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="X155" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="156" spans="11:24">
       <c r="K156" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="X156" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="157" spans="11:24">
       <c r="K157" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="X157" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="158" spans="11:24">
       <c r="K158" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="X158" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="159" spans="11:24">
       <c r="K159" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="X159" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="160" spans="11:24">
       <c r="K160" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="X160" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="161" spans="11:24">
       <c r="K161" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="X161" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="162" spans="11:24">
       <c r="K162" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X162" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="163" spans="11:24">
       <c r="K163" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="X163" t="s">
-        <v>445</v>
+        <v>602</v>
       </c>
     </row>
     <row r="164" spans="11:24">
       <c r="K164" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="X164" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" spans="11:24">
       <c r="K165" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="X165" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="11:24">
       <c r="K166" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="X166" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="167" spans="11:24">
       <c r="K167" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="X167" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="168" spans="11:24">
       <c r="K168" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="X168" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="11:24">
       <c r="K169" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="X169" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="170" spans="11:24">
       <c r="K170" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="X170" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="11:24">
       <c r="K171" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="X171" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="172" spans="11:24">
       <c r="K172" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="X172" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="173" spans="11:24">
       <c r="K173" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="X173" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="174" spans="11:24">
       <c r="K174" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="X174" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="175" spans="11:24">
       <c r="K175" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="X175" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="11:24">
       <c r="K176" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="X176" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="177" spans="11:24">
       <c r="K177" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="X177" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="11:24">
       <c r="K178" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="X178" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="179" spans="11:24">
       <c r="K179" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="X179" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="11:24">
       <c r="K180" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="X180" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="181" spans="11:24">
       <c r="K181" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="X181" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="182" spans="11:24">
       <c r="K182" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="X182" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="183" spans="11:24">
       <c r="K183" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="X183" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="184" spans="11:24">
       <c r="K184" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="X184" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="185" spans="11:24">
       <c r="K185" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="X185" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="186" spans="11:24">
       <c r="K186" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="X186" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="187" spans="11:24">
       <c r="K187" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="X187" t="s">
-        <v>468</v>
+        <v>605</v>
       </c>
     </row>
     <row r="188" spans="11:24">
       <c r="K188" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="X188" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="189" spans="11:24">
       <c r="K189" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="X189" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="190" spans="11:24">
       <c r="K190" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="X190" t="s">
-        <v>601</v>
+        <v>472</v>
       </c>
     </row>
     <row r="191" spans="11:24">
       <c r="K191" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="X191" t="s">
-        <v>471</v>
+        <v>606</v>
       </c>
     </row>
     <row r="192" spans="11:24">
       <c r="K192" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="X192" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="193" spans="11:24">
       <c r="K193" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="X193" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="194" spans="11:24">
       <c r="K194" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X194" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="195" spans="11:24">
       <c r="K195" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="X195" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="196" spans="11:24">
       <c r="K196" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="X196" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="197" spans="11:24">
       <c r="K197" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="X197" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="198" spans="11:24">
       <c r="K198" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="X198" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="199" spans="11:24">
       <c r="K199" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="X199" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="200" spans="11:24">
       <c r="K200" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="X200" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="201" spans="11:24">
       <c r="K201" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X201" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="202" spans="11:24">
       <c r="K202" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X202" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="11:24">
       <c r="K203" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="X203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="11:24">
       <c r="K204" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="X204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="11:24">
       <c r="K205" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="X205" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="206" spans="11:24">
       <c r="K206" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="X206" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="207" spans="11:24">
       <c r="K207" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="X207" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="208" spans="11:24">
       <c r="K208" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="X208" t="s">
-        <v>602</v>
+        <v>489</v>
       </c>
     </row>
     <row r="209" spans="11:24">
       <c r="K209" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="X209" t="s">
-        <v>488</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="11:24">
       <c r="K210" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="X210" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="211" spans="11:24">
       <c r="K211" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X211" t="s">
         <v>491</v>
@@ -5792,7 +5815,7 @@
     </row>
     <row r="212" spans="11:24">
       <c r="K212" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="X212" t="s">
         <v>492</v>
@@ -5800,7 +5823,7 @@
     </row>
     <row r="213" spans="11:24">
       <c r="K213" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="X213" t="s">
         <v>493</v>
@@ -5808,23 +5831,23 @@
     </row>
     <row r="214" spans="11:24">
       <c r="K214" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="X214" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="11:24">
       <c r="K215" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="X215" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="216" spans="11:24">
       <c r="K216" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="X216" t="s">
         <v>497</v>
@@ -5832,7 +5855,7 @@
     </row>
     <row r="217" spans="11:24">
       <c r="K217" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="X217" t="s">
         <v>498</v>
@@ -5840,7 +5863,7 @@
     </row>
     <row r="218" spans="11:24">
       <c r="K218" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="X218" t="s">
         <v>499</v>
@@ -5848,7 +5871,7 @@
     </row>
     <row r="219" spans="11:24">
       <c r="K219" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="X219" t="s">
         <v>500</v>
@@ -5856,55 +5879,55 @@
     </row>
     <row r="220" spans="11:24">
       <c r="K220" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="X220" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="11:24">
       <c r="K221" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="X221" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="222" spans="11:24">
       <c r="K222" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="X222" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="223" spans="11:24">
       <c r="K223" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="X223" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="224" spans="11:24">
       <c r="K224" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="X224" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="225" spans="11:24">
       <c r="K225" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="X225" t="s">
-        <v>603</v>
+        <v>506</v>
       </c>
     </row>
     <row r="226" spans="11:24">
       <c r="K226" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="X226" t="s">
         <v>507</v>
@@ -5912,7 +5935,7 @@
     </row>
     <row r="227" spans="11:24">
       <c r="K227" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="X227" t="s">
         <v>508</v>
@@ -5920,410 +5943,410 @@
     </row>
     <row r="228" spans="11:24">
       <c r="K228" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="X228" t="s">
-        <v>509</v>
+        <v>608</v>
       </c>
     </row>
     <row r="229" spans="11:24">
       <c r="K229" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="X229" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="230" spans="11:24">
       <c r="K230" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="X230" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="231" spans="11:24">
       <c r="K231" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="X231" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="232" spans="11:24">
       <c r="K232" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="X232" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="233" spans="11:24">
       <c r="K233" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="X233" t="s">
-        <v>604</v>
+        <v>513</v>
       </c>
     </row>
     <row r="234" spans="11:24">
       <c r="K234" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="X234" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="235" spans="11:24">
       <c r="K235" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="X235" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="236" spans="11:24">
       <c r="K236" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="X236" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="237" spans="11:24">
       <c r="K237" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="X237" t="s">
-        <v>519</v>
+        <v>609</v>
       </c>
     </row>
     <row r="238" spans="11:24">
       <c r="K238" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X238" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="239" spans="11:24">
       <c r="K239" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="X239" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="240" spans="11:24">
       <c r="K240" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="X240" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="241" spans="11:24">
       <c r="K241" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="X241" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="242" spans="11:24">
       <c r="K242" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="X242" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="243" spans="11:24">
       <c r="K243" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="X243" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="244" spans="11:24">
       <c r="K244" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="X244" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="245" spans="11:24">
       <c r="K245" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="X245" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="246" spans="11:24">
       <c r="K246" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="X246" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="247" spans="11:24">
       <c r="K247" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="X247" t="s">
-        <v>605</v>
+        <v>527</v>
       </c>
     </row>
     <row r="248" spans="11:24">
       <c r="K248" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="X248" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="249" spans="11:24">
       <c r="K249" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="X249" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="250" spans="11:24">
       <c r="K250" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="X250" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="251" spans="11:24">
       <c r="K251" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="X251" t="s">
-        <v>533</v>
+        <v>610</v>
       </c>
     </row>
     <row r="252" spans="11:24">
       <c r="K252" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="X252" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="253" spans="11:24">
       <c r="K253" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="X253" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="254" spans="11:24">
       <c r="K254" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="X254" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="255" spans="11:24">
       <c r="K255" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="X255" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="256" spans="11:24">
       <c r="K256" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="X256" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="257" spans="11:24">
       <c r="K257" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="X257" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="258" spans="11:24">
       <c r="K258" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="X258" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="259" spans="11:24">
       <c r="K259" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="X259" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="260" spans="11:24">
       <c r="K260" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="X260" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="261" spans="11:24">
       <c r="K261" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="X261" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="262" spans="11:24">
       <c r="K262" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="X262" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="263" spans="11:24">
       <c r="K263" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="X263" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="264" spans="11:24">
       <c r="K264" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="X264" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="265" spans="11:24">
       <c r="K265" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="X265" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="266" spans="11:24">
       <c r="K266" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="X266" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="267" spans="11:24">
       <c r="K267" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="X267" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="268" spans="11:24">
       <c r="K268" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="X268" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="269" spans="11:24">
       <c r="K269" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="X269" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="270" spans="11:24">
       <c r="K270" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="X270" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="271" spans="11:24">
       <c r="K271" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="X271" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="272" spans="11:24">
       <c r="K272" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="X272" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="273" spans="11:24">
       <c r="K273" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="X273" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="274" spans="11:24">
       <c r="X274" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="275" spans="11:24">
       <c r="X275" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="276" spans="11:24">
       <c r="X276" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="277" spans="11:24">
       <c r="X277" t="s">
-        <v>606</v>
+        <v>557</v>
       </c>
     </row>
     <row r="278" spans="11:24">
       <c r="X278" t="s">
-        <v>607</v>
+        <v>558</v>
       </c>
     </row>
     <row r="279" spans="11:24">
       <c r="X279" t="s">
-        <v>608</v>
+        <v>559</v>
       </c>
     </row>
     <row r="280" spans="11:24">
       <c r="X280" t="s">
-        <v>609</v>
+        <v>560</v>
       </c>
     </row>
     <row r="281" spans="11:24">
       <c r="X281" t="s">
-        <v>610</v>
+        <v>561</v>
       </c>
     </row>
     <row r="282" spans="11:24">
@@ -6364,6 +6387,31 @@
     <row r="289" spans="24:24">
       <c r="X289" t="s">
         <v>618</v>
+      </c>
+    </row>
+    <row r="290" spans="24:24">
+      <c r="X290" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="291" spans="24:24">
+      <c r="X291" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="292" spans="24:24">
+      <c r="X292" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="293" spans="24:24">
+      <c r="X293" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="294" spans="24:24">
+      <c r="X294" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -17,29 +17,29 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="clinicalsetting">'cv_sample'!$H$1:$H$2</definedName>
-    <definedName name="countryoftravel">'cv_sample'!$I$1:$I$273</definedName>
-    <definedName name="environmentalsample">'cv_sample'!$S$1:$S$2</definedName>
+    <definedName name="clinicalsetting">'cv_sample'!$I$1:$I$2</definedName>
+    <definedName name="countryoftravel">'cv_sample'!$J$1:$J$273</definedName>
+    <definedName name="environmentalsample">'cv_sample'!$T$1:$T$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$V$1:$V$289</definedName>
-    <definedName name="hostdiseaseoutcome">'cv_sample'!$X$1:$X$3</definedName>
-    <definedName name="hosthealthstate">'cv_sample'!$AC$1:$AC$14</definedName>
-    <definedName name="hostsex">'cv_sample'!$AD$1:$AD$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
-    <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AH$1:$AH$2</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
+    <definedName name="hostdiseaseoutcome">'cv_sample'!$Y$1:$Y$3</definedName>
+    <definedName name="hosthealthstate">'cv_sample'!$AD$1:$AD$14</definedName>
+    <definedName name="hostsex">'cv_sample'!$AE$1:$AE$17</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AI$1:$AI$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="travelrelation">'cv_sample'!$G$1:$G$3</definedName>
+    <definedName name="travelrelation">'cv_sample'!$H$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="689">
   <si>
     <t>alias</t>
   </si>
@@ -455,6 +455,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -545,6 +548,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -845,6 +851,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1811,7 +1823,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1823,10 +1835,19 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
   </si>
   <si>
     <t>North Sea</t>
@@ -2611,10 +2632,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2655,10 +2676,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2685,7 +2706,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2702,7 +2723,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2719,7 +2740,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2736,7 +2757,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2753,7 +2774,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2770,7 +2791,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2787,7 +2808,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2804,7 +2825,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2821,7 +2842,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2838,7 +2859,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2852,7 +2873,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2866,7 +2887,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2880,7 +2901,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2894,7 +2915,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2908,7 +2929,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2922,7 +2943,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2936,7 +2957,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2950,7 +2971,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2960,8 +2981,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2972,7 +2996,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2983,7 +3007,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2994,7 +3018,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3005,7 +3029,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3016,7 +3040,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3027,7 +3051,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3038,7 +3062,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3049,7 +3073,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3060,7 +3084,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3071,7 +3095,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3082,7 +3106,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3093,7 +3117,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3104,7 +3128,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3112,7 +3136,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3120,7 +3144,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3128,7 +3152,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3136,7 +3160,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3144,7 +3168,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3152,7 +3176,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3160,7 +3184,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3168,7 +3192,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3176,7 +3200,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3184,236 +3208,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3435,27 +3464,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3475,122 +3504,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3600,13 +3629,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50">
+    <row r="1" spans="1:51">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3614,329 +3643,335 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>556</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>615</v>
+        <v>586</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="150" customHeight="1">
+        <v>685</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>557</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>681</v>
+        <v>686</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>travelrelation</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>clinicalsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>countryoftravel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
       <formula1>environmentalsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
       <formula1>hostdiseaseoutcome</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>hosthealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>hostsex</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI3:AI101">
       <formula1>Isthesequencedpathogenhostassociated</formula1>
     </dataValidation>
   </dataValidations>
@@ -3946,2400 +3981,2425 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AH289"/>
+  <dimension ref="H1:AI294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="7:34">
-      <c r="G1" t="s">
-        <v>274</v>
-      </c>
+    <row r="1" spans="8:35">
       <c r="H1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
         <v>283</v>
       </c>
-      <c r="S1" t="s">
-        <v>576</v>
-      </c>
-      <c r="V1" t="s">
-        <v>283</v>
-      </c>
-      <c r="X1" t="s">
-        <v>619</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>632</v>
+      <c r="J1" t="s">
+        <v>287</v>
+      </c>
+      <c r="T1" t="s">
+        <v>580</v>
+      </c>
+      <c r="W1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>626</v>
       </c>
       <c r="AD1" t="s">
-        <v>636</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="2" spans="7:34">
-      <c r="G2" t="s">
-        <v>275</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>643</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="8:35">
       <c r="H2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I2" t="s">
         <v>284</v>
       </c>
-      <c r="S2" t="s">
-        <v>577</v>
-      </c>
-      <c r="V2" t="s">
-        <v>284</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="J2" t="s">
+        <v>288</v>
+      </c>
+      <c r="T2" t="s">
+        <v>581</v>
+      </c>
+      <c r="W2" t="s">
+        <v>288</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>627</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>640</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>644</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="8:35">
+      <c r="H3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J3" t="s">
+        <v>289</v>
+      </c>
+      <c r="W3" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>628</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>610</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="4" spans="8:35">
+      <c r="J4" t="s">
+        <v>290</v>
+      </c>
+      <c r="W4" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>611</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="5" spans="8:35">
+      <c r="J5" t="s">
+        <v>291</v>
+      </c>
+      <c r="W5" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>612</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="6" spans="8:35">
+      <c r="J6" t="s">
+        <v>292</v>
+      </c>
+      <c r="W6" t="s">
+        <v>292</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>613</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="7" spans="8:35">
+      <c r="J7" t="s">
+        <v>293</v>
+      </c>
+      <c r="W7" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>614</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="8:35">
+      <c r="J8" t="s">
+        <v>294</v>
+      </c>
+      <c r="W8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="9" spans="8:35">
+      <c r="J9" t="s">
+        <v>295</v>
+      </c>
+      <c r="W9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>616</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="10" spans="8:35">
+      <c r="J10" t="s">
+        <v>296</v>
+      </c>
+      <c r="W10" t="s">
+        <v>588</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>617</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="8:35">
+      <c r="J11" t="s">
+        <v>297</v>
+      </c>
+      <c r="W11" t="s">
+        <v>296</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>618</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="12" spans="8:35">
+      <c r="J12" t="s">
+        <v>298</v>
+      </c>
+      <c r="W12" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>619</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="13" spans="8:35">
+      <c r="J13" t="s">
+        <v>299</v>
+      </c>
+      <c r="W13" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD13" t="s">
         <v>620</v>
       </c>
-      <c r="AC2" t="s">
-        <v>633</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>637</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="3" spans="7:34">
-      <c r="G3" t="s">
-        <v>276</v>
-      </c>
-      <c r="I3" t="s">
-        <v>285</v>
-      </c>
-      <c r="V3" t="s">
-        <v>285</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="AE13" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="14" spans="8:35">
+      <c r="J14" t="s">
+        <v>300</v>
+      </c>
+      <c r="W14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AD14" t="s">
         <v>621</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE14" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="15" spans="8:35">
+      <c r="J15" t="s">
+        <v>301</v>
+      </c>
+      <c r="W15" t="s">
+        <v>589</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="16" spans="8:35">
+      <c r="J16" t="s">
+        <v>302</v>
+      </c>
+      <c r="W16" t="s">
+        <v>300</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="10:31">
+      <c r="J17" t="s">
+        <v>303</v>
+      </c>
+      <c r="W17" t="s">
+        <v>301</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="18" spans="10:31">
+      <c r="J18" t="s">
+        <v>304</v>
+      </c>
+      <c r="W18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="10:31">
+      <c r="J19" t="s">
+        <v>305</v>
+      </c>
+      <c r="W19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="10:31">
+      <c r="J20" t="s">
+        <v>306</v>
+      </c>
+      <c r="W20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="10:31">
+      <c r="J21" t="s">
+        <v>307</v>
+      </c>
+      <c r="W21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="10:31">
+      <c r="J22" t="s">
+        <v>308</v>
+      </c>
+      <c r="W22" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23" spans="10:31">
+      <c r="J23" t="s">
+        <v>309</v>
+      </c>
+      <c r="W23" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" spans="10:31">
+      <c r="J24" t="s">
+        <v>310</v>
+      </c>
+      <c r="W24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="10:31">
+      <c r="J25" t="s">
+        <v>311</v>
+      </c>
+      <c r="W25" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="10:31">
+      <c r="J26" t="s">
+        <v>312</v>
+      </c>
+      <c r="W26" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="10:31">
+      <c r="J27" t="s">
+        <v>313</v>
+      </c>
+      <c r="W27" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="28" spans="10:31">
+      <c r="J28" t="s">
+        <v>314</v>
+      </c>
+      <c r="W28" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" spans="10:31">
+      <c r="J29" t="s">
+        <v>315</v>
+      </c>
+      <c r="W29" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="10:31">
+      <c r="J30" t="s">
+        <v>316</v>
+      </c>
+      <c r="W30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="10:31">
+      <c r="J31" t="s">
+        <v>317</v>
+      </c>
+      <c r="W31" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="10:31">
+      <c r="J32" t="s">
+        <v>318</v>
+      </c>
+      <c r="W32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="10:23">
+      <c r="J33" t="s">
+        <v>319</v>
+      </c>
+      <c r="W33" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="34" spans="10:23">
+      <c r="J34" t="s">
+        <v>320</v>
+      </c>
+      <c r="W34" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="35" spans="10:23">
+      <c r="J35" t="s">
+        <v>321</v>
+      </c>
+      <c r="W35" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="36" spans="10:23">
+      <c r="J36" t="s">
+        <v>322</v>
+      </c>
+      <c r="W36" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" spans="10:23">
+      <c r="J37" t="s">
+        <v>323</v>
+      </c>
+      <c r="W37" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="38" spans="10:23">
+      <c r="J38" t="s">
+        <v>324</v>
+      </c>
+      <c r="W38" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" spans="10:23">
+      <c r="J39" t="s">
+        <v>325</v>
+      </c>
+      <c r="W39" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="40" spans="10:23">
+      <c r="J40" t="s">
+        <v>326</v>
+      </c>
+      <c r="W40" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" spans="10:23">
+      <c r="J41" t="s">
+        <v>327</v>
+      </c>
+      <c r="W41" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="42" spans="10:23">
+      <c r="J42" t="s">
+        <v>328</v>
+      </c>
+      <c r="W42" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" spans="10:23">
+      <c r="J43" t="s">
+        <v>329</v>
+      </c>
+      <c r="W43" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="44" spans="10:23">
+      <c r="J44" t="s">
+        <v>330</v>
+      </c>
+      <c r="W44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="45" spans="10:23">
+      <c r="J45" t="s">
+        <v>331</v>
+      </c>
+      <c r="W45" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="46" spans="10:23">
+      <c r="J46" t="s">
+        <v>332</v>
+      </c>
+      <c r="W46" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="47" spans="10:23">
+      <c r="J47" t="s">
+        <v>333</v>
+      </c>
+      <c r="W47" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48" spans="10:23">
+      <c r="J48" t="s">
+        <v>334</v>
+      </c>
+      <c r="W48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" spans="10:23">
+      <c r="J49" t="s">
+        <v>335</v>
+      </c>
+      <c r="W49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="10:23">
+      <c r="J50" t="s">
+        <v>336</v>
+      </c>
+      <c r="W50" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="51" spans="10:23">
+      <c r="J51" t="s">
+        <v>337</v>
+      </c>
+      <c r="W51" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="52" spans="10:23">
+      <c r="J52" t="s">
+        <v>338</v>
+      </c>
+      <c r="W52" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="10:23">
+      <c r="J53" t="s">
+        <v>339</v>
+      </c>
+      <c r="W53" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="54" spans="10:23">
+      <c r="J54" t="s">
+        <v>340</v>
+      </c>
+      <c r="W54" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="10:23">
+      <c r="J55" t="s">
+        <v>341</v>
+      </c>
+      <c r="W55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="56" spans="10:23">
+      <c r="J56" t="s">
+        <v>342</v>
+      </c>
+      <c r="W56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="10:23">
+      <c r="J57" t="s">
+        <v>343</v>
+      </c>
+      <c r="W57" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="10:23">
+      <c r="J58" t="s">
+        <v>344</v>
+      </c>
+      <c r="W58" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="59" spans="10:23">
+      <c r="J59" t="s">
+        <v>345</v>
+      </c>
+      <c r="W59" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="60" spans="10:23">
+      <c r="J60" t="s">
+        <v>346</v>
+      </c>
+      <c r="W60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="10:23">
+      <c r="J61" t="s">
+        <v>347</v>
+      </c>
+      <c r="W61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="10:23">
+      <c r="J62" t="s">
+        <v>348</v>
+      </c>
+      <c r="W62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="10:23">
+      <c r="J63" t="s">
+        <v>349</v>
+      </c>
+      <c r="W63" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="64" spans="10:23">
+      <c r="J64" t="s">
+        <v>350</v>
+      </c>
+      <c r="W64" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="65" spans="10:23">
+      <c r="J65" t="s">
+        <v>351</v>
+      </c>
+      <c r="W65" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="66" spans="10:23">
+      <c r="J66" t="s">
+        <v>352</v>
+      </c>
+      <c r="W66" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="67" spans="10:23">
+      <c r="J67" t="s">
+        <v>353</v>
+      </c>
+      <c r="W67" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="68" spans="10:23">
+      <c r="J68" t="s">
+        <v>354</v>
+      </c>
+      <c r="W68" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" spans="10:23">
+      <c r="J69" t="s">
+        <v>355</v>
+      </c>
+      <c r="W69" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="10:23">
+      <c r="J70" t="s">
+        <v>356</v>
+      </c>
+      <c r="W70" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="71" spans="10:23">
+      <c r="J71" t="s">
+        <v>357</v>
+      </c>
+      <c r="W71" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="72" spans="10:23">
+      <c r="J72" t="s">
+        <v>358</v>
+      </c>
+      <c r="W72" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="73" spans="10:23">
+      <c r="J73" t="s">
+        <v>359</v>
+      </c>
+      <c r="W73" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="74" spans="10:23">
+      <c r="J74" t="s">
+        <v>360</v>
+      </c>
+      <c r="W74" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="75" spans="10:23">
+      <c r="J75" t="s">
+        <v>361</v>
+      </c>
+      <c r="W75" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="76" spans="10:23">
+      <c r="J76" t="s">
+        <v>362</v>
+      </c>
+      <c r="W76" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="77" spans="10:23">
+      <c r="J77" t="s">
+        <v>363</v>
+      </c>
+      <c r="W77" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="78" spans="10:23">
+      <c r="J78" t="s">
+        <v>364</v>
+      </c>
+      <c r="W78" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="79" spans="10:23">
+      <c r="J79" t="s">
+        <v>365</v>
+      </c>
+      <c r="W79" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="80" spans="10:23">
+      <c r="J80" t="s">
+        <v>366</v>
+      </c>
+      <c r="W80" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" spans="10:23">
+      <c r="J81" t="s">
+        <v>367</v>
+      </c>
+      <c r="W81" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="82" spans="10:23">
+      <c r="J82" t="s">
+        <v>368</v>
+      </c>
+      <c r="W82" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="83" spans="10:23">
+      <c r="J83" t="s">
+        <v>369</v>
+      </c>
+      <c r="W83" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84" spans="10:23">
+      <c r="J84" t="s">
+        <v>370</v>
+      </c>
+      <c r="W84" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" spans="10:23">
+      <c r="J85" t="s">
+        <v>371</v>
+      </c>
+      <c r="W85" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="86" spans="10:23">
+      <c r="J86" t="s">
+        <v>372</v>
+      </c>
+      <c r="W86" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="87" spans="10:23">
+      <c r="J87" t="s">
+        <v>373</v>
+      </c>
+      <c r="W87" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="88" spans="10:23">
+      <c r="J88" t="s">
+        <v>374</v>
+      </c>
+      <c r="W88" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="89" spans="10:23">
+      <c r="J89" t="s">
+        <v>375</v>
+      </c>
+      <c r="W89" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="90" spans="10:23">
+      <c r="J90" t="s">
+        <v>376</v>
+      </c>
+      <c r="W90" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="91" spans="10:23">
+      <c r="J91" t="s">
+        <v>377</v>
+      </c>
+      <c r="W91" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="92" spans="10:23">
+      <c r="J92" t="s">
+        <v>378</v>
+      </c>
+      <c r="W92" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="93" spans="10:23">
+      <c r="J93" t="s">
+        <v>379</v>
+      </c>
+      <c r="W93" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="94" spans="10:23">
+      <c r="J94" t="s">
+        <v>380</v>
+      </c>
+      <c r="W94" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="95" spans="10:23">
+      <c r="J95" t="s">
+        <v>381</v>
+      </c>
+      <c r="W95" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="96" spans="10:23">
+      <c r="J96" t="s">
+        <v>382</v>
+      </c>
+      <c r="W96" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="97" spans="10:23">
+      <c r="J97" t="s">
+        <v>383</v>
+      </c>
+      <c r="W97" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="98" spans="10:23">
+      <c r="J98" t="s">
+        <v>384</v>
+      </c>
+      <c r="W98" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="99" spans="10:23">
+      <c r="J99" t="s">
+        <v>385</v>
+      </c>
+      <c r="W99" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="100" spans="10:23">
+      <c r="J100" t="s">
+        <v>386</v>
+      </c>
+      <c r="W100" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="101" spans="10:23">
+      <c r="J101" t="s">
+        <v>387</v>
+      </c>
+      <c r="W101" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="102" spans="10:23">
+      <c r="J102" t="s">
+        <v>388</v>
+      </c>
+      <c r="W102" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="103" spans="10:23">
+      <c r="J103" t="s">
+        <v>389</v>
+      </c>
+      <c r="W103" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="104" spans="10:23">
+      <c r="J104" t="s">
+        <v>390</v>
+      </c>
+      <c r="W104" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="105" spans="10:23">
+      <c r="J105" t="s">
+        <v>391</v>
+      </c>
+      <c r="W105" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="106" spans="10:23">
+      <c r="J106" t="s">
+        <v>392</v>
+      </c>
+      <c r="W106" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="107" spans="10:23">
+      <c r="J107" t="s">
+        <v>393</v>
+      </c>
+      <c r="W107" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="108" spans="10:23">
+      <c r="J108" t="s">
+        <v>394</v>
+      </c>
+      <c r="W108" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" spans="10:23">
+      <c r="J109" t="s">
+        <v>395</v>
+      </c>
+      <c r="W109" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="110" spans="10:23">
+      <c r="J110" t="s">
+        <v>396</v>
+      </c>
+      <c r="W110" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="111" spans="10:23">
+      <c r="J111" t="s">
+        <v>397</v>
+      </c>
+      <c r="W111" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="112" spans="10:23">
+      <c r="J112" t="s">
+        <v>398</v>
+      </c>
+      <c r="W112" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="113" spans="10:23">
+      <c r="J113" t="s">
+        <v>399</v>
+      </c>
+      <c r="W113" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="114" spans="10:23">
+      <c r="J114" t="s">
+        <v>400</v>
+      </c>
+      <c r="W114" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="115" spans="10:23">
+      <c r="J115" t="s">
+        <v>401</v>
+      </c>
+      <c r="W115" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="116" spans="10:23">
+      <c r="J116" t="s">
+        <v>402</v>
+      </c>
+      <c r="W116" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="117" spans="10:23">
+      <c r="J117" t="s">
+        <v>403</v>
+      </c>
+      <c r="W117" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="118" spans="10:23">
+      <c r="J118" t="s">
+        <v>404</v>
+      </c>
+      <c r="W118" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="119" spans="10:23">
+      <c r="J119" t="s">
+        <v>405</v>
+      </c>
+      <c r="W119" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="120" spans="10:23">
+      <c r="J120" t="s">
+        <v>406</v>
+      </c>
+      <c r="W120" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="121" spans="10:23">
+      <c r="J121" t="s">
+        <v>407</v>
+      </c>
+      <c r="W121" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="122" spans="10:23">
+      <c r="J122" t="s">
+        <v>408</v>
+      </c>
+      <c r="W122" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="123" spans="10:23">
+      <c r="J123" t="s">
+        <v>409</v>
+      </c>
+      <c r="W123" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="124" spans="10:23">
+      <c r="J124" t="s">
+        <v>410</v>
+      </c>
+      <c r="W124" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="125" spans="10:23">
+      <c r="J125" t="s">
+        <v>411</v>
+      </c>
+      <c r="W125" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="126" spans="10:23">
+      <c r="J126" t="s">
+        <v>412</v>
+      </c>
+      <c r="W126" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="127" spans="10:23">
+      <c r="J127" t="s">
+        <v>413</v>
+      </c>
+      <c r="W127" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="128" spans="10:23">
+      <c r="J128" t="s">
+        <v>414</v>
+      </c>
+      <c r="W128" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="129" spans="10:23">
+      <c r="J129" t="s">
+        <v>415</v>
+      </c>
+      <c r="W129" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="130" spans="10:23">
+      <c r="J130" t="s">
+        <v>416</v>
+      </c>
+      <c r="W130" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="131" spans="10:23">
+      <c r="J131" t="s">
+        <v>417</v>
+      </c>
+      <c r="W131" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="132" spans="10:23">
+      <c r="J132" t="s">
+        <v>418</v>
+      </c>
+      <c r="W132" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="10:23">
+      <c r="J133" t="s">
+        <v>419</v>
+      </c>
+      <c r="W133" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="134" spans="10:23">
+      <c r="J134" t="s">
+        <v>420</v>
+      </c>
+      <c r="W134" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="135" spans="10:23">
+      <c r="J135" t="s">
+        <v>421</v>
+      </c>
+      <c r="W135" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="136" spans="10:23">
+      <c r="J136" t="s">
+        <v>422</v>
+      </c>
+      <c r="W136" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="137" spans="10:23">
+      <c r="J137" t="s">
+        <v>423</v>
+      </c>
+      <c r="W137" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="138" spans="10:23">
+      <c r="J138" t="s">
+        <v>424</v>
+      </c>
+      <c r="W138" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="139" spans="10:23">
+      <c r="J139" t="s">
+        <v>425</v>
+      </c>
+      <c r="W139" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="140" spans="10:23">
+      <c r="J140" t="s">
+        <v>426</v>
+      </c>
+      <c r="W140" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="141" spans="10:23">
+      <c r="J141" t="s">
+        <v>427</v>
+      </c>
+      <c r="W141" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="142" spans="10:23">
+      <c r="J142" t="s">
+        <v>428</v>
+      </c>
+      <c r="W142" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="143" spans="10:23">
+      <c r="J143" t="s">
+        <v>429</v>
+      </c>
+      <c r="W143" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="144" spans="10:23">
+      <c r="J144" t="s">
+        <v>430</v>
+      </c>
+      <c r="W144" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="145" spans="10:23">
+      <c r="J145" t="s">
+        <v>431</v>
+      </c>
+      <c r="W145" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="146" spans="10:23">
+      <c r="J146" t="s">
+        <v>432</v>
+      </c>
+      <c r="W146" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="147" spans="10:23">
+      <c r="J147" t="s">
+        <v>433</v>
+      </c>
+      <c r="W147" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="148" spans="10:23">
+      <c r="J148" t="s">
+        <v>434</v>
+      </c>
+      <c r="W148" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="149" spans="10:23">
+      <c r="J149" t="s">
+        <v>435</v>
+      </c>
+      <c r="W149" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="150" spans="10:23">
+      <c r="J150" t="s">
+        <v>436</v>
+      </c>
+      <c r="W150" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="151" spans="10:23">
+      <c r="J151" t="s">
+        <v>437</v>
+      </c>
+      <c r="W151" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="152" spans="10:23">
+      <c r="J152" t="s">
+        <v>438</v>
+      </c>
+      <c r="W152" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="153" spans="10:23">
+      <c r="J153" t="s">
+        <v>439</v>
+      </c>
+      <c r="W153" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="154" spans="10:23">
+      <c r="J154" t="s">
+        <v>440</v>
+      </c>
+      <c r="W154" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="155" spans="10:23">
+      <c r="J155" t="s">
+        <v>441</v>
+      </c>
+      <c r="W155" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="156" spans="10:23">
+      <c r="J156" t="s">
+        <v>442</v>
+      </c>
+      <c r="W156" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="157" spans="10:23">
+      <c r="J157" t="s">
+        <v>443</v>
+      </c>
+      <c r="W157" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="158" spans="10:23">
+      <c r="J158" t="s">
+        <v>444</v>
+      </c>
+      <c r="W158" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="159" spans="10:23">
+      <c r="J159" t="s">
+        <v>445</v>
+      </c>
+      <c r="W159" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="160" spans="10:23">
+      <c r="J160" t="s">
+        <v>446</v>
+      </c>
+      <c r="W160" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="161" spans="10:23">
+      <c r="J161" t="s">
+        <v>447</v>
+      </c>
+      <c r="W161" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="162" spans="10:23">
+      <c r="J162" t="s">
+        <v>448</v>
+      </c>
+      <c r="W162" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="163" spans="10:23">
+      <c r="J163" t="s">
+        <v>449</v>
+      </c>
+      <c r="W163" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="164" spans="10:23">
+      <c r="J164" t="s">
+        <v>450</v>
+      </c>
+      <c r="W164" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="165" spans="10:23">
+      <c r="J165" t="s">
+        <v>451</v>
+      </c>
+      <c r="W165" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="166" spans="10:23">
+      <c r="J166" t="s">
+        <v>452</v>
+      </c>
+      <c r="W166" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="167" spans="10:23">
+      <c r="J167" t="s">
+        <v>453</v>
+      </c>
+      <c r="W167" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="168" spans="10:23">
+      <c r="J168" t="s">
+        <v>454</v>
+      </c>
+      <c r="W168" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="169" spans="10:23">
+      <c r="J169" t="s">
+        <v>455</v>
+      </c>
+      <c r="W169" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="170" spans="10:23">
+      <c r="J170" t="s">
+        <v>456</v>
+      </c>
+      <c r="W170" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="171" spans="10:23">
+      <c r="J171" t="s">
+        <v>457</v>
+      </c>
+      <c r="W171" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="172" spans="10:23">
+      <c r="J172" t="s">
+        <v>458</v>
+      </c>
+      <c r="W172" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="173" spans="10:23">
+      <c r="J173" t="s">
+        <v>459</v>
+      </c>
+      <c r="W173" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="174" spans="10:23">
+      <c r="J174" t="s">
+        <v>460</v>
+      </c>
+      <c r="W174" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="175" spans="10:23">
+      <c r="J175" t="s">
+        <v>461</v>
+      </c>
+      <c r="W175" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="176" spans="10:23">
+      <c r="J176" t="s">
+        <v>462</v>
+      </c>
+      <c r="W176" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="177" spans="10:23">
+      <c r="J177" t="s">
+        <v>463</v>
+      </c>
+      <c r="W177" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="178" spans="10:23">
+      <c r="J178" t="s">
+        <v>464</v>
+      </c>
+      <c r="W178" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="179" spans="10:23">
+      <c r="J179" t="s">
+        <v>465</v>
+      </c>
+      <c r="W179" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="180" spans="10:23">
+      <c r="J180" t="s">
+        <v>466</v>
+      </c>
+      <c r="W180" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="181" spans="10:23">
+      <c r="J181" t="s">
+        <v>467</v>
+      </c>
+      <c r="W181" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="182" spans="10:23">
+      <c r="J182" t="s">
+        <v>468</v>
+      </c>
+      <c r="W182" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="183" spans="10:23">
+      <c r="J183" t="s">
+        <v>469</v>
+      </c>
+      <c r="W183" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="184" spans="10:23">
+      <c r="J184" t="s">
+        <v>470</v>
+      </c>
+      <c r="W184" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="185" spans="10:23">
+      <c r="J185" t="s">
+        <v>471</v>
+      </c>
+      <c r="W185" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="186" spans="10:23">
+      <c r="J186" t="s">
+        <v>472</v>
+      </c>
+      <c r="W186" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="187" spans="10:23">
+      <c r="J187" t="s">
+        <v>473</v>
+      </c>
+      <c r="W187" t="s">
         <v>603</v>
       </c>
-      <c r="AD3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="4" spans="7:34">
-      <c r="I4" t="s">
-        <v>286</v>
-      </c>
-      <c r="V4" t="s">
-        <v>286</v>
-      </c>
-      <c r="AC4" t="s">
+    </row>
+    <row r="188" spans="10:23">
+      <c r="J188" t="s">
+        <v>474</v>
+      </c>
+      <c r="W188" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="189" spans="10:23">
+      <c r="J189" t="s">
+        <v>475</v>
+      </c>
+      <c r="W189" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="190" spans="10:23">
+      <c r="J190" t="s">
+        <v>476</v>
+      </c>
+      <c r="W190" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="191" spans="10:23">
+      <c r="J191" t="s">
+        <v>477</v>
+      </c>
+      <c r="W191" t="s">
         <v>604</v>
       </c>
-      <c r="AD4" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="5" spans="7:34">
-      <c r="I5" t="s">
-        <v>287</v>
-      </c>
-      <c r="V5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AC5" t="s">
+    </row>
+    <row r="192" spans="10:23">
+      <c r="J192" t="s">
+        <v>478</v>
+      </c>
+      <c r="W192" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="193" spans="10:23">
+      <c r="J193" t="s">
+        <v>479</v>
+      </c>
+      <c r="W193" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="194" spans="10:23">
+      <c r="J194" t="s">
+        <v>480</v>
+      </c>
+      <c r="W194" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="195" spans="10:23">
+      <c r="J195" t="s">
+        <v>481</v>
+      </c>
+      <c r="W195" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="196" spans="10:23">
+      <c r="J196" t="s">
+        <v>482</v>
+      </c>
+      <c r="W196" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="197" spans="10:23">
+      <c r="J197" t="s">
+        <v>483</v>
+      </c>
+      <c r="W197" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="198" spans="10:23">
+      <c r="J198" t="s">
+        <v>484</v>
+      </c>
+      <c r="W198" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="199" spans="10:23">
+      <c r="J199" t="s">
+        <v>485</v>
+      </c>
+      <c r="W199" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="200" spans="10:23">
+      <c r="J200" t="s">
+        <v>486</v>
+      </c>
+      <c r="W200" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="201" spans="10:23">
+      <c r="J201" t="s">
+        <v>487</v>
+      </c>
+      <c r="W201" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="202" spans="10:23">
+      <c r="J202" t="s">
+        <v>488</v>
+      </c>
+      <c r="W202" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="203" spans="10:23">
+      <c r="J203" t="s">
+        <v>489</v>
+      </c>
+      <c r="W203" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="204" spans="10:23">
+      <c r="J204" t="s">
+        <v>490</v>
+      </c>
+      <c r="W204" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="205" spans="10:23">
+      <c r="J205" t="s">
+        <v>491</v>
+      </c>
+      <c r="W205" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="206" spans="10:23">
+      <c r="J206" t="s">
+        <v>492</v>
+      </c>
+      <c r="W206" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="207" spans="10:23">
+      <c r="J207" t="s">
+        <v>493</v>
+      </c>
+      <c r="W207" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="208" spans="10:23">
+      <c r="J208" t="s">
+        <v>494</v>
+      </c>
+      <c r="W208" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="209" spans="10:23">
+      <c r="J209" t="s">
+        <v>495</v>
+      </c>
+      <c r="W209" t="s">
         <v>605</v>
       </c>
-      <c r="AD5" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="6" spans="7:34">
-      <c r="I6" t="s">
-        <v>288</v>
-      </c>
-      <c r="V6" t="s">
-        <v>288</v>
-      </c>
-      <c r="AC6" t="s">
+    </row>
+    <row r="210" spans="10:23">
+      <c r="J210" t="s">
+        <v>496</v>
+      </c>
+      <c r="W210" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="211" spans="10:23">
+      <c r="J211" t="s">
+        <v>497</v>
+      </c>
+      <c r="W211" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="212" spans="10:23">
+      <c r="J212" t="s">
+        <v>498</v>
+      </c>
+      <c r="W212" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="213" spans="10:23">
+      <c r="J213" t="s">
+        <v>499</v>
+      </c>
+      <c r="W213" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="214" spans="10:23">
+      <c r="J214" t="s">
+        <v>500</v>
+      </c>
+      <c r="W214" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="215" spans="10:23">
+      <c r="J215" t="s">
+        <v>501</v>
+      </c>
+      <c r="W215" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="216" spans="10:23">
+      <c r="J216" t="s">
+        <v>502</v>
+      </c>
+      <c r="W216" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="217" spans="10:23">
+      <c r="J217" t="s">
+        <v>503</v>
+      </c>
+      <c r="W217" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="218" spans="10:23">
+      <c r="J218" t="s">
+        <v>504</v>
+      </c>
+      <c r="W218" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="219" spans="10:23">
+      <c r="J219" t="s">
+        <v>505</v>
+      </c>
+      <c r="W219" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="220" spans="10:23">
+      <c r="J220" t="s">
+        <v>506</v>
+      </c>
+      <c r="W220" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="221" spans="10:23">
+      <c r="J221" t="s">
+        <v>507</v>
+      </c>
+      <c r="W221" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="222" spans="10:23">
+      <c r="J222" t="s">
+        <v>508</v>
+      </c>
+      <c r="W222" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223" spans="10:23">
+      <c r="J223" t="s">
+        <v>509</v>
+      </c>
+      <c r="W223" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="224" spans="10:23">
+      <c r="J224" t="s">
+        <v>510</v>
+      </c>
+      <c r="W224" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="225" spans="10:23">
+      <c r="J225" t="s">
+        <v>511</v>
+      </c>
+      <c r="W225" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="226" spans="10:23">
+      <c r="J226" t="s">
+        <v>512</v>
+      </c>
+      <c r="W226" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="227" spans="10:23">
+      <c r="J227" t="s">
+        <v>513</v>
+      </c>
+      <c r="W227" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="228" spans="10:23">
+      <c r="J228" t="s">
+        <v>514</v>
+      </c>
+      <c r="W228" t="s">
         <v>606</v>
       </c>
-      <c r="AD6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="7" spans="7:34">
-      <c r="I7" t="s">
-        <v>289</v>
-      </c>
-      <c r="V7" t="s">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="s">
+    </row>
+    <row r="229" spans="10:23">
+      <c r="J229" t="s">
+        <v>515</v>
+      </c>
+      <c r="W229" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="230" spans="10:23">
+      <c r="J230" t="s">
+        <v>516</v>
+      </c>
+      <c r="W230" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="231" spans="10:23">
+      <c r="J231" t="s">
+        <v>517</v>
+      </c>
+      <c r="W231" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="232" spans="10:23">
+      <c r="J232" t="s">
+        <v>518</v>
+      </c>
+      <c r="W232" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="233" spans="10:23">
+      <c r="J233" t="s">
+        <v>519</v>
+      </c>
+      <c r="W233" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="234" spans="10:23">
+      <c r="J234" t="s">
+        <v>520</v>
+      </c>
+      <c r="W234" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="235" spans="10:23">
+      <c r="J235" t="s">
+        <v>521</v>
+      </c>
+      <c r="W235" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="236" spans="10:23">
+      <c r="J236" t="s">
+        <v>522</v>
+      </c>
+      <c r="W236" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="237" spans="10:23">
+      <c r="J237" t="s">
+        <v>523</v>
+      </c>
+      <c r="W237" t="s">
         <v>607</v>
       </c>
-      <c r="AD7" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="8" spans="7:34">
-      <c r="I8" t="s">
-        <v>290</v>
-      </c>
-      <c r="V8" t="s">
-        <v>290</v>
-      </c>
-      <c r="AC8" t="s">
+    </row>
+    <row r="238" spans="10:23">
+      <c r="J238" t="s">
+        <v>524</v>
+      </c>
+      <c r="W238" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="239" spans="10:23">
+      <c r="J239" t="s">
+        <v>525</v>
+      </c>
+      <c r="W239" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="240" spans="10:23">
+      <c r="J240" t="s">
+        <v>526</v>
+      </c>
+      <c r="W240" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="241" spans="10:23">
+      <c r="J241" t="s">
+        <v>527</v>
+      </c>
+      <c r="W241" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="242" spans="10:23">
+      <c r="J242" t="s">
+        <v>528</v>
+      </c>
+      <c r="W242" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="243" spans="10:23">
+      <c r="J243" t="s">
+        <v>529</v>
+      </c>
+      <c r="W243" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="244" spans="10:23">
+      <c r="J244" t="s">
+        <v>530</v>
+      </c>
+      <c r="W244" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="245" spans="10:23">
+      <c r="J245" t="s">
+        <v>531</v>
+      </c>
+      <c r="W245" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="246" spans="10:23">
+      <c r="J246" t="s">
+        <v>532</v>
+      </c>
+      <c r="W246" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="247" spans="10:23">
+      <c r="J247" t="s">
+        <v>533</v>
+      </c>
+      <c r="W247" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="248" spans="10:23">
+      <c r="J248" t="s">
+        <v>534</v>
+      </c>
+      <c r="W248" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="249" spans="10:23">
+      <c r="J249" t="s">
+        <v>535</v>
+      </c>
+      <c r="W249" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="250" spans="10:23">
+      <c r="J250" t="s">
+        <v>536</v>
+      </c>
+      <c r="W250" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="251" spans="10:23">
+      <c r="J251" t="s">
+        <v>537</v>
+      </c>
+      <c r="W251" t="s">
         <v>608</v>
       </c>
-      <c r="AD8" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="9" spans="7:34">
-      <c r="I9" t="s">
-        <v>291</v>
-      </c>
-      <c r="V9" t="s">
-        <v>291</v>
-      </c>
-      <c r="AC9" t="s">
+    </row>
+    <row r="252" spans="10:23">
+      <c r="J252" t="s">
+        <v>538</v>
+      </c>
+      <c r="W252" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="253" spans="10:23">
+      <c r="J253" t="s">
+        <v>539</v>
+      </c>
+      <c r="W253" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="254" spans="10:23">
+      <c r="J254" t="s">
+        <v>540</v>
+      </c>
+      <c r="W254" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="255" spans="10:23">
+      <c r="J255" t="s">
+        <v>541</v>
+      </c>
+      <c r="W255" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="256" spans="10:23">
+      <c r="J256" t="s">
+        <v>542</v>
+      </c>
+      <c r="W256" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="257" spans="10:23">
+      <c r="J257" t="s">
+        <v>543</v>
+      </c>
+      <c r="W257" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="258" spans="10:23">
+      <c r="J258" t="s">
+        <v>544</v>
+      </c>
+      <c r="W258" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="259" spans="10:23">
+      <c r="J259" t="s">
+        <v>545</v>
+      </c>
+      <c r="W259" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="260" spans="10:23">
+      <c r="J260" t="s">
+        <v>546</v>
+      </c>
+      <c r="W260" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="261" spans="10:23">
+      <c r="J261" t="s">
+        <v>547</v>
+      </c>
+      <c r="W261" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="262" spans="10:23">
+      <c r="J262" t="s">
+        <v>548</v>
+      </c>
+      <c r="W262" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="263" spans="10:23">
+      <c r="J263" t="s">
+        <v>549</v>
+      </c>
+      <c r="W263" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="264" spans="10:23">
+      <c r="J264" t="s">
+        <v>550</v>
+      </c>
+      <c r="W264" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="265" spans="10:23">
+      <c r="J265" t="s">
+        <v>551</v>
+      </c>
+      <c r="W265" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="266" spans="10:23">
+      <c r="J266" t="s">
+        <v>552</v>
+      </c>
+      <c r="W266" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="267" spans="10:23">
+      <c r="J267" t="s">
+        <v>553</v>
+      </c>
+      <c r="W267" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="268" spans="10:23">
+      <c r="J268" t="s">
+        <v>554</v>
+      </c>
+      <c r="W268" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="269" spans="10:23">
+      <c r="J269" t="s">
+        <v>555</v>
+      </c>
+      <c r="W269" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="270" spans="10:23">
+      <c r="J270" t="s">
+        <v>556</v>
+      </c>
+      <c r="W270" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="271" spans="10:23">
+      <c r="J271" t="s">
+        <v>557</v>
+      </c>
+      <c r="W271" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="272" spans="10:23">
+      <c r="J272" t="s">
+        <v>558</v>
+      </c>
+      <c r="W272" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="273" spans="10:23">
+      <c r="J273" t="s">
+        <v>559</v>
+      </c>
+      <c r="W273" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="274" spans="10:23">
+      <c r="W274" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="275" spans="10:23">
+      <c r="W275" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="276" spans="10:23">
+      <c r="W276" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="277" spans="10:23">
+      <c r="W277" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="278" spans="10:23">
+      <c r="W278" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="279" spans="10:23">
+      <c r="W279" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="280" spans="10:23">
+      <c r="W280" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="281" spans="10:23">
+      <c r="W281" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="282" spans="10:23">
+      <c r="W282" t="s">
         <v>609</v>
       </c>
-      <c r="AD9" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="10" spans="7:34">
-      <c r="I10" t="s">
-        <v>292</v>
-      </c>
-      <c r="V10" t="s">
-        <v>584</v>
-      </c>
-      <c r="AC10" t="s">
+    </row>
+    <row r="283" spans="10:23">
+      <c r="W283" t="s">
         <v>610</v>
       </c>
-      <c r="AD10" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="11" spans="7:34">
-      <c r="I11" t="s">
-        <v>293</v>
-      </c>
-      <c r="V11" t="s">
-        <v>292</v>
-      </c>
-      <c r="AC11" t="s">
+    </row>
+    <row r="284" spans="10:23">
+      <c r="W284" t="s">
         <v>611</v>
       </c>
-      <c r="AD11" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="12" spans="7:34">
-      <c r="I12" t="s">
-        <v>294</v>
-      </c>
-      <c r="V12" t="s">
-        <v>293</v>
-      </c>
-      <c r="AC12" t="s">
+    </row>
+    <row r="285" spans="10:23">
+      <c r="W285" t="s">
         <v>612</v>
       </c>
-      <c r="AD12" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="13" spans="7:34">
-      <c r="I13" t="s">
-        <v>295</v>
-      </c>
-      <c r="V13" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC13" t="s">
+    </row>
+    <row r="286" spans="10:23">
+      <c r="W286" t="s">
         <v>613</v>
       </c>
-      <c r="AD13" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="14" spans="7:34">
-      <c r="I14" t="s">
-        <v>296</v>
-      </c>
-      <c r="V14" t="s">
-        <v>295</v>
-      </c>
-      <c r="AC14" t="s">
+    </row>
+    <row r="287" spans="10:23">
+      <c r="W287" t="s">
         <v>614</v>
       </c>
-      <c r="AD14" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="15" spans="7:34">
-      <c r="I15" t="s">
-        <v>297</v>
-      </c>
-      <c r="V15" t="s">
-        <v>585</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="16" spans="7:34">
-      <c r="I16" t="s">
-        <v>298</v>
-      </c>
-      <c r="V16" t="s">
-        <v>296</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="9:30">
-      <c r="I17" t="s">
-        <v>299</v>
-      </c>
-      <c r="V17" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="18" spans="9:30">
-      <c r="I18" t="s">
-        <v>300</v>
-      </c>
-      <c r="V18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="19" spans="9:30">
-      <c r="I19" t="s">
-        <v>301</v>
-      </c>
-      <c r="V19" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" spans="9:30">
-      <c r="I20" t="s">
-        <v>302</v>
-      </c>
-      <c r="V20" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="9:30">
-      <c r="I21" t="s">
-        <v>303</v>
-      </c>
-      <c r="V21" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="9:30">
-      <c r="I22" t="s">
-        <v>304</v>
-      </c>
-      <c r="V22" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="23" spans="9:30">
-      <c r="I23" t="s">
-        <v>305</v>
-      </c>
-      <c r="V23" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="24" spans="9:30">
-      <c r="I24" t="s">
-        <v>306</v>
-      </c>
-      <c r="V24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="9:30">
-      <c r="I25" t="s">
-        <v>307</v>
-      </c>
-      <c r="V25" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="26" spans="9:30">
-      <c r="I26" t="s">
-        <v>308</v>
-      </c>
-      <c r="V26" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="27" spans="9:30">
-      <c r="I27" t="s">
-        <v>309</v>
-      </c>
-      <c r="V27" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="28" spans="9:30">
-      <c r="I28" t="s">
-        <v>310</v>
-      </c>
-      <c r="V28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="29" spans="9:30">
-      <c r="I29" t="s">
-        <v>311</v>
-      </c>
-      <c r="V29" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="30" spans="9:30">
-      <c r="I30" t="s">
-        <v>312</v>
-      </c>
-      <c r="V30" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="9:30">
-      <c r="I31" t="s">
-        <v>313</v>
-      </c>
-      <c r="V31" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32" spans="9:30">
-      <c r="I32" t="s">
-        <v>314</v>
-      </c>
-      <c r="V32" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="33" spans="9:22">
-      <c r="I33" t="s">
-        <v>315</v>
-      </c>
-      <c r="V33" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="34" spans="9:22">
-      <c r="I34" t="s">
-        <v>316</v>
-      </c>
-      <c r="V34" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="35" spans="9:22">
-      <c r="I35" t="s">
-        <v>317</v>
-      </c>
-      <c r="V35" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="36" spans="9:22">
-      <c r="I36" t="s">
-        <v>318</v>
-      </c>
-      <c r="V36" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="37" spans="9:22">
-      <c r="I37" t="s">
-        <v>319</v>
-      </c>
-      <c r="V37" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="38" spans="9:22">
-      <c r="I38" t="s">
-        <v>320</v>
-      </c>
-      <c r="V38" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="39" spans="9:22">
-      <c r="I39" t="s">
-        <v>321</v>
-      </c>
-      <c r="V39" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="40" spans="9:22">
-      <c r="I40" t="s">
-        <v>322</v>
-      </c>
-      <c r="V40" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="41" spans="9:22">
-      <c r="I41" t="s">
-        <v>323</v>
-      </c>
-      <c r="V41" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="42" spans="9:22">
-      <c r="I42" t="s">
-        <v>324</v>
-      </c>
-      <c r="V42" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="43" spans="9:22">
-      <c r="I43" t="s">
-        <v>325</v>
-      </c>
-      <c r="V43" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="44" spans="9:22">
-      <c r="I44" t="s">
-        <v>326</v>
-      </c>
-      <c r="V44" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="45" spans="9:22">
-      <c r="I45" t="s">
-        <v>327</v>
-      </c>
-      <c r="V45" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="46" spans="9:22">
-      <c r="I46" t="s">
-        <v>328</v>
-      </c>
-      <c r="V46" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="47" spans="9:22">
-      <c r="I47" t="s">
-        <v>329</v>
-      </c>
-      <c r="V47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="48" spans="9:22">
-      <c r="I48" t="s">
-        <v>330</v>
-      </c>
-      <c r="V48" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="49" spans="9:22">
-      <c r="I49" t="s">
-        <v>331</v>
-      </c>
-      <c r="V49" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="50" spans="9:22">
-      <c r="I50" t="s">
-        <v>332</v>
-      </c>
-      <c r="V50" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="51" spans="9:22">
-      <c r="I51" t="s">
-        <v>333</v>
-      </c>
-      <c r="V51" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="52" spans="9:22">
-      <c r="I52" t="s">
-        <v>334</v>
-      </c>
-      <c r="V52" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="53" spans="9:22">
-      <c r="I53" t="s">
-        <v>335</v>
-      </c>
-      <c r="V53" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="54" spans="9:22">
-      <c r="I54" t="s">
-        <v>336</v>
-      </c>
-      <c r="V54" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="55" spans="9:22">
-      <c r="I55" t="s">
-        <v>337</v>
-      </c>
-      <c r="V55" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="56" spans="9:22">
-      <c r="I56" t="s">
-        <v>338</v>
-      </c>
-      <c r="V56" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="57" spans="9:22">
-      <c r="I57" t="s">
-        <v>339</v>
-      </c>
-      <c r="V57" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="58" spans="9:22">
-      <c r="I58" t="s">
-        <v>340</v>
-      </c>
-      <c r="V58" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="59" spans="9:22">
-      <c r="I59" t="s">
-        <v>341</v>
-      </c>
-      <c r="V59" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="60" spans="9:22">
-      <c r="I60" t="s">
-        <v>342</v>
-      </c>
-      <c r="V60" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="61" spans="9:22">
-      <c r="I61" t="s">
-        <v>343</v>
-      </c>
-      <c r="V61" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="62" spans="9:22">
-      <c r="I62" t="s">
-        <v>344</v>
-      </c>
-      <c r="V62" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="63" spans="9:22">
-      <c r="I63" t="s">
-        <v>345</v>
-      </c>
-      <c r="V63" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="64" spans="9:22">
-      <c r="I64" t="s">
-        <v>346</v>
-      </c>
-      <c r="V64" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="65" spans="9:22">
-      <c r="I65" t="s">
-        <v>347</v>
-      </c>
-      <c r="V65" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="66" spans="9:22">
-      <c r="I66" t="s">
-        <v>348</v>
-      </c>
-      <c r="V66" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="67" spans="9:22">
-      <c r="I67" t="s">
-        <v>349</v>
-      </c>
-      <c r="V67" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="68" spans="9:22">
-      <c r="I68" t="s">
-        <v>350</v>
-      </c>
-      <c r="V68" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="69" spans="9:22">
-      <c r="I69" t="s">
-        <v>351</v>
-      </c>
-      <c r="V69" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="70" spans="9:22">
-      <c r="I70" t="s">
-        <v>352</v>
-      </c>
-      <c r="V70" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="71" spans="9:22">
-      <c r="I71" t="s">
-        <v>353</v>
-      </c>
-      <c r="V71" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="9:22">
-      <c r="I72" t="s">
-        <v>354</v>
-      </c>
-      <c r="V72" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="73" spans="9:22">
-      <c r="I73" t="s">
-        <v>355</v>
-      </c>
-      <c r="V73" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="74" spans="9:22">
-      <c r="I74" t="s">
-        <v>356</v>
-      </c>
-      <c r="V74" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="75" spans="9:22">
-      <c r="I75" t="s">
-        <v>357</v>
-      </c>
-      <c r="V75" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="76" spans="9:22">
-      <c r="I76" t="s">
-        <v>358</v>
-      </c>
-      <c r="V76" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="77" spans="9:22">
-      <c r="I77" t="s">
-        <v>359</v>
-      </c>
-      <c r="V77" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="9:22">
-      <c r="I78" t="s">
-        <v>360</v>
-      </c>
-      <c r="V78" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="79" spans="9:22">
-      <c r="I79" t="s">
-        <v>361</v>
-      </c>
-      <c r="V79" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="80" spans="9:22">
-      <c r="I80" t="s">
-        <v>362</v>
-      </c>
-      <c r="V80" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="81" spans="9:22">
-      <c r="I81" t="s">
-        <v>363</v>
-      </c>
-      <c r="V81" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="82" spans="9:22">
-      <c r="I82" t="s">
-        <v>364</v>
-      </c>
-      <c r="V82" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="83" spans="9:22">
-      <c r="I83" t="s">
-        <v>365</v>
-      </c>
-      <c r="V83" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="84" spans="9:22">
-      <c r="I84" t="s">
-        <v>366</v>
-      </c>
-      <c r="V84" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="85" spans="9:22">
-      <c r="I85" t="s">
-        <v>367</v>
-      </c>
-      <c r="V85" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="86" spans="9:22">
-      <c r="I86" t="s">
-        <v>368</v>
-      </c>
-      <c r="V86" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="87" spans="9:22">
-      <c r="I87" t="s">
-        <v>369</v>
-      </c>
-      <c r="V87" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="88" spans="9:22">
-      <c r="I88" t="s">
-        <v>370</v>
-      </c>
-      <c r="V88" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="89" spans="9:22">
-      <c r="I89" t="s">
-        <v>371</v>
-      </c>
-      <c r="V89" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="90" spans="9:22">
-      <c r="I90" t="s">
-        <v>372</v>
-      </c>
-      <c r="V90" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="91" spans="9:22">
-      <c r="I91" t="s">
-        <v>373</v>
-      </c>
-      <c r="V91" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="92" spans="9:22">
-      <c r="I92" t="s">
-        <v>374</v>
-      </c>
-      <c r="V92" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="93" spans="9:22">
-      <c r="I93" t="s">
-        <v>375</v>
-      </c>
-      <c r="V93" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="94" spans="9:22">
-      <c r="I94" t="s">
-        <v>376</v>
-      </c>
-      <c r="V94" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="95" spans="9:22">
-      <c r="I95" t="s">
-        <v>377</v>
-      </c>
-      <c r="V95" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="96" spans="9:22">
-      <c r="I96" t="s">
-        <v>378</v>
-      </c>
-      <c r="V96" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="97" spans="9:22">
-      <c r="I97" t="s">
-        <v>379</v>
-      </c>
-      <c r="V97" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="98" spans="9:22">
-      <c r="I98" t="s">
-        <v>380</v>
-      </c>
-      <c r="V98" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="99" spans="9:22">
-      <c r="I99" t="s">
-        <v>381</v>
-      </c>
-      <c r="V99" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="100" spans="9:22">
-      <c r="I100" t="s">
-        <v>382</v>
-      </c>
-      <c r="V100" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="101" spans="9:22">
-      <c r="I101" t="s">
-        <v>383</v>
-      </c>
-      <c r="V101" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="102" spans="9:22">
-      <c r="I102" t="s">
-        <v>384</v>
-      </c>
-      <c r="V102" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="103" spans="9:22">
-      <c r="I103" t="s">
-        <v>385</v>
-      </c>
-      <c r="V103" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="104" spans="9:22">
-      <c r="I104" t="s">
-        <v>386</v>
-      </c>
-      <c r="V104" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="105" spans="9:22">
-      <c r="I105" t="s">
-        <v>387</v>
-      </c>
-      <c r="V105" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="106" spans="9:22">
-      <c r="I106" t="s">
-        <v>388</v>
-      </c>
-      <c r="V106" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="107" spans="9:22">
-      <c r="I107" t="s">
-        <v>389</v>
-      </c>
-      <c r="V107" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="108" spans="9:22">
-      <c r="I108" t="s">
-        <v>390</v>
-      </c>
-      <c r="V108" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="109" spans="9:22">
-      <c r="I109" t="s">
-        <v>391</v>
-      </c>
-      <c r="V109" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="110" spans="9:22">
-      <c r="I110" t="s">
-        <v>392</v>
-      </c>
-      <c r="V110" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="111" spans="9:22">
-      <c r="I111" t="s">
-        <v>393</v>
-      </c>
-      <c r="V111" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="112" spans="9:22">
-      <c r="I112" t="s">
-        <v>394</v>
-      </c>
-      <c r="V112" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="113" spans="9:22">
-      <c r="I113" t="s">
-        <v>395</v>
-      </c>
-      <c r="V113" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="114" spans="9:22">
-      <c r="I114" t="s">
-        <v>396</v>
-      </c>
-      <c r="V114" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="115" spans="9:22">
-      <c r="I115" t="s">
-        <v>397</v>
-      </c>
-      <c r="V115" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="116" spans="9:22">
-      <c r="I116" t="s">
-        <v>398</v>
-      </c>
-      <c r="V116" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="117" spans="9:22">
-      <c r="I117" t="s">
-        <v>399</v>
-      </c>
-      <c r="V117" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="118" spans="9:22">
-      <c r="I118" t="s">
-        <v>400</v>
-      </c>
-      <c r="V118" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="119" spans="9:22">
-      <c r="I119" t="s">
-        <v>401</v>
-      </c>
-      <c r="V119" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="120" spans="9:22">
-      <c r="I120" t="s">
-        <v>402</v>
-      </c>
-      <c r="V120" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="121" spans="9:22">
-      <c r="I121" t="s">
-        <v>403</v>
-      </c>
-      <c r="V121" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="122" spans="9:22">
-      <c r="I122" t="s">
-        <v>404</v>
-      </c>
-      <c r="V122" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="123" spans="9:22">
-      <c r="I123" t="s">
-        <v>405</v>
-      </c>
-      <c r="V123" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="124" spans="9:22">
-      <c r="I124" t="s">
-        <v>406</v>
-      </c>
-      <c r="V124" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="125" spans="9:22">
-      <c r="I125" t="s">
-        <v>407</v>
-      </c>
-      <c r="V125" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="126" spans="9:22">
-      <c r="I126" t="s">
-        <v>408</v>
-      </c>
-      <c r="V126" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="127" spans="9:22">
-      <c r="I127" t="s">
-        <v>409</v>
-      </c>
-      <c r="V127" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="128" spans="9:22">
-      <c r="I128" t="s">
-        <v>410</v>
-      </c>
-      <c r="V128" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="129" spans="9:22">
-      <c r="I129" t="s">
-        <v>411</v>
-      </c>
-      <c r="V129" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="130" spans="9:22">
-      <c r="I130" t="s">
-        <v>412</v>
-      </c>
-      <c r="V130" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="131" spans="9:22">
-      <c r="I131" t="s">
-        <v>413</v>
-      </c>
-      <c r="V131" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="132" spans="9:22">
-      <c r="I132" t="s">
-        <v>414</v>
-      </c>
-      <c r="V132" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="133" spans="9:22">
-      <c r="I133" t="s">
-        <v>415</v>
-      </c>
-      <c r="V133" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="134" spans="9:22">
-      <c r="I134" t="s">
-        <v>416</v>
-      </c>
-      <c r="V134" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="135" spans="9:22">
-      <c r="I135" t="s">
-        <v>417</v>
-      </c>
-      <c r="V135" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="136" spans="9:22">
-      <c r="I136" t="s">
-        <v>418</v>
-      </c>
-      <c r="V136" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="137" spans="9:22">
-      <c r="I137" t="s">
-        <v>419</v>
-      </c>
-      <c r="V137" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="138" spans="9:22">
-      <c r="I138" t="s">
-        <v>420</v>
-      </c>
-      <c r="V138" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="139" spans="9:22">
-      <c r="I139" t="s">
-        <v>421</v>
-      </c>
-      <c r="V139" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="140" spans="9:22">
-      <c r="I140" t="s">
-        <v>422</v>
-      </c>
-      <c r="V140" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="141" spans="9:22">
-      <c r="I141" t="s">
-        <v>423</v>
-      </c>
-      <c r="V141" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="142" spans="9:22">
-      <c r="I142" t="s">
-        <v>424</v>
-      </c>
-      <c r="V142" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="143" spans="9:22">
-      <c r="I143" t="s">
-        <v>425</v>
-      </c>
-      <c r="V143" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="144" spans="9:22">
-      <c r="I144" t="s">
-        <v>426</v>
-      </c>
-      <c r="V144" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="145" spans="9:22">
-      <c r="I145" t="s">
-        <v>427</v>
-      </c>
-      <c r="V145" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="146" spans="9:22">
-      <c r="I146" t="s">
-        <v>428</v>
-      </c>
-      <c r="V146" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="147" spans="9:22">
-      <c r="I147" t="s">
-        <v>429</v>
-      </c>
-      <c r="V147" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="148" spans="9:22">
-      <c r="I148" t="s">
-        <v>430</v>
-      </c>
-      <c r="V148" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="149" spans="9:22">
-      <c r="I149" t="s">
-        <v>431</v>
-      </c>
-      <c r="V149" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="150" spans="9:22">
-      <c r="I150" t="s">
-        <v>432</v>
-      </c>
-      <c r="V150" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="151" spans="9:22">
-      <c r="I151" t="s">
-        <v>433</v>
-      </c>
-      <c r="V151" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="152" spans="9:22">
-      <c r="I152" t="s">
-        <v>434</v>
-      </c>
-      <c r="V152" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="153" spans="9:22">
-      <c r="I153" t="s">
-        <v>435</v>
-      </c>
-      <c r="V153" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="154" spans="9:22">
-      <c r="I154" t="s">
-        <v>436</v>
-      </c>
-      <c r="V154" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="155" spans="9:22">
-      <c r="I155" t="s">
-        <v>437</v>
-      </c>
-      <c r="V155" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="156" spans="9:22">
-      <c r="I156" t="s">
-        <v>438</v>
-      </c>
-      <c r="V156" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="157" spans="9:22">
-      <c r="I157" t="s">
-        <v>439</v>
-      </c>
-      <c r="V157" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="158" spans="9:22">
-      <c r="I158" t="s">
-        <v>440</v>
-      </c>
-      <c r="V158" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="159" spans="9:22">
-      <c r="I159" t="s">
-        <v>441</v>
-      </c>
-      <c r="V159" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="160" spans="9:22">
-      <c r="I160" t="s">
-        <v>442</v>
-      </c>
-      <c r="V160" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="161" spans="9:22">
-      <c r="I161" t="s">
-        <v>443</v>
-      </c>
-      <c r="V161" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="162" spans="9:22">
-      <c r="I162" t="s">
-        <v>444</v>
-      </c>
-      <c r="V162" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="163" spans="9:22">
-      <c r="I163" t="s">
-        <v>445</v>
-      </c>
-      <c r="V163" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="164" spans="9:22">
-      <c r="I164" t="s">
-        <v>446</v>
-      </c>
-      <c r="V164" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="165" spans="9:22">
-      <c r="I165" t="s">
-        <v>447</v>
-      </c>
-      <c r="V165" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="166" spans="9:22">
-      <c r="I166" t="s">
-        <v>448</v>
-      </c>
-      <c r="V166" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="167" spans="9:22">
-      <c r="I167" t="s">
-        <v>449</v>
-      </c>
-      <c r="V167" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="168" spans="9:22">
-      <c r="I168" t="s">
-        <v>450</v>
-      </c>
-      <c r="V168" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="169" spans="9:22">
-      <c r="I169" t="s">
-        <v>451</v>
-      </c>
-      <c r="V169" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="170" spans="9:22">
-      <c r="I170" t="s">
-        <v>452</v>
-      </c>
-      <c r="V170" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="171" spans="9:22">
-      <c r="I171" t="s">
-        <v>453</v>
-      </c>
-      <c r="V171" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="172" spans="9:22">
-      <c r="I172" t="s">
-        <v>454</v>
-      </c>
-      <c r="V172" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="173" spans="9:22">
-      <c r="I173" t="s">
-        <v>455</v>
-      </c>
-      <c r="V173" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="174" spans="9:22">
-      <c r="I174" t="s">
-        <v>456</v>
-      </c>
-      <c r="V174" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="175" spans="9:22">
-      <c r="I175" t="s">
-        <v>457</v>
-      </c>
-      <c r="V175" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="176" spans="9:22">
-      <c r="I176" t="s">
-        <v>458</v>
-      </c>
-      <c r="V176" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="177" spans="9:22">
-      <c r="I177" t="s">
-        <v>459</v>
-      </c>
-      <c r="V177" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="178" spans="9:22">
-      <c r="I178" t="s">
-        <v>460</v>
-      </c>
-      <c r="V178" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="179" spans="9:22">
-      <c r="I179" t="s">
-        <v>461</v>
-      </c>
-      <c r="V179" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="180" spans="9:22">
-      <c r="I180" t="s">
-        <v>462</v>
-      </c>
-      <c r="V180" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="181" spans="9:22">
-      <c r="I181" t="s">
-        <v>463</v>
-      </c>
-      <c r="V181" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="182" spans="9:22">
-      <c r="I182" t="s">
-        <v>464</v>
-      </c>
-      <c r="V182" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="183" spans="9:22">
-      <c r="I183" t="s">
-        <v>465</v>
-      </c>
-      <c r="V183" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="184" spans="9:22">
-      <c r="I184" t="s">
-        <v>466</v>
-      </c>
-      <c r="V184" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="185" spans="9:22">
-      <c r="I185" t="s">
-        <v>467</v>
-      </c>
-      <c r="V185" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="186" spans="9:22">
-      <c r="I186" t="s">
-        <v>468</v>
-      </c>
-      <c r="V186" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="187" spans="9:22">
-      <c r="I187" t="s">
-        <v>469</v>
-      </c>
-      <c r="V187" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="188" spans="9:22">
-      <c r="I188" t="s">
-        <v>470</v>
-      </c>
-      <c r="V188" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="189" spans="9:22">
-      <c r="I189" t="s">
-        <v>471</v>
-      </c>
-      <c r="V189" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="190" spans="9:22">
-      <c r="I190" t="s">
-        <v>472</v>
-      </c>
-      <c r="V190" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="191" spans="9:22">
-      <c r="I191" t="s">
-        <v>473</v>
-      </c>
-      <c r="V191" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="192" spans="9:22">
-      <c r="I192" t="s">
-        <v>474</v>
-      </c>
-      <c r="V192" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="193" spans="9:22">
-      <c r="I193" t="s">
-        <v>475</v>
-      </c>
-      <c r="V193" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="194" spans="9:22">
-      <c r="I194" t="s">
-        <v>476</v>
-      </c>
-      <c r="V194" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="195" spans="9:22">
-      <c r="I195" t="s">
-        <v>477</v>
-      </c>
-      <c r="V195" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="196" spans="9:22">
-      <c r="I196" t="s">
-        <v>478</v>
-      </c>
-      <c r="V196" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="197" spans="9:22">
-      <c r="I197" t="s">
-        <v>479</v>
-      </c>
-      <c r="V197" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="198" spans="9:22">
-      <c r="I198" t="s">
-        <v>480</v>
-      </c>
-      <c r="V198" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="199" spans="9:22">
-      <c r="I199" t="s">
-        <v>481</v>
-      </c>
-      <c r="V199" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="200" spans="9:22">
-      <c r="I200" t="s">
-        <v>482</v>
-      </c>
-      <c r="V200" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="201" spans="9:22">
-      <c r="I201" t="s">
-        <v>483</v>
-      </c>
-      <c r="V201" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="202" spans="9:22">
-      <c r="I202" t="s">
-        <v>484</v>
-      </c>
-      <c r="V202" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="203" spans="9:22">
-      <c r="I203" t="s">
-        <v>485</v>
-      </c>
-      <c r="V203" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="204" spans="9:22">
-      <c r="I204" t="s">
-        <v>486</v>
-      </c>
-      <c r="V204" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="205" spans="9:22">
-      <c r="I205" t="s">
-        <v>487</v>
-      </c>
-      <c r="V205" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="206" spans="9:22">
-      <c r="I206" t="s">
-        <v>488</v>
-      </c>
-      <c r="V206" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="207" spans="9:22">
-      <c r="I207" t="s">
-        <v>489</v>
-      </c>
-      <c r="V207" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="208" spans="9:22">
-      <c r="I208" t="s">
-        <v>490</v>
-      </c>
-      <c r="V208" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="209" spans="9:22">
-      <c r="I209" t="s">
-        <v>491</v>
-      </c>
-      <c r="V209" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="210" spans="9:22">
-      <c r="I210" t="s">
-        <v>492</v>
-      </c>
-      <c r="V210" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="211" spans="9:22">
-      <c r="I211" t="s">
-        <v>493</v>
-      </c>
-      <c r="V211" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="212" spans="9:22">
-      <c r="I212" t="s">
-        <v>494</v>
-      </c>
-      <c r="V212" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="213" spans="9:22">
-      <c r="I213" t="s">
-        <v>495</v>
-      </c>
-      <c r="V213" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="214" spans="9:22">
-      <c r="I214" t="s">
-        <v>496</v>
-      </c>
-      <c r="V214" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="215" spans="9:22">
-      <c r="I215" t="s">
-        <v>497</v>
-      </c>
-      <c r="V215" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="216" spans="9:22">
-      <c r="I216" t="s">
-        <v>498</v>
-      </c>
-      <c r="V216" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="217" spans="9:22">
-      <c r="I217" t="s">
-        <v>499</v>
-      </c>
-      <c r="V217" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="218" spans="9:22">
-      <c r="I218" t="s">
-        <v>500</v>
-      </c>
-      <c r="V218" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="219" spans="9:22">
-      <c r="I219" t="s">
-        <v>501</v>
-      </c>
-      <c r="V219" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="220" spans="9:22">
-      <c r="I220" t="s">
-        <v>502</v>
-      </c>
-      <c r="V220" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="221" spans="9:22">
-      <c r="I221" t="s">
-        <v>503</v>
-      </c>
-      <c r="V221" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="222" spans="9:22">
-      <c r="I222" t="s">
-        <v>504</v>
-      </c>
-      <c r="V222" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="9:22">
-      <c r="I223" t="s">
-        <v>505</v>
-      </c>
-      <c r="V223" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="224" spans="9:22">
-      <c r="I224" t="s">
-        <v>506</v>
-      </c>
-      <c r="V224" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="225" spans="9:22">
-      <c r="I225" t="s">
-        <v>507</v>
-      </c>
-      <c r="V225" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="226" spans="9:22">
-      <c r="I226" t="s">
-        <v>508</v>
-      </c>
-      <c r="V226" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="227" spans="9:22">
-      <c r="I227" t="s">
-        <v>509</v>
-      </c>
-      <c r="V227" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="228" spans="9:22">
-      <c r="I228" t="s">
-        <v>510</v>
-      </c>
-      <c r="V228" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="229" spans="9:22">
-      <c r="I229" t="s">
-        <v>511</v>
-      </c>
-      <c r="V229" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="230" spans="9:22">
-      <c r="I230" t="s">
-        <v>512</v>
-      </c>
-      <c r="V230" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="231" spans="9:22">
-      <c r="I231" t="s">
-        <v>513</v>
-      </c>
-      <c r="V231" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="232" spans="9:22">
-      <c r="I232" t="s">
-        <v>514</v>
-      </c>
-      <c r="V232" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="233" spans="9:22">
-      <c r="I233" t="s">
-        <v>515</v>
-      </c>
-      <c r="V233" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="234" spans="9:22">
-      <c r="I234" t="s">
-        <v>516</v>
-      </c>
-      <c r="V234" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="235" spans="9:22">
-      <c r="I235" t="s">
-        <v>517</v>
-      </c>
-      <c r="V235" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="236" spans="9:22">
-      <c r="I236" t="s">
-        <v>518</v>
-      </c>
-      <c r="V236" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="237" spans="9:22">
-      <c r="I237" t="s">
-        <v>519</v>
-      </c>
-      <c r="V237" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="238" spans="9:22">
-      <c r="I238" t="s">
-        <v>520</v>
-      </c>
-      <c r="V238" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="239" spans="9:22">
-      <c r="I239" t="s">
-        <v>521</v>
-      </c>
-      <c r="V239" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="240" spans="9:22">
-      <c r="I240" t="s">
-        <v>522</v>
-      </c>
-      <c r="V240" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="241" spans="9:22">
-      <c r="I241" t="s">
-        <v>523</v>
-      </c>
-      <c r="V241" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="242" spans="9:22">
-      <c r="I242" t="s">
-        <v>524</v>
-      </c>
-      <c r="V242" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="243" spans="9:22">
-      <c r="I243" t="s">
-        <v>525</v>
-      </c>
-      <c r="V243" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="244" spans="9:22">
-      <c r="I244" t="s">
-        <v>526</v>
-      </c>
-      <c r="V244" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="245" spans="9:22">
-      <c r="I245" t="s">
-        <v>527</v>
-      </c>
-      <c r="V245" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="246" spans="9:22">
-      <c r="I246" t="s">
-        <v>528</v>
-      </c>
-      <c r="V246" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="247" spans="9:22">
-      <c r="I247" t="s">
-        <v>529</v>
-      </c>
-      <c r="V247" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="248" spans="9:22">
-      <c r="I248" t="s">
-        <v>530</v>
-      </c>
-      <c r="V248" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="249" spans="9:22">
-      <c r="I249" t="s">
-        <v>531</v>
-      </c>
-      <c r="V249" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="250" spans="9:22">
-      <c r="I250" t="s">
-        <v>532</v>
-      </c>
-      <c r="V250" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="251" spans="9:22">
-      <c r="I251" t="s">
-        <v>533</v>
-      </c>
-      <c r="V251" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="252" spans="9:22">
-      <c r="I252" t="s">
-        <v>534</v>
-      </c>
-      <c r="V252" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="253" spans="9:22">
-      <c r="I253" t="s">
-        <v>535</v>
-      </c>
-      <c r="V253" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="254" spans="9:22">
-      <c r="I254" t="s">
-        <v>536</v>
-      </c>
-      <c r="V254" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="255" spans="9:22">
-      <c r="I255" t="s">
-        <v>537</v>
-      </c>
-      <c r="V255" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="256" spans="9:22">
-      <c r="I256" t="s">
-        <v>538</v>
-      </c>
-      <c r="V256" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="257" spans="9:22">
-      <c r="I257" t="s">
-        <v>539</v>
-      </c>
-      <c r="V257" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="258" spans="9:22">
-      <c r="I258" t="s">
-        <v>540</v>
-      </c>
-      <c r="V258" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="259" spans="9:22">
-      <c r="I259" t="s">
-        <v>541</v>
-      </c>
-      <c r="V259" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="260" spans="9:22">
-      <c r="I260" t="s">
-        <v>542</v>
-      </c>
-      <c r="V260" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="261" spans="9:22">
-      <c r="I261" t="s">
-        <v>543</v>
-      </c>
-      <c r="V261" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="262" spans="9:22">
-      <c r="I262" t="s">
-        <v>544</v>
-      </c>
-      <c r="V262" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="263" spans="9:22">
-      <c r="I263" t="s">
-        <v>545</v>
-      </c>
-      <c r="V263" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="264" spans="9:22">
-      <c r="I264" t="s">
-        <v>546</v>
-      </c>
-      <c r="V264" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="265" spans="9:22">
-      <c r="I265" t="s">
-        <v>547</v>
-      </c>
-      <c r="V265" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="266" spans="9:22">
-      <c r="I266" t="s">
-        <v>548</v>
-      </c>
-      <c r="V266" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="267" spans="9:22">
-      <c r="I267" t="s">
-        <v>549</v>
-      </c>
-      <c r="V267" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="268" spans="9:22">
-      <c r="I268" t="s">
-        <v>550</v>
-      </c>
-      <c r="V268" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="269" spans="9:22">
-      <c r="I269" t="s">
-        <v>551</v>
-      </c>
-      <c r="V269" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="270" spans="9:22">
-      <c r="I270" t="s">
-        <v>552</v>
-      </c>
-      <c r="V270" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="271" spans="9:22">
-      <c r="I271" t="s">
-        <v>553</v>
-      </c>
-      <c r="V271" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="272" spans="9:22">
-      <c r="I272" t="s">
-        <v>554</v>
-      </c>
-      <c r="V272" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="273" spans="9:22">
-      <c r="I273" t="s">
-        <v>555</v>
-      </c>
-      <c r="V273" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="274" spans="9:22">
-      <c r="V274" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="275" spans="9:22">
-      <c r="V275" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="276" spans="9:22">
-      <c r="V276" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="277" spans="9:22">
-      <c r="V277" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="278" spans="9:22">
-      <c r="V278" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="279" spans="9:22">
-      <c r="V279" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="280" spans="9:22">
-      <c r="V280" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="281" spans="9:22">
-      <c r="V281" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="282" spans="9:22">
-      <c r="V282" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="283" spans="9:22">
-      <c r="V283" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="284" spans="9:22">
-      <c r="V284" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="285" spans="9:22">
-      <c r="V285" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="286" spans="9:22">
-      <c r="V286" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="287" spans="9:22">
-      <c r="V287" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="288" spans="9:22">
-      <c r="V288" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="289" spans="22:22">
-      <c r="V289" t="s">
-        <v>614</v>
+    </row>
+    <row r="288" spans="10:23">
+      <c r="W288" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="289" spans="23:23">
+      <c r="W289" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="290" spans="23:23">
+      <c r="W290" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="291" spans="23:23">
+      <c r="W291" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="292" spans="23:23">
+      <c r="W292" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="293" spans="23:23">
+      <c r="W293" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="294" spans="23:23">
+      <c r="W294" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -17,29 +17,29 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="clinicalsetting">'cv_sample'!$I$1:$I$2</definedName>
-    <definedName name="countryoftravel">'cv_sample'!$J$1:$J$273</definedName>
-    <definedName name="environmentalsample">'cv_sample'!$T$1:$T$2</definedName>
+    <definedName name="clinicalsetting">'cv_sample'!$J$1:$J$2</definedName>
+    <definedName name="countryoftravel">'cv_sample'!$K$1:$K$273</definedName>
+    <definedName name="environmentalsample">'cv_sample'!$U$1:$U$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$W$1:$W$294</definedName>
-    <definedName name="hostdiseaseoutcome">'cv_sample'!$Y$1:$Y$3</definedName>
-    <definedName name="hosthealthstate">'cv_sample'!$AD$1:$AD$14</definedName>
-    <definedName name="hostsex">'cv_sample'!$AE$1:$AE$17</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$X$1:$X$294</definedName>
+    <definedName name="hostdiseaseoutcome">'cv_sample'!$Z$1:$Z$3</definedName>
+    <definedName name="hosthealthstate">'cv_sample'!$AE$1:$AE$14</definedName>
+    <definedName name="hostsex">'cv_sample'!$AF$1:$AF$17</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
-    <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AI$1:$AI$2</definedName>
+    <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AJ$1:$AJ$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="travelrelation">'cv_sample'!$H$1:$H$3</definedName>
+    <definedName name="travelrelation">'cv_sample'!$I$1:$I$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="691">
   <si>
     <t>alias</t>
   </si>
@@ -855,6 +855,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3629,13 +3635,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:52">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3658,13 +3664,13 @@
         <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>560</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>562</v>
@@ -3694,7 +3700,7 @@
         <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>584</v>
@@ -3703,13 +3709,13 @@
         <v>586</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>624</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>631</v>
@@ -3724,10 +3730,10 @@
         <v>637</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>649</v>
@@ -3789,8 +3795,11 @@
       <c r="AY1" s="1" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="2" spans="1:51" ht="150" customHeight="1">
+      <c r="AZ1" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3813,13 +3822,13 @@
         <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>561</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>563</v>
@@ -3849,7 +3858,7 @@
         <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>585</v>
@@ -3858,13 +3867,13 @@
         <v>587</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>623</v>
+        <v>589</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>625</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>632</v>
@@ -3879,10 +3888,10 @@
         <v>638</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>650</v>
@@ -3944,34 +3953,37 @@
       <c r="AY2" s="2" t="s">
         <v>688</v>
       </c>
+      <c r="AZ2" s="2" t="s">
+        <v>690</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>travelrelation</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>clinicalsetting</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>countryoftravel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
       <formula1>environmentalsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
       <formula1>hostdiseaseoutcome</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>hosthealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
       <formula1>hostsex</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI3:AI101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ3:AJ101">
       <formula1>Isthesequencedpathogenhostassociated</formula1>
     </dataValidation>
   </dataValidations>
@@ -3981,2425 +3993,2425 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H1:AI294"/>
+  <dimension ref="I1:AJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="8:35">
-      <c r="H1" t="s">
-        <v>278</v>
-      </c>
+    <row r="1" spans="9:36">
       <c r="I1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J1" t="s">
-        <v>287</v>
-      </c>
-      <c r="T1" t="s">
-        <v>580</v>
-      </c>
-      <c r="W1" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>626</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>639</v>
+        <v>285</v>
+      </c>
+      <c r="K1" t="s">
+        <v>289</v>
+      </c>
+      <c r="U1" t="s">
+        <v>582</v>
+      </c>
+      <c r="X1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>628</v>
       </c>
       <c r="AE1" t="s">
-        <v>643</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="2" spans="8:35">
-      <c r="H2" t="s">
-        <v>279</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>645</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2" spans="9:36">
       <c r="I2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
-      </c>
-      <c r="T2" t="s">
-        <v>581</v>
-      </c>
-      <c r="W2" t="s">
-        <v>288</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>627</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>640</v>
+        <v>286</v>
+      </c>
+      <c r="K2" t="s">
+        <v>290</v>
+      </c>
+      <c r="U2" t="s">
+        <v>583</v>
+      </c>
+      <c r="X2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>629</v>
       </c>
       <c r="AE2" t="s">
-        <v>644</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="3" spans="8:35">
-      <c r="H3" t="s">
-        <v>280</v>
-      </c>
-      <c r="J3" t="s">
-        <v>289</v>
-      </c>
-      <c r="W3" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>628</v>
-      </c>
-      <c r="AD3" t="s">
+        <v>642</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>646</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3" spans="9:36">
+      <c r="I3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K3" t="s">
+        <v>291</v>
+      </c>
+      <c r="X3" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>630</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>612</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="4" spans="9:36">
+      <c r="K4" t="s">
+        <v>292</v>
+      </c>
+      <c r="X4" t="s">
+        <v>292</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>613</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="5" spans="9:36">
+      <c r="K5" t="s">
+        <v>293</v>
+      </c>
+      <c r="X5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>614</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="9:36">
+      <c r="K6" t="s">
+        <v>294</v>
+      </c>
+      <c r="X6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>615</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="9:36">
+      <c r="K7" t="s">
+        <v>295</v>
+      </c>
+      <c r="X7" t="s">
+        <v>295</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>616</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="8" spans="9:36">
+      <c r="K8" t="s">
+        <v>296</v>
+      </c>
+      <c r="X8" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>617</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="9" spans="9:36">
+      <c r="K9" t="s">
+        <v>297</v>
+      </c>
+      <c r="X9" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>618</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="10" spans="9:36">
+      <c r="K10" t="s">
+        <v>298</v>
+      </c>
+      <c r="X10" t="s">
+        <v>590</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="11" spans="9:36">
+      <c r="K11" t="s">
+        <v>299</v>
+      </c>
+      <c r="X11" t="s">
+        <v>298</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>620</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="12" spans="9:36">
+      <c r="K12" t="s">
+        <v>300</v>
+      </c>
+      <c r="X12" t="s">
+        <v>299</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>621</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="13" spans="9:36">
+      <c r="K13" t="s">
+        <v>301</v>
+      </c>
+      <c r="X13" t="s">
+        <v>300</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>622</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="14" spans="9:36">
+      <c r="K14" t="s">
+        <v>302</v>
+      </c>
+      <c r="X14" t="s">
+        <v>301</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>623</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="15" spans="9:36">
+      <c r="K15" t="s">
+        <v>303</v>
+      </c>
+      <c r="X15" t="s">
+        <v>591</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="16" spans="9:36">
+      <c r="K16" t="s">
+        <v>304</v>
+      </c>
+      <c r="X16" t="s">
+        <v>302</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="11:32">
+      <c r="K17" t="s">
+        <v>305</v>
+      </c>
+      <c r="X17" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="18" spans="11:32">
+      <c r="K18" t="s">
+        <v>306</v>
+      </c>
+      <c r="X18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="11:32">
+      <c r="K19" t="s">
+        <v>307</v>
+      </c>
+      <c r="X19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="11:32">
+      <c r="K20" t="s">
+        <v>308</v>
+      </c>
+      <c r="X20" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="11:32">
+      <c r="K21" t="s">
+        <v>309</v>
+      </c>
+      <c r="X21" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="11:32">
+      <c r="K22" t="s">
+        <v>310</v>
+      </c>
+      <c r="X22" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="23" spans="11:32">
+      <c r="K23" t="s">
+        <v>311</v>
+      </c>
+      <c r="X23" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="11:32">
+      <c r="K24" t="s">
+        <v>312</v>
+      </c>
+      <c r="X24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="11:32">
+      <c r="K25" t="s">
+        <v>313</v>
+      </c>
+      <c r="X25" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="11:32">
+      <c r="K26" t="s">
+        <v>314</v>
+      </c>
+      <c r="X26" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="27" spans="11:32">
+      <c r="K27" t="s">
+        <v>315</v>
+      </c>
+      <c r="X27" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="28" spans="11:32">
+      <c r="K28" t="s">
+        <v>316</v>
+      </c>
+      <c r="X28" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="29" spans="11:32">
+      <c r="K29" t="s">
+        <v>317</v>
+      </c>
+      <c r="X29" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="11:32">
+      <c r="K30" t="s">
+        <v>318</v>
+      </c>
+      <c r="X30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="11:32">
+      <c r="K31" t="s">
+        <v>319</v>
+      </c>
+      <c r="X31" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="11:32">
+      <c r="K32" t="s">
+        <v>320</v>
+      </c>
+      <c r="X32" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="33" spans="11:24">
+      <c r="K33" t="s">
+        <v>321</v>
+      </c>
+      <c r="X33" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="34" spans="11:24">
+      <c r="K34" t="s">
+        <v>322</v>
+      </c>
+      <c r="X34" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="11:24">
+      <c r="K35" t="s">
+        <v>323</v>
+      </c>
+      <c r="X35" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="36" spans="11:24">
+      <c r="K36" t="s">
+        <v>324</v>
+      </c>
+      <c r="X36" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" spans="11:24">
+      <c r="K37" t="s">
+        <v>325</v>
+      </c>
+      <c r="X37" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="38" spans="11:24">
+      <c r="K38" t="s">
+        <v>326</v>
+      </c>
+      <c r="X38" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="11:24">
+      <c r="K39" t="s">
+        <v>327</v>
+      </c>
+      <c r="X39" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="40" spans="11:24">
+      <c r="K40" t="s">
+        <v>328</v>
+      </c>
+      <c r="X40" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41" spans="11:24">
+      <c r="K41" t="s">
+        <v>329</v>
+      </c>
+      <c r="X41" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="11:24">
+      <c r="K42" t="s">
+        <v>330</v>
+      </c>
+      <c r="X42" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="43" spans="11:24">
+      <c r="K43" t="s">
+        <v>331</v>
+      </c>
+      <c r="X43" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="44" spans="11:24">
+      <c r="K44" t="s">
+        <v>332</v>
+      </c>
+      <c r="X44" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="11:24">
+      <c r="K45" t="s">
+        <v>333</v>
+      </c>
+      <c r="X45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="11:24">
+      <c r="K46" t="s">
+        <v>334</v>
+      </c>
+      <c r="X46" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" spans="11:24">
+      <c r="K47" t="s">
+        <v>335</v>
+      </c>
+      <c r="X47" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="48" spans="11:24">
+      <c r="K48" t="s">
+        <v>336</v>
+      </c>
+      <c r="X48" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="49" spans="11:24">
+      <c r="K49" t="s">
+        <v>337</v>
+      </c>
+      <c r="X49" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="50" spans="11:24">
+      <c r="K50" t="s">
+        <v>338</v>
+      </c>
+      <c r="X50" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="51" spans="11:24">
+      <c r="K51" t="s">
+        <v>339</v>
+      </c>
+      <c r="X51" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="52" spans="11:24">
+      <c r="K52" t="s">
+        <v>340</v>
+      </c>
+      <c r="X52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="53" spans="11:24">
+      <c r="K53" t="s">
+        <v>341</v>
+      </c>
+      <c r="X53" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="54" spans="11:24">
+      <c r="K54" t="s">
+        <v>342</v>
+      </c>
+      <c r="X54" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="55" spans="11:24">
+      <c r="K55" t="s">
+        <v>343</v>
+      </c>
+      <c r="X55" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" spans="11:24">
+      <c r="K56" t="s">
+        <v>344</v>
+      </c>
+      <c r="X56" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="57" spans="11:24">
+      <c r="K57" t="s">
+        <v>345</v>
+      </c>
+      <c r="X57" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="58" spans="11:24">
+      <c r="K58" t="s">
+        <v>346</v>
+      </c>
+      <c r="X58" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="59" spans="11:24">
+      <c r="K59" t="s">
+        <v>347</v>
+      </c>
+      <c r="X59" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="11:24">
+      <c r="K60" t="s">
+        <v>348</v>
+      </c>
+      <c r="X60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="11:24">
+      <c r="K61" t="s">
+        <v>349</v>
+      </c>
+      <c r="X61" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="11:24">
+      <c r="K62" t="s">
+        <v>350</v>
+      </c>
+      <c r="X62" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="63" spans="11:24">
+      <c r="K63" t="s">
+        <v>351</v>
+      </c>
+      <c r="X63" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="64" spans="11:24">
+      <c r="K64" t="s">
+        <v>352</v>
+      </c>
+      <c r="X64" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="11:24">
+      <c r="K65" t="s">
+        <v>353</v>
+      </c>
+      <c r="X65" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="66" spans="11:24">
+      <c r="K66" t="s">
+        <v>354</v>
+      </c>
+      <c r="X66" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="67" spans="11:24">
+      <c r="K67" t="s">
+        <v>355</v>
+      </c>
+      <c r="X67" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="11:24">
+      <c r="K68" t="s">
+        <v>356</v>
+      </c>
+      <c r="X68" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="69" spans="11:24">
+      <c r="K69" t="s">
+        <v>357</v>
+      </c>
+      <c r="X69" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="70" spans="11:24">
+      <c r="K70" t="s">
+        <v>358</v>
+      </c>
+      <c r="X70" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="71" spans="11:24">
+      <c r="K71" t="s">
+        <v>359</v>
+      </c>
+      <c r="X71" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="72" spans="11:24">
+      <c r="K72" t="s">
+        <v>360</v>
+      </c>
+      <c r="X72" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="73" spans="11:24">
+      <c r="K73" t="s">
+        <v>361</v>
+      </c>
+      <c r="X73" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="74" spans="11:24">
+      <c r="K74" t="s">
+        <v>362</v>
+      </c>
+      <c r="X74" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="75" spans="11:24">
+      <c r="K75" t="s">
+        <v>363</v>
+      </c>
+      <c r="X75" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="76" spans="11:24">
+      <c r="K76" t="s">
+        <v>364</v>
+      </c>
+      <c r="X76" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="77" spans="11:24">
+      <c r="K77" t="s">
+        <v>365</v>
+      </c>
+      <c r="X77" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="78" spans="11:24">
+      <c r="K78" t="s">
+        <v>366</v>
+      </c>
+      <c r="X78" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="79" spans="11:24">
+      <c r="K79" t="s">
+        <v>367</v>
+      </c>
+      <c r="X79" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="80" spans="11:24">
+      <c r="K80" t="s">
+        <v>368</v>
+      </c>
+      <c r="X80" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="81" spans="11:24">
+      <c r="K81" t="s">
+        <v>369</v>
+      </c>
+      <c r="X81" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="82" spans="11:24">
+      <c r="K82" t="s">
+        <v>370</v>
+      </c>
+      <c r="X82" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="83" spans="11:24">
+      <c r="K83" t="s">
+        <v>371</v>
+      </c>
+      <c r="X83" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="84" spans="11:24">
+      <c r="K84" t="s">
+        <v>372</v>
+      </c>
+      <c r="X84" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="85" spans="11:24">
+      <c r="K85" t="s">
+        <v>373</v>
+      </c>
+      <c r="X85" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="11:24">
+      <c r="K86" t="s">
+        <v>374</v>
+      </c>
+      <c r="X86" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87" spans="11:24">
+      <c r="K87" t="s">
+        <v>375</v>
+      </c>
+      <c r="X87" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="88" spans="11:24">
+      <c r="K88" t="s">
+        <v>376</v>
+      </c>
+      <c r="X88" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="89" spans="11:24">
+      <c r="K89" t="s">
+        <v>377</v>
+      </c>
+      <c r="X89" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="90" spans="11:24">
+      <c r="K90" t="s">
+        <v>378</v>
+      </c>
+      <c r="X90" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="91" spans="11:24">
+      <c r="K91" t="s">
+        <v>379</v>
+      </c>
+      <c r="X91" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="92" spans="11:24">
+      <c r="K92" t="s">
+        <v>380</v>
+      </c>
+      <c r="X92" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="93" spans="11:24">
+      <c r="K93" t="s">
+        <v>381</v>
+      </c>
+      <c r="X93" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="94" spans="11:24">
+      <c r="K94" t="s">
+        <v>382</v>
+      </c>
+      <c r="X94" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="95" spans="11:24">
+      <c r="K95" t="s">
+        <v>383</v>
+      </c>
+      <c r="X95" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="96" spans="11:24">
+      <c r="K96" t="s">
+        <v>384</v>
+      </c>
+      <c r="X96" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="97" spans="11:24">
+      <c r="K97" t="s">
+        <v>385</v>
+      </c>
+      <c r="X97" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="11:24">
+      <c r="K98" t="s">
+        <v>386</v>
+      </c>
+      <c r="X98" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="99" spans="11:24">
+      <c r="K99" t="s">
+        <v>387</v>
+      </c>
+      <c r="X99" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="100" spans="11:24">
+      <c r="K100" t="s">
+        <v>388</v>
+      </c>
+      <c r="X100" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="101" spans="11:24">
+      <c r="K101" t="s">
+        <v>389</v>
+      </c>
+      <c r="X101" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="102" spans="11:24">
+      <c r="K102" t="s">
+        <v>390</v>
+      </c>
+      <c r="X102" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="103" spans="11:24">
+      <c r="K103" t="s">
+        <v>391</v>
+      </c>
+      <c r="X103" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="104" spans="11:24">
+      <c r="K104" t="s">
+        <v>392</v>
+      </c>
+      <c r="X104" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="105" spans="11:24">
+      <c r="K105" t="s">
+        <v>393</v>
+      </c>
+      <c r="X105" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="106" spans="11:24">
+      <c r="K106" t="s">
+        <v>394</v>
+      </c>
+      <c r="X106" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="107" spans="11:24">
+      <c r="K107" t="s">
+        <v>395</v>
+      </c>
+      <c r="X107" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="108" spans="11:24">
+      <c r="K108" t="s">
+        <v>396</v>
+      </c>
+      <c r="X108" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="109" spans="11:24">
+      <c r="K109" t="s">
+        <v>397</v>
+      </c>
+      <c r="X109" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="110" spans="11:24">
+      <c r="K110" t="s">
+        <v>398</v>
+      </c>
+      <c r="X110" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" spans="11:24">
+      <c r="K111" t="s">
+        <v>399</v>
+      </c>
+      <c r="X111" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="112" spans="11:24">
+      <c r="K112" t="s">
+        <v>400</v>
+      </c>
+      <c r="X112" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="113" spans="11:24">
+      <c r="K113" t="s">
+        <v>401</v>
+      </c>
+      <c r="X113" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="114" spans="11:24">
+      <c r="K114" t="s">
+        <v>402</v>
+      </c>
+      <c r="X114" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="115" spans="11:24">
+      <c r="K115" t="s">
+        <v>403</v>
+      </c>
+      <c r="X115" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="116" spans="11:24">
+      <c r="K116" t="s">
+        <v>404</v>
+      </c>
+      <c r="X116" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="117" spans="11:24">
+      <c r="K117" t="s">
+        <v>405</v>
+      </c>
+      <c r="X117" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="118" spans="11:24">
+      <c r="K118" t="s">
+        <v>406</v>
+      </c>
+      <c r="X118" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="119" spans="11:24">
+      <c r="K119" t="s">
+        <v>407</v>
+      </c>
+      <c r="X119" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="120" spans="11:24">
+      <c r="K120" t="s">
+        <v>408</v>
+      </c>
+      <c r="X120" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="121" spans="11:24">
+      <c r="K121" t="s">
+        <v>409</v>
+      </c>
+      <c r="X121" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="122" spans="11:24">
+      <c r="K122" t="s">
+        <v>410</v>
+      </c>
+      <c r="X122" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="123" spans="11:24">
+      <c r="K123" t="s">
+        <v>411</v>
+      </c>
+      <c r="X123" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="124" spans="11:24">
+      <c r="K124" t="s">
+        <v>412</v>
+      </c>
+      <c r="X124" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="125" spans="11:24">
+      <c r="K125" t="s">
+        <v>413</v>
+      </c>
+      <c r="X125" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="126" spans="11:24">
+      <c r="K126" t="s">
+        <v>414</v>
+      </c>
+      <c r="X126" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="127" spans="11:24">
+      <c r="K127" t="s">
+        <v>415</v>
+      </c>
+      <c r="X127" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="128" spans="11:24">
+      <c r="K128" t="s">
+        <v>416</v>
+      </c>
+      <c r="X128" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="129" spans="11:24">
+      <c r="K129" t="s">
+        <v>417</v>
+      </c>
+      <c r="X129" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="130" spans="11:24">
+      <c r="K130" t="s">
+        <v>418</v>
+      </c>
+      <c r="X130" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="131" spans="11:24">
+      <c r="K131" t="s">
+        <v>419</v>
+      </c>
+      <c r="X131" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="132" spans="11:24">
+      <c r="K132" t="s">
+        <v>420</v>
+      </c>
+      <c r="X132" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" spans="11:24">
+      <c r="K133" t="s">
+        <v>421</v>
+      </c>
+      <c r="X133" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="134" spans="11:24">
+      <c r="K134" t="s">
+        <v>422</v>
+      </c>
+      <c r="X134" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="135" spans="11:24">
+      <c r="K135" t="s">
+        <v>423</v>
+      </c>
+      <c r="X135" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="136" spans="11:24">
+      <c r="K136" t="s">
+        <v>424</v>
+      </c>
+      <c r="X136" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="137" spans="11:24">
+      <c r="K137" t="s">
+        <v>425</v>
+      </c>
+      <c r="X137" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="138" spans="11:24">
+      <c r="K138" t="s">
+        <v>426</v>
+      </c>
+      <c r="X138" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="139" spans="11:24">
+      <c r="K139" t="s">
+        <v>427</v>
+      </c>
+      <c r="X139" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="140" spans="11:24">
+      <c r="K140" t="s">
+        <v>428</v>
+      </c>
+      <c r="X140" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="141" spans="11:24">
+      <c r="K141" t="s">
+        <v>429</v>
+      </c>
+      <c r="X141" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="142" spans="11:24">
+      <c r="K142" t="s">
+        <v>430</v>
+      </c>
+      <c r="X142" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="143" spans="11:24">
+      <c r="K143" t="s">
+        <v>431</v>
+      </c>
+      <c r="X143" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="144" spans="11:24">
+      <c r="K144" t="s">
+        <v>432</v>
+      </c>
+      <c r="X144" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="145" spans="11:24">
+      <c r="K145" t="s">
+        <v>433</v>
+      </c>
+      <c r="X145" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="146" spans="11:24">
+      <c r="K146" t="s">
+        <v>434</v>
+      </c>
+      <c r="X146" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="147" spans="11:24">
+      <c r="K147" t="s">
+        <v>435</v>
+      </c>
+      <c r="X147" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="148" spans="11:24">
+      <c r="K148" t="s">
+        <v>436</v>
+      </c>
+      <c r="X148" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="149" spans="11:24">
+      <c r="K149" t="s">
+        <v>437</v>
+      </c>
+      <c r="X149" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="150" spans="11:24">
+      <c r="K150" t="s">
+        <v>438</v>
+      </c>
+      <c r="X150" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="151" spans="11:24">
+      <c r="K151" t="s">
+        <v>439</v>
+      </c>
+      <c r="X151" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="152" spans="11:24">
+      <c r="K152" t="s">
+        <v>440</v>
+      </c>
+      <c r="X152" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="153" spans="11:24">
+      <c r="K153" t="s">
+        <v>441</v>
+      </c>
+      <c r="X153" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="154" spans="11:24">
+      <c r="K154" t="s">
+        <v>442</v>
+      </c>
+      <c r="X154" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="155" spans="11:24">
+      <c r="K155" t="s">
+        <v>443</v>
+      </c>
+      <c r="X155" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="156" spans="11:24">
+      <c r="K156" t="s">
+        <v>444</v>
+      </c>
+      <c r="X156" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="157" spans="11:24">
+      <c r="K157" t="s">
+        <v>445</v>
+      </c>
+      <c r="X157" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="158" spans="11:24">
+      <c r="K158" t="s">
+        <v>446</v>
+      </c>
+      <c r="X158" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="159" spans="11:24">
+      <c r="K159" t="s">
+        <v>447</v>
+      </c>
+      <c r="X159" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="160" spans="11:24">
+      <c r="K160" t="s">
+        <v>448</v>
+      </c>
+      <c r="X160" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="161" spans="11:24">
+      <c r="K161" t="s">
+        <v>449</v>
+      </c>
+      <c r="X161" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="162" spans="11:24">
+      <c r="K162" t="s">
+        <v>450</v>
+      </c>
+      <c r="X162" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="163" spans="11:24">
+      <c r="K163" t="s">
+        <v>451</v>
+      </c>
+      <c r="X163" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="164" spans="11:24">
+      <c r="K164" t="s">
+        <v>452</v>
+      </c>
+      <c r="X164" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="165" spans="11:24">
+      <c r="K165" t="s">
+        <v>453</v>
+      </c>
+      <c r="X165" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="166" spans="11:24">
+      <c r="K166" t="s">
+        <v>454</v>
+      </c>
+      <c r="X166" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="167" spans="11:24">
+      <c r="K167" t="s">
+        <v>455</v>
+      </c>
+      <c r="X167" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="168" spans="11:24">
+      <c r="K168" t="s">
+        <v>456</v>
+      </c>
+      <c r="X168" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="169" spans="11:24">
+      <c r="K169" t="s">
+        <v>457</v>
+      </c>
+      <c r="X169" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="170" spans="11:24">
+      <c r="K170" t="s">
+        <v>458</v>
+      </c>
+      <c r="X170" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="171" spans="11:24">
+      <c r="K171" t="s">
+        <v>459</v>
+      </c>
+      <c r="X171" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="172" spans="11:24">
+      <c r="K172" t="s">
+        <v>460</v>
+      </c>
+      <c r="X172" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="173" spans="11:24">
+      <c r="K173" t="s">
+        <v>461</v>
+      </c>
+      <c r="X173" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="174" spans="11:24">
+      <c r="K174" t="s">
+        <v>462</v>
+      </c>
+      <c r="X174" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="175" spans="11:24">
+      <c r="K175" t="s">
+        <v>463</v>
+      </c>
+      <c r="X175" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="176" spans="11:24">
+      <c r="K176" t="s">
+        <v>464</v>
+      </c>
+      <c r="X176" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="177" spans="11:24">
+      <c r="K177" t="s">
+        <v>465</v>
+      </c>
+      <c r="X177" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="178" spans="11:24">
+      <c r="K178" t="s">
+        <v>466</v>
+      </c>
+      <c r="X178" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="179" spans="11:24">
+      <c r="K179" t="s">
+        <v>467</v>
+      </c>
+      <c r="X179" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="180" spans="11:24">
+      <c r="K180" t="s">
+        <v>468</v>
+      </c>
+      <c r="X180" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="181" spans="11:24">
+      <c r="K181" t="s">
+        <v>469</v>
+      </c>
+      <c r="X181" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="182" spans="11:24">
+      <c r="K182" t="s">
+        <v>470</v>
+      </c>
+      <c r="X182" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="183" spans="11:24">
+      <c r="K183" t="s">
+        <v>471</v>
+      </c>
+      <c r="X183" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="184" spans="11:24">
+      <c r="K184" t="s">
+        <v>472</v>
+      </c>
+      <c r="X184" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="185" spans="11:24">
+      <c r="K185" t="s">
+        <v>473</v>
+      </c>
+      <c r="X185" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="186" spans="11:24">
+      <c r="K186" t="s">
+        <v>474</v>
+      </c>
+      <c r="X186" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="187" spans="11:24">
+      <c r="K187" t="s">
+        <v>475</v>
+      </c>
+      <c r="X187" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="188" spans="11:24">
+      <c r="K188" t="s">
+        <v>476</v>
+      </c>
+      <c r="X188" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="189" spans="11:24">
+      <c r="K189" t="s">
+        <v>477</v>
+      </c>
+      <c r="X189" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="190" spans="11:24">
+      <c r="K190" t="s">
+        <v>478</v>
+      </c>
+      <c r="X190" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="191" spans="11:24">
+      <c r="K191" t="s">
+        <v>479</v>
+      </c>
+      <c r="X191" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="192" spans="11:24">
+      <c r="K192" t="s">
+        <v>480</v>
+      </c>
+      <c r="X192" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="193" spans="11:24">
+      <c r="K193" t="s">
+        <v>481</v>
+      </c>
+      <c r="X193" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="194" spans="11:24">
+      <c r="K194" t="s">
+        <v>482</v>
+      </c>
+      <c r="X194" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="195" spans="11:24">
+      <c r="K195" t="s">
+        <v>483</v>
+      </c>
+      <c r="X195" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="196" spans="11:24">
+      <c r="K196" t="s">
+        <v>484</v>
+      </c>
+      <c r="X196" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="197" spans="11:24">
+      <c r="K197" t="s">
+        <v>485</v>
+      </c>
+      <c r="X197" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="198" spans="11:24">
+      <c r="K198" t="s">
+        <v>486</v>
+      </c>
+      <c r="X198" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="199" spans="11:24">
+      <c r="K199" t="s">
+        <v>487</v>
+      </c>
+      <c r="X199" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="200" spans="11:24">
+      <c r="K200" t="s">
+        <v>488</v>
+      </c>
+      <c r="X200" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="201" spans="11:24">
+      <c r="K201" t="s">
+        <v>489</v>
+      </c>
+      <c r="X201" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="202" spans="11:24">
+      <c r="K202" t="s">
+        <v>490</v>
+      </c>
+      <c r="X202" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="203" spans="11:24">
+      <c r="K203" t="s">
+        <v>491</v>
+      </c>
+      <c r="X203" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="204" spans="11:24">
+      <c r="K204" t="s">
+        <v>492</v>
+      </c>
+      <c r="X204" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="205" spans="11:24">
+      <c r="K205" t="s">
+        <v>493</v>
+      </c>
+      <c r="X205" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="206" spans="11:24">
+      <c r="K206" t="s">
+        <v>494</v>
+      </c>
+      <c r="X206" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="207" spans="11:24">
+      <c r="K207" t="s">
+        <v>495</v>
+      </c>
+      <c r="X207" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="208" spans="11:24">
+      <c r="K208" t="s">
+        <v>496</v>
+      </c>
+      <c r="X208" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="209" spans="11:24">
+      <c r="K209" t="s">
+        <v>497</v>
+      </c>
+      <c r="X209" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="210" spans="11:24">
+      <c r="K210" t="s">
+        <v>498</v>
+      </c>
+      <c r="X210" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="211" spans="11:24">
+      <c r="K211" t="s">
+        <v>499</v>
+      </c>
+      <c r="X211" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="212" spans="11:24">
+      <c r="K212" t="s">
+        <v>500</v>
+      </c>
+      <c r="X212" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="213" spans="11:24">
+      <c r="K213" t="s">
+        <v>501</v>
+      </c>
+      <c r="X213" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="214" spans="11:24">
+      <c r="K214" t="s">
+        <v>502</v>
+      </c>
+      <c r="X214" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="215" spans="11:24">
+      <c r="K215" t="s">
+        <v>503</v>
+      </c>
+      <c r="X215" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="216" spans="11:24">
+      <c r="K216" t="s">
+        <v>504</v>
+      </c>
+      <c r="X216" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="217" spans="11:24">
+      <c r="K217" t="s">
+        <v>505</v>
+      </c>
+      <c r="X217" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="218" spans="11:24">
+      <c r="K218" t="s">
+        <v>506</v>
+      </c>
+      <c r="X218" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="219" spans="11:24">
+      <c r="K219" t="s">
+        <v>507</v>
+      </c>
+      <c r="X219" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="220" spans="11:24">
+      <c r="K220" t="s">
+        <v>508</v>
+      </c>
+      <c r="X220" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="221" spans="11:24">
+      <c r="K221" t="s">
+        <v>509</v>
+      </c>
+      <c r="X221" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="222" spans="11:24">
+      <c r="K222" t="s">
+        <v>510</v>
+      </c>
+      <c r="X222" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="223" spans="11:24">
+      <c r="K223" t="s">
+        <v>511</v>
+      </c>
+      <c r="X223" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="224" spans="11:24">
+      <c r="K224" t="s">
+        <v>512</v>
+      </c>
+      <c r="X224" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="225" spans="11:24">
+      <c r="K225" t="s">
+        <v>513</v>
+      </c>
+      <c r="X225" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="226" spans="11:24">
+      <c r="K226" t="s">
+        <v>514</v>
+      </c>
+      <c r="X226" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="227" spans="11:24">
+      <c r="K227" t="s">
+        <v>515</v>
+      </c>
+      <c r="X227" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="228" spans="11:24">
+      <c r="K228" t="s">
+        <v>516</v>
+      </c>
+      <c r="X228" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="229" spans="11:24">
+      <c r="K229" t="s">
+        <v>517</v>
+      </c>
+      <c r="X229" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="230" spans="11:24">
+      <c r="K230" t="s">
+        <v>518</v>
+      </c>
+      <c r="X230" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="231" spans="11:24">
+      <c r="K231" t="s">
+        <v>519</v>
+      </c>
+      <c r="X231" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="232" spans="11:24">
+      <c r="K232" t="s">
+        <v>520</v>
+      </c>
+      <c r="X232" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="233" spans="11:24">
+      <c r="K233" t="s">
+        <v>521</v>
+      </c>
+      <c r="X233" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="234" spans="11:24">
+      <c r="K234" t="s">
+        <v>522</v>
+      </c>
+      <c r="X234" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="235" spans="11:24">
+      <c r="K235" t="s">
+        <v>523</v>
+      </c>
+      <c r="X235" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="236" spans="11:24">
+      <c r="K236" t="s">
+        <v>524</v>
+      </c>
+      <c r="X236" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="237" spans="11:24">
+      <c r="K237" t="s">
+        <v>525</v>
+      </c>
+      <c r="X237" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="238" spans="11:24">
+      <c r="K238" t="s">
+        <v>526</v>
+      </c>
+      <c r="X238" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="239" spans="11:24">
+      <c r="K239" t="s">
+        <v>527</v>
+      </c>
+      <c r="X239" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="240" spans="11:24">
+      <c r="K240" t="s">
+        <v>528</v>
+      </c>
+      <c r="X240" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="241" spans="11:24">
+      <c r="K241" t="s">
+        <v>529</v>
+      </c>
+      <c r="X241" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="242" spans="11:24">
+      <c r="K242" t="s">
+        <v>530</v>
+      </c>
+      <c r="X242" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="243" spans="11:24">
+      <c r="K243" t="s">
+        <v>531</v>
+      </c>
+      <c r="X243" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="244" spans="11:24">
+      <c r="K244" t="s">
+        <v>532</v>
+      </c>
+      <c r="X244" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="245" spans="11:24">
+      <c r="K245" t="s">
+        <v>533</v>
+      </c>
+      <c r="X245" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="246" spans="11:24">
+      <c r="K246" t="s">
+        <v>534</v>
+      </c>
+      <c r="X246" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="247" spans="11:24">
+      <c r="K247" t="s">
+        <v>535</v>
+      </c>
+      <c r="X247" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="248" spans="11:24">
+      <c r="K248" t="s">
+        <v>536</v>
+      </c>
+      <c r="X248" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="249" spans="11:24">
+      <c r="K249" t="s">
+        <v>537</v>
+      </c>
+      <c r="X249" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="250" spans="11:24">
+      <c r="K250" t="s">
+        <v>538</v>
+      </c>
+      <c r="X250" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="251" spans="11:24">
+      <c r="K251" t="s">
+        <v>539</v>
+      </c>
+      <c r="X251" t="s">
         <v>610</v>
       </c>
-      <c r="AE3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="4" spans="8:35">
-      <c r="J4" t="s">
-        <v>290</v>
-      </c>
-      <c r="W4" t="s">
-        <v>290</v>
-      </c>
-      <c r="AD4" t="s">
+    </row>
+    <row r="252" spans="11:24">
+      <c r="K252" t="s">
+        <v>540</v>
+      </c>
+      <c r="X252" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="253" spans="11:24">
+      <c r="K253" t="s">
+        <v>541</v>
+      </c>
+      <c r="X253" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="254" spans="11:24">
+      <c r="K254" t="s">
+        <v>542</v>
+      </c>
+      <c r="X254" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="255" spans="11:24">
+      <c r="K255" t="s">
+        <v>543</v>
+      </c>
+      <c r="X255" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="256" spans="11:24">
+      <c r="K256" t="s">
+        <v>544</v>
+      </c>
+      <c r="X256" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="257" spans="11:24">
+      <c r="K257" t="s">
+        <v>545</v>
+      </c>
+      <c r="X257" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="258" spans="11:24">
+      <c r="K258" t="s">
+        <v>546</v>
+      </c>
+      <c r="X258" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="259" spans="11:24">
+      <c r="K259" t="s">
+        <v>547</v>
+      </c>
+      <c r="X259" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="260" spans="11:24">
+      <c r="K260" t="s">
+        <v>548</v>
+      </c>
+      <c r="X260" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="261" spans="11:24">
+      <c r="K261" t="s">
+        <v>549</v>
+      </c>
+      <c r="X261" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="262" spans="11:24">
+      <c r="K262" t="s">
+        <v>550</v>
+      </c>
+      <c r="X262" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="263" spans="11:24">
+      <c r="K263" t="s">
+        <v>551</v>
+      </c>
+      <c r="X263" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="264" spans="11:24">
+      <c r="K264" t="s">
+        <v>552</v>
+      </c>
+      <c r="X264" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="265" spans="11:24">
+      <c r="K265" t="s">
+        <v>553</v>
+      </c>
+      <c r="X265" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="266" spans="11:24">
+      <c r="K266" t="s">
+        <v>554</v>
+      </c>
+      <c r="X266" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="267" spans="11:24">
+      <c r="K267" t="s">
+        <v>555</v>
+      </c>
+      <c r="X267" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="268" spans="11:24">
+      <c r="K268" t="s">
+        <v>556</v>
+      </c>
+      <c r="X268" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="269" spans="11:24">
+      <c r="K269" t="s">
+        <v>557</v>
+      </c>
+      <c r="X269" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="270" spans="11:24">
+      <c r="K270" t="s">
+        <v>558</v>
+      </c>
+      <c r="X270" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="271" spans="11:24">
+      <c r="K271" t="s">
+        <v>559</v>
+      </c>
+      <c r="X271" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="272" spans="11:24">
+      <c r="K272" t="s">
+        <v>560</v>
+      </c>
+      <c r="X272" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="273" spans="11:24">
+      <c r="K273" t="s">
+        <v>561</v>
+      </c>
+      <c r="X273" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="274" spans="11:24">
+      <c r="X274" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="275" spans="11:24">
+      <c r="X275" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="276" spans="11:24">
+      <c r="X276" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="277" spans="11:24">
+      <c r="X277" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="278" spans="11:24">
+      <c r="X278" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="279" spans="11:24">
+      <c r="X279" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="280" spans="11:24">
+      <c r="X280" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="281" spans="11:24">
+      <c r="X281" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="282" spans="11:24">
+      <c r="X282" t="s">
         <v>611</v>
       </c>
-      <c r="AE4" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="5" spans="8:35">
-      <c r="J5" t="s">
-        <v>291</v>
-      </c>
-      <c r="W5" t="s">
-        <v>291</v>
-      </c>
-      <c r="AD5" t="s">
+    </row>
+    <row r="283" spans="11:24">
+      <c r="X283" t="s">
         <v>612</v>
       </c>
-      <c r="AE5" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="6" spans="8:35">
-      <c r="J6" t="s">
-        <v>292</v>
-      </c>
-      <c r="W6" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD6" t="s">
+    </row>
+    <row r="284" spans="11:24">
+      <c r="X284" t="s">
         <v>613</v>
       </c>
-      <c r="AE6" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="7" spans="8:35">
-      <c r="J7" t="s">
-        <v>293</v>
-      </c>
-      <c r="W7" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD7" t="s">
+    </row>
+    <row r="285" spans="11:24">
+      <c r="X285" t="s">
         <v>614</v>
       </c>
-      <c r="AE7" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="8" spans="8:35">
-      <c r="J8" t="s">
-        <v>294</v>
-      </c>
-      <c r="W8" t="s">
-        <v>294</v>
-      </c>
-      <c r="AD8" t="s">
+    </row>
+    <row r="286" spans="11:24">
+      <c r="X286" t="s">
         <v>615</v>
       </c>
-      <c r="AE8" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="9" spans="8:35">
-      <c r="J9" t="s">
-        <v>295</v>
-      </c>
-      <c r="W9" t="s">
-        <v>295</v>
-      </c>
-      <c r="AD9" t="s">
+    </row>
+    <row r="287" spans="11:24">
+      <c r="X287" t="s">
         <v>616</v>
       </c>
-      <c r="AE9" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="10" spans="8:35">
-      <c r="J10" t="s">
-        <v>296</v>
-      </c>
-      <c r="W10" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD10" t="s">
+    </row>
+    <row r="288" spans="11:24">
+      <c r="X288" t="s">
         <v>617</v>
       </c>
-      <c r="AE10" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="11" spans="8:35">
-      <c r="J11" t="s">
-        <v>297</v>
-      </c>
-      <c r="W11" t="s">
-        <v>296</v>
-      </c>
-      <c r="AD11" t="s">
+    </row>
+    <row r="289" spans="24:24">
+      <c r="X289" t="s">
         <v>618</v>
       </c>
-      <c r="AE11" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="12" spans="8:35">
-      <c r="J12" t="s">
-        <v>298</v>
-      </c>
-      <c r="W12" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD12" t="s">
+    </row>
+    <row r="290" spans="24:24">
+      <c r="X290" t="s">
         <v>619</v>
       </c>
-      <c r="AE12" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="13" spans="8:35">
-      <c r="J13" t="s">
-        <v>299</v>
-      </c>
-      <c r="W13" t="s">
-        <v>298</v>
-      </c>
-      <c r="AD13" t="s">
+    </row>
+    <row r="291" spans="24:24">
+      <c r="X291" t="s">
         <v>620</v>
       </c>
-      <c r="AE13" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="14" spans="8:35">
-      <c r="J14" t="s">
-        <v>300</v>
-      </c>
-      <c r="W14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AD14" t="s">
+    </row>
+    <row r="292" spans="24:24">
+      <c r="X292" t="s">
         <v>621</v>
       </c>
-      <c r="AE14" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="15" spans="8:35">
-      <c r="J15" t="s">
-        <v>301</v>
-      </c>
-      <c r="W15" t="s">
-        <v>589</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="16" spans="8:35">
-      <c r="J16" t="s">
-        <v>302</v>
-      </c>
-      <c r="W16" t="s">
-        <v>300</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="10:31">
-      <c r="J17" t="s">
-        <v>303</v>
-      </c>
-      <c r="W17" t="s">
-        <v>301</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="18" spans="10:31">
-      <c r="J18" t="s">
-        <v>304</v>
-      </c>
-      <c r="W18" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="19" spans="10:31">
-      <c r="J19" t="s">
-        <v>305</v>
-      </c>
-      <c r="W19" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="20" spans="10:31">
-      <c r="J20" t="s">
-        <v>306</v>
-      </c>
-      <c r="W20" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="21" spans="10:31">
-      <c r="J21" t="s">
-        <v>307</v>
-      </c>
-      <c r="W21" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="22" spans="10:31">
-      <c r="J22" t="s">
-        <v>308</v>
-      </c>
-      <c r="W22" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="23" spans="10:31">
-      <c r="J23" t="s">
-        <v>309</v>
-      </c>
-      <c r="W23" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="24" spans="10:31">
-      <c r="J24" t="s">
-        <v>310</v>
-      </c>
-      <c r="W24" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="25" spans="10:31">
-      <c r="J25" t="s">
-        <v>311</v>
-      </c>
-      <c r="W25" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="26" spans="10:31">
-      <c r="J26" t="s">
-        <v>312</v>
-      </c>
-      <c r="W26" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="27" spans="10:31">
-      <c r="J27" t="s">
-        <v>313</v>
-      </c>
-      <c r="W27" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="28" spans="10:31">
-      <c r="J28" t="s">
-        <v>314</v>
-      </c>
-      <c r="W28" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="29" spans="10:31">
-      <c r="J29" t="s">
-        <v>315</v>
-      </c>
-      <c r="W29" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="30" spans="10:31">
-      <c r="J30" t="s">
-        <v>316</v>
-      </c>
-      <c r="W30" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" spans="10:31">
-      <c r="J31" t="s">
-        <v>317</v>
-      </c>
-      <c r="W31" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="32" spans="10:31">
-      <c r="J32" t="s">
-        <v>318</v>
-      </c>
-      <c r="W32" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="33" spans="10:23">
-      <c r="J33" t="s">
-        <v>319</v>
-      </c>
-      <c r="W33" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="34" spans="10:23">
-      <c r="J34" t="s">
-        <v>320</v>
-      </c>
-      <c r="W34" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="35" spans="10:23">
-      <c r="J35" t="s">
-        <v>321</v>
-      </c>
-      <c r="W35" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="36" spans="10:23">
-      <c r="J36" t="s">
-        <v>322</v>
-      </c>
-      <c r="W36" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="37" spans="10:23">
-      <c r="J37" t="s">
-        <v>323</v>
-      </c>
-      <c r="W37" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="38" spans="10:23">
-      <c r="J38" t="s">
-        <v>324</v>
-      </c>
-      <c r="W38" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="39" spans="10:23">
-      <c r="J39" t="s">
-        <v>325</v>
-      </c>
-      <c r="W39" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="40" spans="10:23">
-      <c r="J40" t="s">
-        <v>326</v>
-      </c>
-      <c r="W40" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="41" spans="10:23">
-      <c r="J41" t="s">
-        <v>327</v>
-      </c>
-      <c r="W41" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="42" spans="10:23">
-      <c r="J42" t="s">
-        <v>328</v>
-      </c>
-      <c r="W42" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="43" spans="10:23">
-      <c r="J43" t="s">
-        <v>329</v>
-      </c>
-      <c r="W43" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="44" spans="10:23">
-      <c r="J44" t="s">
-        <v>330</v>
-      </c>
-      <c r="W44" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="45" spans="10:23">
-      <c r="J45" t="s">
-        <v>331</v>
-      </c>
-      <c r="W45" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="46" spans="10:23">
-      <c r="J46" t="s">
-        <v>332</v>
-      </c>
-      <c r="W46" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="47" spans="10:23">
-      <c r="J47" t="s">
-        <v>333</v>
-      </c>
-      <c r="W47" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="48" spans="10:23">
-      <c r="J48" t="s">
-        <v>334</v>
-      </c>
-      <c r="W48" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="49" spans="10:23">
-      <c r="J49" t="s">
-        <v>335</v>
-      </c>
-      <c r="W49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="50" spans="10:23">
-      <c r="J50" t="s">
-        <v>336</v>
-      </c>
-      <c r="W50" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="51" spans="10:23">
-      <c r="J51" t="s">
-        <v>337</v>
-      </c>
-      <c r="W51" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="52" spans="10:23">
-      <c r="J52" t="s">
-        <v>338</v>
-      </c>
-      <c r="W52" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="53" spans="10:23">
-      <c r="J53" t="s">
-        <v>339</v>
-      </c>
-      <c r="W53" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="54" spans="10:23">
-      <c r="J54" t="s">
-        <v>340</v>
-      </c>
-      <c r="W54" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="55" spans="10:23">
-      <c r="J55" t="s">
-        <v>341</v>
-      </c>
-      <c r="W55" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="56" spans="10:23">
-      <c r="J56" t="s">
-        <v>342</v>
-      </c>
-      <c r="W56" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="57" spans="10:23">
-      <c r="J57" t="s">
-        <v>343</v>
-      </c>
-      <c r="W57" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="58" spans="10:23">
-      <c r="J58" t="s">
-        <v>344</v>
-      </c>
-      <c r="W58" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="59" spans="10:23">
-      <c r="J59" t="s">
-        <v>345</v>
-      </c>
-      <c r="W59" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="60" spans="10:23">
-      <c r="J60" t="s">
-        <v>346</v>
-      </c>
-      <c r="W60" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="61" spans="10:23">
-      <c r="J61" t="s">
-        <v>347</v>
-      </c>
-      <c r="W61" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="62" spans="10:23">
-      <c r="J62" t="s">
-        <v>348</v>
-      </c>
-      <c r="W62" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="63" spans="10:23">
-      <c r="J63" t="s">
-        <v>349</v>
-      </c>
-      <c r="W63" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="64" spans="10:23">
-      <c r="J64" t="s">
-        <v>350</v>
-      </c>
-      <c r="W64" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="65" spans="10:23">
-      <c r="J65" t="s">
-        <v>351</v>
-      </c>
-      <c r="W65" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="66" spans="10:23">
-      <c r="J66" t="s">
-        <v>352</v>
-      </c>
-      <c r="W66" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="67" spans="10:23">
-      <c r="J67" t="s">
-        <v>353</v>
-      </c>
-      <c r="W67" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="68" spans="10:23">
-      <c r="J68" t="s">
-        <v>354</v>
-      </c>
-      <c r="W68" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="69" spans="10:23">
-      <c r="J69" t="s">
-        <v>355</v>
-      </c>
-      <c r="W69" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="70" spans="10:23">
-      <c r="J70" t="s">
-        <v>356</v>
-      </c>
-      <c r="W70" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="71" spans="10:23">
-      <c r="J71" t="s">
-        <v>357</v>
-      </c>
-      <c r="W71" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="72" spans="10:23">
-      <c r="J72" t="s">
-        <v>358</v>
-      </c>
-      <c r="W72" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="73" spans="10:23">
-      <c r="J73" t="s">
-        <v>359</v>
-      </c>
-      <c r="W73" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="74" spans="10:23">
-      <c r="J74" t="s">
-        <v>360</v>
-      </c>
-      <c r="W74" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="75" spans="10:23">
-      <c r="J75" t="s">
-        <v>361</v>
-      </c>
-      <c r="W75" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="76" spans="10:23">
-      <c r="J76" t="s">
-        <v>362</v>
-      </c>
-      <c r="W76" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="77" spans="10:23">
-      <c r="J77" t="s">
-        <v>363</v>
-      </c>
-      <c r="W77" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="78" spans="10:23">
-      <c r="J78" t="s">
-        <v>364</v>
-      </c>
-      <c r="W78" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="79" spans="10:23">
-      <c r="J79" t="s">
-        <v>365</v>
-      </c>
-      <c r="W79" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="80" spans="10:23">
-      <c r="J80" t="s">
-        <v>366</v>
-      </c>
-      <c r="W80" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="81" spans="10:23">
-      <c r="J81" t="s">
-        <v>367</v>
-      </c>
-      <c r="W81" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="82" spans="10:23">
-      <c r="J82" t="s">
-        <v>368</v>
-      </c>
-      <c r="W82" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="83" spans="10:23">
-      <c r="J83" t="s">
-        <v>369</v>
-      </c>
-      <c r="W83" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="84" spans="10:23">
-      <c r="J84" t="s">
-        <v>370</v>
-      </c>
-      <c r="W84" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="85" spans="10:23">
-      <c r="J85" t="s">
-        <v>371</v>
-      </c>
-      <c r="W85" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="86" spans="10:23">
-      <c r="J86" t="s">
-        <v>372</v>
-      </c>
-      <c r="W86" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="87" spans="10:23">
-      <c r="J87" t="s">
-        <v>373</v>
-      </c>
-      <c r="W87" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="88" spans="10:23">
-      <c r="J88" t="s">
-        <v>374</v>
-      </c>
-      <c r="W88" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="89" spans="10:23">
-      <c r="J89" t="s">
-        <v>375</v>
-      </c>
-      <c r="W89" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="90" spans="10:23">
-      <c r="J90" t="s">
-        <v>376</v>
-      </c>
-      <c r="W90" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="91" spans="10:23">
-      <c r="J91" t="s">
-        <v>377</v>
-      </c>
-      <c r="W91" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="92" spans="10:23">
-      <c r="J92" t="s">
-        <v>378</v>
-      </c>
-      <c r="W92" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="93" spans="10:23">
-      <c r="J93" t="s">
-        <v>379</v>
-      </c>
-      <c r="W93" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="94" spans="10:23">
-      <c r="J94" t="s">
-        <v>380</v>
-      </c>
-      <c r="W94" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="95" spans="10:23">
-      <c r="J95" t="s">
-        <v>381</v>
-      </c>
-      <c r="W95" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="96" spans="10:23">
-      <c r="J96" t="s">
-        <v>382</v>
-      </c>
-      <c r="W96" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="97" spans="10:23">
-      <c r="J97" t="s">
-        <v>383</v>
-      </c>
-      <c r="W97" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="98" spans="10:23">
-      <c r="J98" t="s">
-        <v>384</v>
-      </c>
-      <c r="W98" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="99" spans="10:23">
-      <c r="J99" t="s">
-        <v>385</v>
-      </c>
-      <c r="W99" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="100" spans="10:23">
-      <c r="J100" t="s">
-        <v>386</v>
-      </c>
-      <c r="W100" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="101" spans="10:23">
-      <c r="J101" t="s">
-        <v>387</v>
-      </c>
-      <c r="W101" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="102" spans="10:23">
-      <c r="J102" t="s">
-        <v>388</v>
-      </c>
-      <c r="W102" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="103" spans="10:23">
-      <c r="J103" t="s">
-        <v>389</v>
-      </c>
-      <c r="W103" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="104" spans="10:23">
-      <c r="J104" t="s">
-        <v>390</v>
-      </c>
-      <c r="W104" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="105" spans="10:23">
-      <c r="J105" t="s">
-        <v>391</v>
-      </c>
-      <c r="W105" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="106" spans="10:23">
-      <c r="J106" t="s">
-        <v>392</v>
-      </c>
-      <c r="W106" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="107" spans="10:23">
-      <c r="J107" t="s">
-        <v>393</v>
-      </c>
-      <c r="W107" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="108" spans="10:23">
-      <c r="J108" t="s">
-        <v>394</v>
-      </c>
-      <c r="W108" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="109" spans="10:23">
-      <c r="J109" t="s">
-        <v>395</v>
-      </c>
-      <c r="W109" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="110" spans="10:23">
-      <c r="J110" t="s">
-        <v>396</v>
-      </c>
-      <c r="W110" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="111" spans="10:23">
-      <c r="J111" t="s">
-        <v>397</v>
-      </c>
-      <c r="W111" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="112" spans="10:23">
-      <c r="J112" t="s">
-        <v>398</v>
-      </c>
-      <c r="W112" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="113" spans="10:23">
-      <c r="J113" t="s">
-        <v>399</v>
-      </c>
-      <c r="W113" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="114" spans="10:23">
-      <c r="J114" t="s">
-        <v>400</v>
-      </c>
-      <c r="W114" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="115" spans="10:23">
-      <c r="J115" t="s">
-        <v>401</v>
-      </c>
-      <c r="W115" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="116" spans="10:23">
-      <c r="J116" t="s">
-        <v>402</v>
-      </c>
-      <c r="W116" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="117" spans="10:23">
-      <c r="J117" t="s">
-        <v>403</v>
-      </c>
-      <c r="W117" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="118" spans="10:23">
-      <c r="J118" t="s">
-        <v>404</v>
-      </c>
-      <c r="W118" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="119" spans="10:23">
-      <c r="J119" t="s">
-        <v>405</v>
-      </c>
-      <c r="W119" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="120" spans="10:23">
-      <c r="J120" t="s">
-        <v>406</v>
-      </c>
-      <c r="W120" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="121" spans="10:23">
-      <c r="J121" t="s">
-        <v>407</v>
-      </c>
-      <c r="W121" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="122" spans="10:23">
-      <c r="J122" t="s">
-        <v>408</v>
-      </c>
-      <c r="W122" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="123" spans="10:23">
-      <c r="J123" t="s">
-        <v>409</v>
-      </c>
-      <c r="W123" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="124" spans="10:23">
-      <c r="J124" t="s">
-        <v>410</v>
-      </c>
-      <c r="W124" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="125" spans="10:23">
-      <c r="J125" t="s">
-        <v>411</v>
-      </c>
-      <c r="W125" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="126" spans="10:23">
-      <c r="J126" t="s">
-        <v>412</v>
-      </c>
-      <c r="W126" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="127" spans="10:23">
-      <c r="J127" t="s">
-        <v>413</v>
-      </c>
-      <c r="W127" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="128" spans="10:23">
-      <c r="J128" t="s">
-        <v>414</v>
-      </c>
-      <c r="W128" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="129" spans="10:23">
-      <c r="J129" t="s">
-        <v>415</v>
-      </c>
-      <c r="W129" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="130" spans="10:23">
-      <c r="J130" t="s">
-        <v>416</v>
-      </c>
-      <c r="W130" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="131" spans="10:23">
-      <c r="J131" t="s">
-        <v>417</v>
-      </c>
-      <c r="W131" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="132" spans="10:23">
-      <c r="J132" t="s">
-        <v>418</v>
-      </c>
-      <c r="W132" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="10:23">
-      <c r="J133" t="s">
-        <v>419</v>
-      </c>
-      <c r="W133" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="134" spans="10:23">
-      <c r="J134" t="s">
-        <v>420</v>
-      </c>
-      <c r="W134" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="135" spans="10:23">
-      <c r="J135" t="s">
-        <v>421</v>
-      </c>
-      <c r="W135" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="136" spans="10:23">
-      <c r="J136" t="s">
-        <v>422</v>
-      </c>
-      <c r="W136" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="137" spans="10:23">
-      <c r="J137" t="s">
-        <v>423</v>
-      </c>
-      <c r="W137" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="138" spans="10:23">
-      <c r="J138" t="s">
-        <v>424</v>
-      </c>
-      <c r="W138" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="139" spans="10:23">
-      <c r="J139" t="s">
-        <v>425</v>
-      </c>
-      <c r="W139" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="140" spans="10:23">
-      <c r="J140" t="s">
-        <v>426</v>
-      </c>
-      <c r="W140" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="141" spans="10:23">
-      <c r="J141" t="s">
-        <v>427</v>
-      </c>
-      <c r="W141" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="142" spans="10:23">
-      <c r="J142" t="s">
-        <v>428</v>
-      </c>
-      <c r="W142" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="143" spans="10:23">
-      <c r="J143" t="s">
-        <v>429</v>
-      </c>
-      <c r="W143" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="144" spans="10:23">
-      <c r="J144" t="s">
-        <v>430</v>
-      </c>
-      <c r="W144" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="145" spans="10:23">
-      <c r="J145" t="s">
-        <v>431</v>
-      </c>
-      <c r="W145" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="146" spans="10:23">
-      <c r="J146" t="s">
-        <v>432</v>
-      </c>
-      <c r="W146" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="147" spans="10:23">
-      <c r="J147" t="s">
-        <v>433</v>
-      </c>
-      <c r="W147" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="148" spans="10:23">
-      <c r="J148" t="s">
-        <v>434</v>
-      </c>
-      <c r="W148" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="149" spans="10:23">
-      <c r="J149" t="s">
-        <v>435</v>
-      </c>
-      <c r="W149" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="150" spans="10:23">
-      <c r="J150" t="s">
-        <v>436</v>
-      </c>
-      <c r="W150" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="151" spans="10:23">
-      <c r="J151" t="s">
-        <v>437</v>
-      </c>
-      <c r="W151" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="152" spans="10:23">
-      <c r="J152" t="s">
-        <v>438</v>
-      </c>
-      <c r="W152" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="153" spans="10:23">
-      <c r="J153" t="s">
-        <v>439</v>
-      </c>
-      <c r="W153" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="154" spans="10:23">
-      <c r="J154" t="s">
-        <v>440</v>
-      </c>
-      <c r="W154" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="155" spans="10:23">
-      <c r="J155" t="s">
-        <v>441</v>
-      </c>
-      <c r="W155" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="156" spans="10:23">
-      <c r="J156" t="s">
-        <v>442</v>
-      </c>
-      <c r="W156" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="157" spans="10:23">
-      <c r="J157" t="s">
-        <v>443</v>
-      </c>
-      <c r="W157" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="158" spans="10:23">
-      <c r="J158" t="s">
-        <v>444</v>
-      </c>
-      <c r="W158" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="159" spans="10:23">
-      <c r="J159" t="s">
-        <v>445</v>
-      </c>
-      <c r="W159" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="160" spans="10:23">
-      <c r="J160" t="s">
-        <v>446</v>
-      </c>
-      <c r="W160" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="161" spans="10:23">
-      <c r="J161" t="s">
-        <v>447</v>
-      </c>
-      <c r="W161" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="162" spans="10:23">
-      <c r="J162" t="s">
-        <v>448</v>
-      </c>
-      <c r="W162" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="163" spans="10:23">
-      <c r="J163" t="s">
-        <v>449</v>
-      </c>
-      <c r="W163" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="164" spans="10:23">
-      <c r="J164" t="s">
-        <v>450</v>
-      </c>
-      <c r="W164" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="165" spans="10:23">
-      <c r="J165" t="s">
-        <v>451</v>
-      </c>
-      <c r="W165" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="166" spans="10:23">
-      <c r="J166" t="s">
-        <v>452</v>
-      </c>
-      <c r="W166" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="167" spans="10:23">
-      <c r="J167" t="s">
-        <v>453</v>
-      </c>
-      <c r="W167" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="168" spans="10:23">
-      <c r="J168" t="s">
-        <v>454</v>
-      </c>
-      <c r="W168" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="169" spans="10:23">
-      <c r="J169" t="s">
-        <v>455</v>
-      </c>
-      <c r="W169" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="170" spans="10:23">
-      <c r="J170" t="s">
-        <v>456</v>
-      </c>
-      <c r="W170" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="171" spans="10:23">
-      <c r="J171" t="s">
-        <v>457</v>
-      </c>
-      <c r="W171" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="172" spans="10:23">
-      <c r="J172" t="s">
-        <v>458</v>
-      </c>
-      <c r="W172" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="173" spans="10:23">
-      <c r="J173" t="s">
-        <v>459</v>
-      </c>
-      <c r="W173" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="174" spans="10:23">
-      <c r="J174" t="s">
-        <v>460</v>
-      </c>
-      <c r="W174" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="175" spans="10:23">
-      <c r="J175" t="s">
-        <v>461</v>
-      </c>
-      <c r="W175" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="176" spans="10:23">
-      <c r="J176" t="s">
-        <v>462</v>
-      </c>
-      <c r="W176" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="177" spans="10:23">
-      <c r="J177" t="s">
-        <v>463</v>
-      </c>
-      <c r="W177" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="178" spans="10:23">
-      <c r="J178" t="s">
-        <v>464</v>
-      </c>
-      <c r="W178" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="179" spans="10:23">
-      <c r="J179" t="s">
-        <v>465</v>
-      </c>
-      <c r="W179" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="180" spans="10:23">
-      <c r="J180" t="s">
-        <v>466</v>
-      </c>
-      <c r="W180" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="181" spans="10:23">
-      <c r="J181" t="s">
-        <v>467</v>
-      </c>
-      <c r="W181" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="182" spans="10:23">
-      <c r="J182" t="s">
-        <v>468</v>
-      </c>
-      <c r="W182" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="183" spans="10:23">
-      <c r="J183" t="s">
-        <v>469</v>
-      </c>
-      <c r="W183" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="184" spans="10:23">
-      <c r="J184" t="s">
-        <v>470</v>
-      </c>
-      <c r="W184" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="185" spans="10:23">
-      <c r="J185" t="s">
-        <v>471</v>
-      </c>
-      <c r="W185" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="186" spans="10:23">
-      <c r="J186" t="s">
-        <v>472</v>
-      </c>
-      <c r="W186" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="187" spans="10:23">
-      <c r="J187" t="s">
-        <v>473</v>
-      </c>
-      <c r="W187" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="188" spans="10:23">
-      <c r="J188" t="s">
-        <v>474</v>
-      </c>
-      <c r="W188" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="189" spans="10:23">
-      <c r="J189" t="s">
-        <v>475</v>
-      </c>
-      <c r="W189" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="190" spans="10:23">
-      <c r="J190" t="s">
-        <v>476</v>
-      </c>
-      <c r="W190" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="191" spans="10:23">
-      <c r="J191" t="s">
-        <v>477</v>
-      </c>
-      <c r="W191" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="192" spans="10:23">
-      <c r="J192" t="s">
-        <v>478</v>
-      </c>
-      <c r="W192" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="193" spans="10:23">
-      <c r="J193" t="s">
-        <v>479</v>
-      </c>
-      <c r="W193" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="194" spans="10:23">
-      <c r="J194" t="s">
-        <v>480</v>
-      </c>
-      <c r="W194" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="195" spans="10:23">
-      <c r="J195" t="s">
-        <v>481</v>
-      </c>
-      <c r="W195" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="196" spans="10:23">
-      <c r="J196" t="s">
-        <v>482</v>
-      </c>
-      <c r="W196" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="197" spans="10:23">
-      <c r="J197" t="s">
-        <v>483</v>
-      </c>
-      <c r="W197" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="198" spans="10:23">
-      <c r="J198" t="s">
-        <v>484</v>
-      </c>
-      <c r="W198" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="199" spans="10:23">
-      <c r="J199" t="s">
-        <v>485</v>
-      </c>
-      <c r="W199" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="200" spans="10:23">
-      <c r="J200" t="s">
-        <v>486</v>
-      </c>
-      <c r="W200" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="201" spans="10:23">
-      <c r="J201" t="s">
-        <v>487</v>
-      </c>
-      <c r="W201" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="202" spans="10:23">
-      <c r="J202" t="s">
-        <v>488</v>
-      </c>
-      <c r="W202" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="203" spans="10:23">
-      <c r="J203" t="s">
-        <v>489</v>
-      </c>
-      <c r="W203" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="204" spans="10:23">
-      <c r="J204" t="s">
-        <v>490</v>
-      </c>
-      <c r="W204" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="205" spans="10:23">
-      <c r="J205" t="s">
-        <v>491</v>
-      </c>
-      <c r="W205" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="206" spans="10:23">
-      <c r="J206" t="s">
-        <v>492</v>
-      </c>
-      <c r="W206" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="207" spans="10:23">
-      <c r="J207" t="s">
-        <v>493</v>
-      </c>
-      <c r="W207" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="208" spans="10:23">
-      <c r="J208" t="s">
-        <v>494</v>
-      </c>
-      <c r="W208" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="209" spans="10:23">
-      <c r="J209" t="s">
-        <v>495</v>
-      </c>
-      <c r="W209" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="210" spans="10:23">
-      <c r="J210" t="s">
-        <v>496</v>
-      </c>
-      <c r="W210" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="211" spans="10:23">
-      <c r="J211" t="s">
-        <v>497</v>
-      </c>
-      <c r="W211" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="212" spans="10:23">
-      <c r="J212" t="s">
-        <v>498</v>
-      </c>
-      <c r="W212" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="213" spans="10:23">
-      <c r="J213" t="s">
-        <v>499</v>
-      </c>
-      <c r="W213" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="214" spans="10:23">
-      <c r="J214" t="s">
-        <v>500</v>
-      </c>
-      <c r="W214" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="215" spans="10:23">
-      <c r="J215" t="s">
-        <v>501</v>
-      </c>
-      <c r="W215" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="216" spans="10:23">
-      <c r="J216" t="s">
-        <v>502</v>
-      </c>
-      <c r="W216" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="217" spans="10:23">
-      <c r="J217" t="s">
-        <v>503</v>
-      </c>
-      <c r="W217" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="218" spans="10:23">
-      <c r="J218" t="s">
-        <v>504</v>
-      </c>
-      <c r="W218" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="219" spans="10:23">
-      <c r="J219" t="s">
-        <v>505</v>
-      </c>
-      <c r="W219" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="220" spans="10:23">
-      <c r="J220" t="s">
-        <v>506</v>
-      </c>
-      <c r="W220" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="221" spans="10:23">
-      <c r="J221" t="s">
-        <v>507</v>
-      </c>
-      <c r="W221" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="222" spans="10:23">
-      <c r="J222" t="s">
-        <v>508</v>
-      </c>
-      <c r="W222" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="10:23">
-      <c r="J223" t="s">
-        <v>509</v>
-      </c>
-      <c r="W223" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="224" spans="10:23">
-      <c r="J224" t="s">
-        <v>510</v>
-      </c>
-      <c r="W224" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="225" spans="10:23">
-      <c r="J225" t="s">
-        <v>511</v>
-      </c>
-      <c r="W225" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="226" spans="10:23">
-      <c r="J226" t="s">
-        <v>512</v>
-      </c>
-      <c r="W226" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="227" spans="10:23">
-      <c r="J227" t="s">
-        <v>513</v>
-      </c>
-      <c r="W227" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="228" spans="10:23">
-      <c r="J228" t="s">
-        <v>514</v>
-      </c>
-      <c r="W228" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="229" spans="10:23">
-      <c r="J229" t="s">
-        <v>515</v>
-      </c>
-      <c r="W229" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="230" spans="10:23">
-      <c r="J230" t="s">
-        <v>516</v>
-      </c>
-      <c r="W230" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="231" spans="10:23">
-      <c r="J231" t="s">
-        <v>517</v>
-      </c>
-      <c r="W231" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="232" spans="10:23">
-      <c r="J232" t="s">
-        <v>518</v>
-      </c>
-      <c r="W232" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="233" spans="10:23">
-      <c r="J233" t="s">
-        <v>519</v>
-      </c>
-      <c r="W233" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="234" spans="10:23">
-      <c r="J234" t="s">
-        <v>520</v>
-      </c>
-      <c r="W234" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="235" spans="10:23">
-      <c r="J235" t="s">
-        <v>521</v>
-      </c>
-      <c r="W235" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="236" spans="10:23">
-      <c r="J236" t="s">
-        <v>522</v>
-      </c>
-      <c r="W236" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="237" spans="10:23">
-      <c r="J237" t="s">
-        <v>523</v>
-      </c>
-      <c r="W237" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="238" spans="10:23">
-      <c r="J238" t="s">
-        <v>524</v>
-      </c>
-      <c r="W238" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="239" spans="10:23">
-      <c r="J239" t="s">
-        <v>525</v>
-      </c>
-      <c r="W239" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="240" spans="10:23">
-      <c r="J240" t="s">
-        <v>526</v>
-      </c>
-      <c r="W240" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="241" spans="10:23">
-      <c r="J241" t="s">
-        <v>527</v>
-      </c>
-      <c r="W241" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="242" spans="10:23">
-      <c r="J242" t="s">
-        <v>528</v>
-      </c>
-      <c r="W242" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="243" spans="10:23">
-      <c r="J243" t="s">
-        <v>529</v>
-      </c>
-      <c r="W243" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="244" spans="10:23">
-      <c r="J244" t="s">
-        <v>530</v>
-      </c>
-      <c r="W244" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="245" spans="10:23">
-      <c r="J245" t="s">
-        <v>531</v>
-      </c>
-      <c r="W245" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="246" spans="10:23">
-      <c r="J246" t="s">
-        <v>532</v>
-      </c>
-      <c r="W246" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="247" spans="10:23">
-      <c r="J247" t="s">
-        <v>533</v>
-      </c>
-      <c r="W247" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="248" spans="10:23">
-      <c r="J248" t="s">
-        <v>534</v>
-      </c>
-      <c r="W248" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="249" spans="10:23">
-      <c r="J249" t="s">
-        <v>535</v>
-      </c>
-      <c r="W249" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="250" spans="10:23">
-      <c r="J250" t="s">
-        <v>536</v>
-      </c>
-      <c r="W250" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="251" spans="10:23">
-      <c r="J251" t="s">
-        <v>537</v>
-      </c>
-      <c r="W251" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="252" spans="10:23">
-      <c r="J252" t="s">
-        <v>538</v>
-      </c>
-      <c r="W252" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="253" spans="10:23">
-      <c r="J253" t="s">
-        <v>539</v>
-      </c>
-      <c r="W253" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="254" spans="10:23">
-      <c r="J254" t="s">
-        <v>540</v>
-      </c>
-      <c r="W254" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="255" spans="10:23">
-      <c r="J255" t="s">
-        <v>541</v>
-      </c>
-      <c r="W255" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="256" spans="10:23">
-      <c r="J256" t="s">
-        <v>542</v>
-      </c>
-      <c r="W256" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="257" spans="10:23">
-      <c r="J257" t="s">
-        <v>543</v>
-      </c>
-      <c r="W257" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="258" spans="10:23">
-      <c r="J258" t="s">
-        <v>544</v>
-      </c>
-      <c r="W258" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="259" spans="10:23">
-      <c r="J259" t="s">
-        <v>545</v>
-      </c>
-      <c r="W259" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="260" spans="10:23">
-      <c r="J260" t="s">
-        <v>546</v>
-      </c>
-      <c r="W260" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="261" spans="10:23">
-      <c r="J261" t="s">
-        <v>547</v>
-      </c>
-      <c r="W261" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="262" spans="10:23">
-      <c r="J262" t="s">
-        <v>548</v>
-      </c>
-      <c r="W262" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="263" spans="10:23">
-      <c r="J263" t="s">
-        <v>549</v>
-      </c>
-      <c r="W263" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="264" spans="10:23">
-      <c r="J264" t="s">
-        <v>550</v>
-      </c>
-      <c r="W264" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="265" spans="10:23">
-      <c r="J265" t="s">
-        <v>551</v>
-      </c>
-      <c r="W265" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="266" spans="10:23">
-      <c r="J266" t="s">
-        <v>552</v>
-      </c>
-      <c r="W266" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="267" spans="10:23">
-      <c r="J267" t="s">
-        <v>553</v>
-      </c>
-      <c r="W267" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="268" spans="10:23">
-      <c r="J268" t="s">
-        <v>554</v>
-      </c>
-      <c r="W268" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="269" spans="10:23">
-      <c r="J269" t="s">
-        <v>555</v>
-      </c>
-      <c r="W269" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="270" spans="10:23">
-      <c r="J270" t="s">
-        <v>556</v>
-      </c>
-      <c r="W270" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="271" spans="10:23">
-      <c r="J271" t="s">
-        <v>557</v>
-      </c>
-      <c r="W271" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="272" spans="10:23">
-      <c r="J272" t="s">
-        <v>558</v>
-      </c>
-      <c r="W272" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="273" spans="10:23">
-      <c r="J273" t="s">
-        <v>559</v>
-      </c>
-      <c r="W273" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="274" spans="10:23">
-      <c r="W274" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="275" spans="10:23">
-      <c r="W275" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="276" spans="10:23">
-      <c r="W276" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="277" spans="10:23">
-      <c r="W277" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="278" spans="10:23">
-      <c r="W278" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="279" spans="10:23">
-      <c r="W279" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="280" spans="10:23">
-      <c r="W280" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="281" spans="10:23">
-      <c r="W281" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="282" spans="10:23">
-      <c r="W282" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="283" spans="10:23">
-      <c r="W283" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="284" spans="10:23">
-      <c r="W284" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="285" spans="10:23">
-      <c r="W285" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="286" spans="10:23">
-      <c r="W286" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="287" spans="10:23">
-      <c r="W287" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="288" spans="10:23">
-      <c r="W288" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="289" spans="23:23">
-      <c r="W289" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="290" spans="23:23">
-      <c r="W290" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="291" spans="23:23">
-      <c r="W291" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="292" spans="23:23">
-      <c r="W292" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="293" spans="23:23">
-      <c r="W293" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="294" spans="23:23">
-      <c r="W294" t="s">
-        <v>621</v>
+    </row>
+    <row r="293" spans="24:24">
+      <c r="X293" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="294" spans="24:24">
+      <c r="X294" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -21,16 +21,16 @@
     <definedName name="countryoftravel">'cv_sample'!$K$1:$K$273</definedName>
     <definedName name="environmentalsample">'cv_sample'!$U$1:$U$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$X$1:$X$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$X$1:$X$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$AE$1:$AE$14</definedName>
     <definedName name="hostsex">'cv_sample'!$AF$1:$AF$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AJ$1:$AJ$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
     <definedName name="travelrelation">'cv_sample'!$I$1:$I$3</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="691">
   <si>
     <t>alias</t>
   </si>
@@ -455,6 +455,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -545,6 +548,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1823,7 +1829,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1835,10 +1841,19 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
   </si>
   <si>
     <t>North Sea</t>
@@ -2623,10 +2638,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2667,10 +2682,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2697,7 +2712,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2714,7 +2729,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2731,7 +2746,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2748,7 +2763,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2765,7 +2780,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2782,7 +2797,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2799,7 +2814,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2816,7 +2831,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2833,7 +2848,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2850,7 +2865,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2864,7 +2879,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2878,7 +2893,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2892,7 +2907,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2906,7 +2921,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2920,7 +2935,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2934,7 +2949,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2948,7 +2963,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2962,7 +2977,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2972,8 +2987,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2984,7 +3002,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2995,7 +3013,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3006,7 +3024,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3017,7 +3035,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3028,7 +3046,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3039,7 +3057,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3050,7 +3068,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3061,7 +3079,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3072,7 +3090,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3083,7 +3101,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3094,7 +3112,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3105,7 +3123,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3116,7 +3134,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3124,7 +3142,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3132,7 +3150,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3140,7 +3158,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3148,7 +3166,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3156,7 +3174,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3164,7 +3182,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3172,7 +3190,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3180,7 +3198,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3188,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3196,236 +3214,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3447,27 +3470,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3487,122 +3510,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3626,312 +3649,312 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:52" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -3970,258 +3993,258 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I1:AJ289"/>
+  <dimension ref="I1:AJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="9:36">
       <c r="I1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="X1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AE1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AF1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="AJ1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="9:36">
       <c r="I2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="U2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z2" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AE2" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="AF2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="AJ2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="9:36">
       <c r="I3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="X3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Z3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AE3" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AF3" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="9:36">
       <c r="K4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="X4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AE4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AF4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="9:36">
       <c r="K5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="X5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AE5" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AF5" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="9:36">
       <c r="K6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="X6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AE6" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AF6" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" spans="9:36">
       <c r="K7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="X7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AE7" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AF7" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="9:36">
       <c r="K8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AE8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AF8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="9:36">
       <c r="K9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="X9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AE9" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AF9" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="9:36">
       <c r="K10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="X10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AE10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AF10" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="9:36">
       <c r="K11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="X11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AE11" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AF11" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="9:36">
       <c r="K12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="X12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AE12" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AF12" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="9:36">
       <c r="K13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="X13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AE13" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="AF13" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="9:36">
       <c r="K14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="X14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AE14" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AF14" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15" spans="9:36">
       <c r="K15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="X15" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AF15" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="16" spans="9:36">
       <c r="K16" t="s">
+        <v>304</v>
+      </c>
+      <c r="X16" t="s">
         <v>302</v>
-      </c>
-      <c r="X16" t="s">
-        <v>300</v>
       </c>
       <c r="AF16" t="s">
         <v>116</v>
@@ -4229,1562 +4252,1562 @@
     </row>
     <row r="17" spans="11:32">
       <c r="K17" t="s">
+        <v>305</v>
+      </c>
+      <c r="X17" t="s">
         <v>303</v>
       </c>
-      <c r="X17" t="s">
-        <v>301</v>
-      </c>
       <c r="AF17" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" spans="11:32">
       <c r="K18" t="s">
+        <v>306</v>
+      </c>
+      <c r="X18" t="s">
         <v>304</v>
-      </c>
-      <c r="X18" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="19" spans="11:32">
       <c r="K19" t="s">
+        <v>307</v>
+      </c>
+      <c r="X19" t="s">
         <v>305</v>
-      </c>
-      <c r="X19" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="20" spans="11:32">
       <c r="K20" t="s">
+        <v>308</v>
+      </c>
+      <c r="X20" t="s">
         <v>306</v>
-      </c>
-      <c r="X20" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="21" spans="11:32">
       <c r="K21" t="s">
+        <v>309</v>
+      </c>
+      <c r="X21" t="s">
         <v>307</v>
-      </c>
-      <c r="X21" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="22" spans="11:32">
       <c r="K22" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="X22" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="23" spans="11:32">
       <c r="K23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="X23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="11:32">
       <c r="K24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="X24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="11:32">
       <c r="K25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="11:32">
       <c r="K26" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="11:32">
       <c r="K27" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="X27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="11:32">
       <c r="K28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="X28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="11:32">
       <c r="K29" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X29" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="11:32">
       <c r="K30" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="11:32">
       <c r="K31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="X31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="11:32">
       <c r="K32" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X32" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="11:24">
       <c r="K33" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="X33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="34" spans="11:24">
       <c r="K34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="X34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" spans="11:24">
       <c r="K35" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="X35" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="11:24">
       <c r="K36" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="X36" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="11:24">
       <c r="K37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="X37" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="11:24">
       <c r="K38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="X38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="11:24">
       <c r="K39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="X39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="11:24">
       <c r="K40" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="X40" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="11:24">
       <c r="K41" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="X41" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="11:24">
       <c r="K42" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="X42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="11:24">
       <c r="K43" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="X43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="11:24">
       <c r="K44" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="X44" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="11:24">
       <c r="K45" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="X45" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="11:24">
       <c r="K46" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="X46" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="11:24">
       <c r="K47" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="X47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="11:24">
       <c r="K48" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="X48" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" spans="11:24">
       <c r="K49" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="X49" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="11:24">
       <c r="K50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="X50" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="11:24">
       <c r="K51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="X51" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="11:24">
       <c r="K52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="X52" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="11:24">
       <c r="K53" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="X53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="11:24">
       <c r="K54" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="X54" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="11:24">
       <c r="K55" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="X55" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="11:24">
       <c r="K56" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X56" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="11:24">
       <c r="K57" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="X57" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="11:24">
       <c r="K58" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X58" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="11:24">
       <c r="K59" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="X59" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="11:24">
       <c r="K60" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="X60" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="11:24">
       <c r="K61" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="X61" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="11:24">
       <c r="K62" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X62" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="11:24">
       <c r="K63" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X63" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="64" spans="11:24">
       <c r="K64" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X64" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="11:24">
       <c r="K65" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X65" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="11:24">
       <c r="K66" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="X66" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="11:24">
       <c r="K67" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="X67" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="11:24">
       <c r="K68" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="X68" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="11:24">
       <c r="K69" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="X69" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="11:24">
       <c r="K70" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="X70" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="11:24">
       <c r="K71" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="X71" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="72" spans="11:24">
       <c r="K72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="X72" t="s">
-        <v>594</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="11:24">
       <c r="K73" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="X73" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="74" spans="11:24">
       <c r="K74" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="X74" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="75" spans="11:24">
       <c r="K75" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="X75" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" spans="11:24">
       <c r="K76" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="X76" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="11:24">
       <c r="K77" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="X77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78" spans="11:24">
       <c r="K78" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="X78" t="s">
-        <v>359</v>
+        <v>596</v>
       </c>
     </row>
     <row r="79" spans="11:24">
       <c r="K79" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="X79" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="80" spans="11:24">
       <c r="K80" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="X80" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="11:24">
       <c r="K81" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="X81" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="82" spans="11:24">
       <c r="K82" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="X82" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="83" spans="11:24">
       <c r="K83" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="X83" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="11:24">
       <c r="K84" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="X84" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" spans="11:24">
       <c r="K85" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="X85" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="86" spans="11:24">
       <c r="K86" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="X86" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="11:24">
       <c r="K87" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="X87" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="88" spans="11:24">
       <c r="K88" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="X88" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="11:24">
       <c r="K89" t="s">
+        <v>377</v>
+      </c>
+      <c r="X89" t="s">
         <v>375</v>
-      </c>
-      <c r="X89" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="90" spans="11:24">
       <c r="K90" t="s">
+        <v>378</v>
+      </c>
+      <c r="X90" t="s">
         <v>376</v>
-      </c>
-      <c r="X90" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="91" spans="11:24">
       <c r="K91" t="s">
+        <v>379</v>
+      </c>
+      <c r="X91" t="s">
         <v>377</v>
-      </c>
-      <c r="X91" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="92" spans="11:24">
       <c r="K92" t="s">
+        <v>380</v>
+      </c>
+      <c r="X92" t="s">
         <v>378</v>
-      </c>
-      <c r="X92" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="93" spans="11:24">
       <c r="K93" t="s">
+        <v>381</v>
+      </c>
+      <c r="X93" t="s">
         <v>379</v>
-      </c>
-      <c r="X93" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="94" spans="11:24">
       <c r="K94" t="s">
+        <v>382</v>
+      </c>
+      <c r="X94" t="s">
         <v>380</v>
-      </c>
-      <c r="X94" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="95" spans="11:24">
       <c r="K95" t="s">
+        <v>383</v>
+      </c>
+      <c r="X95" t="s">
         <v>381</v>
-      </c>
-      <c r="X95" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="96" spans="11:24">
       <c r="K96" t="s">
+        <v>384</v>
+      </c>
+      <c r="X96" t="s">
         <v>382</v>
-      </c>
-      <c r="X96" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="97" spans="11:24">
       <c r="K97" t="s">
+        <v>385</v>
+      </c>
+      <c r="X97" t="s">
         <v>383</v>
-      </c>
-      <c r="X97" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="98" spans="11:24">
       <c r="K98" t="s">
+        <v>386</v>
+      </c>
+      <c r="X98" t="s">
         <v>384</v>
-      </c>
-      <c r="X98" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="99" spans="11:24">
       <c r="K99" t="s">
+        <v>387</v>
+      </c>
+      <c r="X99" t="s">
         <v>385</v>
-      </c>
-      <c r="X99" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="100" spans="11:24">
       <c r="K100" t="s">
+        <v>388</v>
+      </c>
+      <c r="X100" t="s">
         <v>386</v>
-      </c>
-      <c r="X100" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="101" spans="11:24">
       <c r="K101" t="s">
+        <v>389</v>
+      </c>
+      <c r="X101" t="s">
         <v>387</v>
-      </c>
-      <c r="X101" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="102" spans="11:24">
       <c r="K102" t="s">
+        <v>390</v>
+      </c>
+      <c r="X102" t="s">
         <v>388</v>
-      </c>
-      <c r="X102" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="103" spans="11:24">
       <c r="K103" t="s">
+        <v>391</v>
+      </c>
+      <c r="X103" t="s">
         <v>389</v>
-      </c>
-      <c r="X103" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="104" spans="11:24">
       <c r="K104" t="s">
+        <v>392</v>
+      </c>
+      <c r="X104" t="s">
         <v>390</v>
-      </c>
-      <c r="X104" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="105" spans="11:24">
       <c r="K105" t="s">
+        <v>393</v>
+      </c>
+      <c r="X105" t="s">
         <v>391</v>
-      </c>
-      <c r="X105" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="106" spans="11:24">
       <c r="K106" t="s">
+        <v>394</v>
+      </c>
+      <c r="X106" t="s">
         <v>392</v>
-      </c>
-      <c r="X106" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="107" spans="11:24">
       <c r="K107" t="s">
+        <v>395</v>
+      </c>
+      <c r="X107" t="s">
         <v>393</v>
-      </c>
-      <c r="X107" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="108" spans="11:24">
       <c r="K108" t="s">
+        <v>396</v>
+      </c>
+      <c r="X108" t="s">
         <v>394</v>
-      </c>
-      <c r="X108" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="109" spans="11:24">
       <c r="K109" t="s">
+        <v>397</v>
+      </c>
+      <c r="X109" t="s">
         <v>395</v>
-      </c>
-      <c r="X109" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="110" spans="11:24">
       <c r="K110" t="s">
+        <v>398</v>
+      </c>
+      <c r="X110" t="s">
         <v>396</v>
-      </c>
-      <c r="X110" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="111" spans="11:24">
       <c r="K111" t="s">
+        <v>399</v>
+      </c>
+      <c r="X111" t="s">
         <v>397</v>
-      </c>
-      <c r="X111" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="112" spans="11:24">
       <c r="K112" t="s">
+        <v>400</v>
+      </c>
+      <c r="X112" t="s">
         <v>398</v>
-      </c>
-      <c r="X112" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="113" spans="11:24">
       <c r="K113" t="s">
+        <v>401</v>
+      </c>
+      <c r="X113" t="s">
         <v>399</v>
-      </c>
-      <c r="X113" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="114" spans="11:24">
       <c r="K114" t="s">
+        <v>402</v>
+      </c>
+      <c r="X114" t="s">
         <v>400</v>
-      </c>
-      <c r="X114" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="115" spans="11:24">
       <c r="K115" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="X115" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="116" spans="11:24">
       <c r="K116" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="X116" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="11:24">
       <c r="K117" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="X117" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="11:24">
       <c r="K118" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="X118" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="11:24">
       <c r="K119" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="X119" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="120" spans="11:24">
       <c r="K120" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="X120" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" spans="11:24">
       <c r="K121" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="X121" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="122" spans="11:24">
       <c r="K122" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="X122" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="123" spans="11:24">
       <c r="K123" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="X123" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="124" spans="11:24">
       <c r="K124" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="X124" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="125" spans="11:24">
       <c r="K125" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="X125" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="126" spans="11:24">
       <c r="K126" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="X126" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="127" spans="11:24">
       <c r="K127" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="X127" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="128" spans="11:24">
       <c r="K128" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="X128" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="129" spans="11:24">
       <c r="K129" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="X129" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="11:24">
       <c r="K130" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="X130" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="131" spans="11:24">
       <c r="K131" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="X131" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="132" spans="11:24">
       <c r="K132" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="X132" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="133" spans="11:24">
       <c r="K133" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="X133" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="134" spans="11:24">
       <c r="K134" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="X134" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="135" spans="11:24">
       <c r="K135" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="X135" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="136" spans="11:24">
       <c r="K136" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="X136" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="137" spans="11:24">
       <c r="K137" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="X137" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="11:24">
       <c r="K138" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="X138" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="139" spans="11:24">
       <c r="K139" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="X139" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="140" spans="11:24">
       <c r="K140" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="X140" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="141" spans="11:24">
       <c r="K141" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="X141" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="142" spans="11:24">
       <c r="K142" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="X142" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="143" spans="11:24">
       <c r="K143" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="X143" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="144" spans="11:24">
       <c r="K144" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="X144" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="145" spans="11:24">
       <c r="K145" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="X145" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="146" spans="11:24">
       <c r="K146" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="X146" t="s">
-        <v>429</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147" spans="11:24">
       <c r="K147" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="X147" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="148" spans="11:24">
       <c r="K148" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="X148" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="149" spans="11:24">
       <c r="K149" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="X149" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="150" spans="11:24">
       <c r="K150" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="X150" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="151" spans="11:24">
       <c r="K151" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="X151" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="152" spans="11:24">
       <c r="K152" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="X152" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="153" spans="11:24">
       <c r="K153" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="X153" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="154" spans="11:24">
       <c r="K154" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="X154" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="155" spans="11:24">
       <c r="K155" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="X155" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="156" spans="11:24">
       <c r="K156" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="X156" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="157" spans="11:24">
       <c r="K157" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="X157" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="158" spans="11:24">
       <c r="K158" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="X158" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="159" spans="11:24">
       <c r="K159" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="X159" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="160" spans="11:24">
       <c r="K160" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="X160" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="161" spans="11:24">
       <c r="K161" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="X161" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="162" spans="11:24">
       <c r="K162" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X162" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="163" spans="11:24">
       <c r="K163" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="X163" t="s">
-        <v>445</v>
+        <v>602</v>
       </c>
     </row>
     <row r="164" spans="11:24">
       <c r="K164" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="X164" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" spans="11:24">
       <c r="K165" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="X165" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="11:24">
       <c r="K166" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="X166" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="167" spans="11:24">
       <c r="K167" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="X167" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="168" spans="11:24">
       <c r="K168" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="X168" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="11:24">
       <c r="K169" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="X169" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="170" spans="11:24">
       <c r="K170" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="X170" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="11:24">
       <c r="K171" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="X171" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="172" spans="11:24">
       <c r="K172" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="X172" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="173" spans="11:24">
       <c r="K173" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="X173" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="174" spans="11:24">
       <c r="K174" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="X174" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="175" spans="11:24">
       <c r="K175" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="X175" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="11:24">
       <c r="K176" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="X176" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="177" spans="11:24">
       <c r="K177" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="X177" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="11:24">
       <c r="K178" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="X178" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="179" spans="11:24">
       <c r="K179" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="X179" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="11:24">
       <c r="K180" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="X180" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="181" spans="11:24">
       <c r="K181" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="X181" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="182" spans="11:24">
       <c r="K182" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="X182" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="183" spans="11:24">
       <c r="K183" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="X183" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="184" spans="11:24">
       <c r="K184" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="X184" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="185" spans="11:24">
       <c r="K185" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="X185" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="186" spans="11:24">
       <c r="K186" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="X186" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="187" spans="11:24">
       <c r="K187" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="X187" t="s">
-        <v>468</v>
+        <v>605</v>
       </c>
     </row>
     <row r="188" spans="11:24">
       <c r="K188" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="X188" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="189" spans="11:24">
       <c r="K189" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="X189" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="190" spans="11:24">
       <c r="K190" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="X190" t="s">
-        <v>601</v>
+        <v>472</v>
       </c>
     </row>
     <row r="191" spans="11:24">
       <c r="K191" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="X191" t="s">
-        <v>471</v>
+        <v>606</v>
       </c>
     </row>
     <row r="192" spans="11:24">
       <c r="K192" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="X192" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="193" spans="11:24">
       <c r="K193" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="X193" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="194" spans="11:24">
       <c r="K194" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X194" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="195" spans="11:24">
       <c r="K195" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="X195" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="196" spans="11:24">
       <c r="K196" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="X196" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="197" spans="11:24">
       <c r="K197" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="X197" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="198" spans="11:24">
       <c r="K198" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="X198" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="199" spans="11:24">
       <c r="K199" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="X199" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="200" spans="11:24">
       <c r="K200" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="X200" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="201" spans="11:24">
       <c r="K201" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X201" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="202" spans="11:24">
       <c r="K202" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X202" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="11:24">
       <c r="K203" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="X203" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="11:24">
       <c r="K204" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="X204" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="11:24">
       <c r="K205" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="X205" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="206" spans="11:24">
       <c r="K206" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="X206" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="207" spans="11:24">
       <c r="K207" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="X207" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="208" spans="11:24">
       <c r="K208" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="X208" t="s">
-        <v>602</v>
+        <v>489</v>
       </c>
     </row>
     <row r="209" spans="11:24">
       <c r="K209" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="X209" t="s">
-        <v>488</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="11:24">
       <c r="K210" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="X210" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="211" spans="11:24">
       <c r="K211" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="X211" t="s">
         <v>491</v>
@@ -5792,7 +5815,7 @@
     </row>
     <row r="212" spans="11:24">
       <c r="K212" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="X212" t="s">
         <v>492</v>
@@ -5800,7 +5823,7 @@
     </row>
     <row r="213" spans="11:24">
       <c r="K213" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="X213" t="s">
         <v>493</v>
@@ -5808,23 +5831,23 @@
     </row>
     <row r="214" spans="11:24">
       <c r="K214" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="X214" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="11:24">
       <c r="K215" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="X215" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="216" spans="11:24">
       <c r="K216" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="X216" t="s">
         <v>497</v>
@@ -5832,7 +5855,7 @@
     </row>
     <row r="217" spans="11:24">
       <c r="K217" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="X217" t="s">
         <v>498</v>
@@ -5840,7 +5863,7 @@
     </row>
     <row r="218" spans="11:24">
       <c r="K218" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="X218" t="s">
         <v>499</v>
@@ -5848,7 +5871,7 @@
     </row>
     <row r="219" spans="11:24">
       <c r="K219" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="X219" t="s">
         <v>500</v>
@@ -5856,55 +5879,55 @@
     </row>
     <row r="220" spans="11:24">
       <c r="K220" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="X220" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="11:24">
       <c r="K221" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="X221" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="222" spans="11:24">
       <c r="K222" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="X222" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="223" spans="11:24">
       <c r="K223" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="X223" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="224" spans="11:24">
       <c r="K224" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="X224" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="225" spans="11:24">
       <c r="K225" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="X225" t="s">
-        <v>603</v>
+        <v>506</v>
       </c>
     </row>
     <row r="226" spans="11:24">
       <c r="K226" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="X226" t="s">
         <v>507</v>
@@ -5912,7 +5935,7 @@
     </row>
     <row r="227" spans="11:24">
       <c r="K227" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="X227" t="s">
         <v>508</v>
@@ -5920,410 +5943,410 @@
     </row>
     <row r="228" spans="11:24">
       <c r="K228" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="X228" t="s">
-        <v>509</v>
+        <v>608</v>
       </c>
     </row>
     <row r="229" spans="11:24">
       <c r="K229" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="X229" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="230" spans="11:24">
       <c r="K230" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="X230" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="231" spans="11:24">
       <c r="K231" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="X231" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="232" spans="11:24">
       <c r="K232" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="X232" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="233" spans="11:24">
       <c r="K233" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="X233" t="s">
-        <v>604</v>
+        <v>513</v>
       </c>
     </row>
     <row r="234" spans="11:24">
       <c r="K234" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="X234" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="235" spans="11:24">
       <c r="K235" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="X235" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="236" spans="11:24">
       <c r="K236" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="X236" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="237" spans="11:24">
       <c r="K237" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="X237" t="s">
-        <v>519</v>
+        <v>609</v>
       </c>
     </row>
     <row r="238" spans="11:24">
       <c r="K238" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="X238" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="239" spans="11:24">
       <c r="K239" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="X239" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="240" spans="11:24">
       <c r="K240" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="X240" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="241" spans="11:24">
       <c r="K241" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="X241" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="242" spans="11:24">
       <c r="K242" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="X242" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="243" spans="11:24">
       <c r="K243" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="X243" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="244" spans="11:24">
       <c r="K244" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="X244" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="245" spans="11:24">
       <c r="K245" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="X245" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="246" spans="11:24">
       <c r="K246" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="X246" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="247" spans="11:24">
       <c r="K247" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="X247" t="s">
-        <v>605</v>
+        <v>527</v>
       </c>
     </row>
     <row r="248" spans="11:24">
       <c r="K248" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="X248" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="249" spans="11:24">
       <c r="K249" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="X249" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="250" spans="11:24">
       <c r="K250" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="X250" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="251" spans="11:24">
       <c r="K251" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="X251" t="s">
-        <v>533</v>
+        <v>610</v>
       </c>
     </row>
     <row r="252" spans="11:24">
       <c r="K252" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="X252" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="253" spans="11:24">
       <c r="K253" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="X253" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="254" spans="11:24">
       <c r="K254" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="X254" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="255" spans="11:24">
       <c r="K255" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="X255" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="256" spans="11:24">
       <c r="K256" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="X256" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="257" spans="11:24">
       <c r="K257" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="X257" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="258" spans="11:24">
       <c r="K258" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="X258" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="259" spans="11:24">
       <c r="K259" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="X259" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="260" spans="11:24">
       <c r="K260" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="X260" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="261" spans="11:24">
       <c r="K261" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="X261" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="262" spans="11:24">
       <c r="K262" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="X262" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="263" spans="11:24">
       <c r="K263" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="X263" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="264" spans="11:24">
       <c r="K264" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="X264" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="265" spans="11:24">
       <c r="K265" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="X265" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="266" spans="11:24">
       <c r="K266" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="X266" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="267" spans="11:24">
       <c r="K267" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="X267" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="268" spans="11:24">
       <c r="K268" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="X268" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="269" spans="11:24">
       <c r="K269" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="X269" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="270" spans="11:24">
       <c r="K270" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="X270" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="271" spans="11:24">
       <c r="K271" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="X271" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="272" spans="11:24">
       <c r="K272" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="X272" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="273" spans="11:24">
       <c r="K273" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="X273" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="274" spans="11:24">
       <c r="X274" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="275" spans="11:24">
       <c r="X275" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="276" spans="11:24">
       <c r="X276" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="277" spans="11:24">
       <c r="X277" t="s">
-        <v>606</v>
+        <v>557</v>
       </c>
     </row>
     <row r="278" spans="11:24">
       <c r="X278" t="s">
-        <v>607</v>
+        <v>558</v>
       </c>
     </row>
     <row r="279" spans="11:24">
       <c r="X279" t="s">
-        <v>608</v>
+        <v>559</v>
       </c>
     </row>
     <row r="280" spans="11:24">
       <c r="X280" t="s">
-        <v>609</v>
+        <v>560</v>
       </c>
     </row>
     <row r="281" spans="11:24">
       <c r="X281" t="s">
-        <v>610</v>
+        <v>561</v>
       </c>
     </row>
     <row r="282" spans="11:24">
@@ -6364,6 +6387,31 @@
     <row r="289" spans="24:24">
       <c r="X289" t="s">
         <v>618</v>
+      </c>
+    </row>
+    <row r="290" spans="24:24">
+      <c r="X290" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="291" spans="24:24">
+      <c r="X291" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="292" spans="24:24">
+      <c r="X292" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="293" spans="24:24">
+      <c r="X293" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="294" spans="24:24">
+      <c r="X294" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -25,7 +25,7 @@
     <definedName name="hostdiseaseoutcome">'cv_sample'!$Z$1:$Z$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$AE$1:$AE$14</definedName>
     <definedName name="hostsex">'cv_sample'!$AF$1:$AF$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AJ$1:$AJ$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="692">
   <si>
     <t>alias</t>
   </si>
@@ -735,6 +735,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2641,7 +2644,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2685,7 +2688,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2712,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3449,6 +3452,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3470,27 +3478,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3510,122 +3518,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3649,312 +3657,312 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2" spans="1:52" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -3998,253 +4006,253 @@
   <sheetData>
     <row r="1" spans="9:36">
       <c r="I1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="U1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="X1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AE1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AF1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" spans="9:36">
       <c r="I2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="X2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AE2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AF2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AJ2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" spans="9:36">
       <c r="I3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="X3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AE3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AF3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="9:36">
       <c r="K4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AE4" t="s">
+        <v>614</v>
+      </c>
+      <c r="AF4" t="s">
         <v>613</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="5" spans="9:36">
       <c r="K5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="X5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AE5" t="s">
+        <v>615</v>
+      </c>
+      <c r="AF5" t="s">
         <v>614</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="6" spans="9:36">
       <c r="K6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="X6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AE6" t="s">
+        <v>616</v>
+      </c>
+      <c r="AF6" t="s">
         <v>615</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="7" spans="9:36">
       <c r="K7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="X7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AE7" t="s">
+        <v>617</v>
+      </c>
+      <c r="AF7" t="s">
         <v>616</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="8" spans="9:36">
       <c r="K8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="X8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AE8" t="s">
+        <v>618</v>
+      </c>
+      <c r="AF8" t="s">
         <v>617</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="9" spans="9:36">
       <c r="K9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="X9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AE9" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF9" t="s">
         <v>618</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="10" spans="9:36">
       <c r="K10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AE10" t="s">
+        <v>620</v>
+      </c>
+      <c r="AF10" t="s">
         <v>619</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="11" spans="9:36">
       <c r="K11" t="s">
+        <v>300</v>
+      </c>
+      <c r="X11" t="s">
         <v>299</v>
       </c>
-      <c r="X11" t="s">
-        <v>298</v>
-      </c>
       <c r="AE11" t="s">
+        <v>621</v>
+      </c>
+      <c r="AF11" t="s">
         <v>620</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="12" spans="9:36">
       <c r="K12" t="s">
+        <v>301</v>
+      </c>
+      <c r="X12" t="s">
         <v>300</v>
       </c>
-      <c r="X12" t="s">
-        <v>299</v>
-      </c>
       <c r="AE12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AF12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="9:36">
       <c r="K13" t="s">
+        <v>302</v>
+      </c>
+      <c r="X13" t="s">
         <v>301</v>
       </c>
-      <c r="X13" t="s">
-        <v>300</v>
-      </c>
       <c r="AE13" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AF13" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="9:36">
       <c r="K14" t="s">
+        <v>303</v>
+      </c>
+      <c r="X14" t="s">
         <v>302</v>
       </c>
-      <c r="X14" t="s">
-        <v>301</v>
-      </c>
       <c r="AE14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AF14" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="9:36">
       <c r="K15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="X15" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF15" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16" spans="9:36">
       <c r="K16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="X16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AF16" t="s">
         <v>116</v>
@@ -4252,2166 +4260,2166 @@
     </row>
     <row r="17" spans="11:32">
       <c r="K17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="X17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AF17" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="18" spans="11:32">
       <c r="K18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="X18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="11:32">
       <c r="K19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="X19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="11:32">
       <c r="K20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="11:32">
       <c r="K21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="11:32">
       <c r="K22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="X22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="23" spans="11:32">
       <c r="K23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="11:32">
       <c r="K24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="11:32">
       <c r="K25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="11:32">
       <c r="K26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="11:32">
       <c r="K27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="11:32">
       <c r="K28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="X28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="11:32">
       <c r="K29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="11:32">
       <c r="K30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="X30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="11:32">
       <c r="K31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="11:32">
       <c r="K32" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="11:24">
       <c r="K33" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="X33" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="34" spans="11:24">
       <c r="K34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="11:24">
       <c r="K35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="X35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="11:24">
       <c r="K36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="X36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="11:24">
       <c r="K37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X37" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="11:24">
       <c r="K38" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="11:24">
       <c r="K39" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X39" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="11:24">
       <c r="K40" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="X40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="11:24">
       <c r="K41" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="11:24">
       <c r="K42" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="X42" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="11:24">
       <c r="K43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X43" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44" spans="11:24">
       <c r="K44" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="X44" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="11:24">
       <c r="K45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="X45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="11:24">
       <c r="K46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="X46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="11:24">
       <c r="K47" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="X47" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="11:24">
       <c r="K48" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="X48" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="11:24">
       <c r="K49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X49" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" spans="11:24">
       <c r="K50" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X50" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="11:24">
       <c r="K51" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="X51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="52" spans="11:24">
       <c r="K52" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="X52" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="53" spans="11:24">
       <c r="K53" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="X53" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54" spans="11:24">
       <c r="K54" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="X54" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="55" spans="11:24">
       <c r="K55" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X55" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="11:24">
       <c r="K56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="X56" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57" spans="11:24">
       <c r="K57" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="X57" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="11:24">
       <c r="K58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="X58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" spans="11:24">
       <c r="K59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="X59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="11:24">
       <c r="K60" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="X60" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="11:24">
       <c r="K61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X61" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="11:24">
       <c r="K62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X62" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" spans="11:24">
       <c r="K63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X63" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="64" spans="11:24">
       <c r="K64" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X64" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="11:24">
       <c r="K65" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X65" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="66" spans="11:24">
       <c r="K66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="67" spans="11:24">
       <c r="K67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="X67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="11:24">
       <c r="K68" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X68" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="69" spans="11:24">
       <c r="K69" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="X69" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" spans="11:24">
       <c r="K70" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X70" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="71" spans="11:24">
       <c r="K71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X71" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="72" spans="11:24">
       <c r="K72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="11:24">
       <c r="K73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="X73" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="74" spans="11:24">
       <c r="K74" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X74" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="11:24">
       <c r="K75" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X75" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="11:24">
       <c r="K76" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X76" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="77" spans="11:24">
       <c r="K77" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="X77" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" spans="11:24">
       <c r="K78" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X78" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" spans="11:24">
       <c r="K79" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="X79" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="11:24">
       <c r="K80" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X80" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="11:24">
       <c r="K81" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="X81" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="82" spans="11:24">
       <c r="K82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X82" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="11:24">
       <c r="K83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="X83" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="11:24">
       <c r="K84" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X84" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="11:24">
       <c r="K85" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="X85" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86" spans="11:24">
       <c r="K86" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X86" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87" spans="11:24">
       <c r="K87" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="X87" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="88" spans="11:24">
       <c r="K88" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X88" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="89" spans="11:24">
       <c r="K89" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="X89" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="11:24">
       <c r="K90" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X90" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="11:24">
       <c r="K91" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="X91" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="11:24">
       <c r="K92" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X92" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" spans="11:24">
       <c r="K93" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="X93" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="11:24">
       <c r="K94" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="11:24">
       <c r="K95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X95" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" spans="11:24">
       <c r="K96" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X96" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="11:24">
       <c r="K97" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="X97" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="11:24">
       <c r="K98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X98" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="11:24">
       <c r="K99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="X99" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="11:24">
       <c r="K100" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X100" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="11:24">
       <c r="K101" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X101" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="102" spans="11:24">
       <c r="K102" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="11:24">
       <c r="K103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X103" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="104" spans="11:24">
       <c r="K104" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X104" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="11:24">
       <c r="K105" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="X105" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="11:24">
       <c r="K106" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X106" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="107" spans="11:24">
       <c r="K107" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X107" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="108" spans="11:24">
       <c r="K108" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X108" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="11:24">
       <c r="K109" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="X109" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="11:24">
       <c r="K110" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X110" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="11:24">
       <c r="K111" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="X111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="11:24">
       <c r="K112" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="X112" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="11:24">
       <c r="K113" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="X113" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="11:24">
       <c r="K114" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="X114" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="11:24">
       <c r="K115" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="X115" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="11:24">
       <c r="K116" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="X116" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="117" spans="11:24">
       <c r="K117" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="X117" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="11:24">
       <c r="K118" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="X118" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="119" spans="11:24">
       <c r="K119" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X119" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="120" spans="11:24">
       <c r="K120" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="X120" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="121" spans="11:24">
       <c r="K121" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="X121" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="122" spans="11:24">
       <c r="K122" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="X122" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="123" spans="11:24">
       <c r="K123" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="X123" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="124" spans="11:24">
       <c r="K124" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X124" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="125" spans="11:24">
       <c r="K125" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="X125" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="126" spans="11:24">
       <c r="K126" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="X126" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="127" spans="11:24">
       <c r="K127" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X127" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="128" spans="11:24">
       <c r="K128" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X128" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="129" spans="11:24">
       <c r="K129" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="X129" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="130" spans="11:24">
       <c r="K130" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="X130" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="131" spans="11:24">
       <c r="K131" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="X131" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="132" spans="11:24">
       <c r="K132" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="X132" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="133" spans="11:24">
       <c r="K133" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="X133" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="134" spans="11:24">
       <c r="K134" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="X134" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="135" spans="11:24">
       <c r="K135" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="X135" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="11:24">
       <c r="K136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="X136" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="11:24">
       <c r="K137" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="X137" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="138" spans="11:24">
       <c r="K138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="X138" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="139" spans="11:24">
       <c r="K139" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X139" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="140" spans="11:24">
       <c r="K140" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="X140" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="141" spans="11:24">
       <c r="K141" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="X141" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="142" spans="11:24">
       <c r="K142" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="X142" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="143" spans="11:24">
       <c r="K143" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X143" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="144" spans="11:24">
       <c r="K144" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="X144" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" spans="11:24">
       <c r="K145" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="X145" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="146" spans="11:24">
       <c r="K146" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="X146" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="147" spans="11:24">
       <c r="K147" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="X147" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="148" spans="11:24">
       <c r="K148" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="X148" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="149" spans="11:24">
       <c r="K149" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="X149" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="150" spans="11:24">
       <c r="K150" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="X150" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="151" spans="11:24">
       <c r="K151" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="X151" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="152" spans="11:24">
       <c r="K152" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X152" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="153" spans="11:24">
       <c r="K153" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X153" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="154" spans="11:24">
       <c r="K154" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="X154" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="155" spans="11:24">
       <c r="K155" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="X155" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="156" spans="11:24">
       <c r="K156" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X156" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="157" spans="11:24">
       <c r="K157" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="X157" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="158" spans="11:24">
       <c r="K158" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="X158" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="159" spans="11:24">
       <c r="K159" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="X159" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="160" spans="11:24">
       <c r="K160" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X160" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="161" spans="11:24">
       <c r="K161" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="X161" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="162" spans="11:24">
       <c r="K162" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="X162" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="163" spans="11:24">
       <c r="K163" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="X163" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="164" spans="11:24">
       <c r="K164" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="X164" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="165" spans="11:24">
       <c r="K165" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="X165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="166" spans="11:24">
       <c r="K166" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="X166" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="167" spans="11:24">
       <c r="K167" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="X167" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="168" spans="11:24">
       <c r="K168" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="X168" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="169" spans="11:24">
       <c r="K169" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="X169" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="170" spans="11:24">
       <c r="K170" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="X170" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171" spans="11:24">
       <c r="K171" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="X171" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="172" spans="11:24">
       <c r="K172" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="X172" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="173" spans="11:24">
       <c r="K173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="X173" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="174" spans="11:24">
       <c r="K174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="X174" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="175" spans="11:24">
       <c r="K175" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="X175" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="176" spans="11:24">
       <c r="K176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="X176" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177" spans="11:24">
       <c r="K177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="X177" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178" spans="11:24">
       <c r="K178" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="X178" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="179" spans="11:24">
       <c r="K179" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="X179" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="180" spans="11:24">
       <c r="K180" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="X180" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="181" spans="11:24">
       <c r="K181" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="X181" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="182" spans="11:24">
       <c r="K182" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="X182" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="183" spans="11:24">
       <c r="K183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="X183" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="184" spans="11:24">
       <c r="K184" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="X184" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="185" spans="11:24">
       <c r="K185" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="X185" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="186" spans="11:24">
       <c r="K186" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="X186" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="187" spans="11:24">
       <c r="K187" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="X187" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="188" spans="11:24">
       <c r="K188" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="X188" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="189" spans="11:24">
       <c r="K189" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="X189" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="190" spans="11:24">
       <c r="K190" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="X190" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="191" spans="11:24">
       <c r="K191" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="X191" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="192" spans="11:24">
       <c r="K192" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="X192" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="193" spans="11:24">
       <c r="K193" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X193" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="194" spans="11:24">
       <c r="K194" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="X194" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="195" spans="11:24">
       <c r="K195" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="X195" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="196" spans="11:24">
       <c r="K196" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="X196" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="197" spans="11:24">
       <c r="K197" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="X197" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="198" spans="11:24">
       <c r="K198" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="X198" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="199" spans="11:24">
       <c r="K199" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="X199" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="200" spans="11:24">
       <c r="K200" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="X200" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="201" spans="11:24">
       <c r="K201" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="X201" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="202" spans="11:24">
       <c r="K202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="X202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="11:24">
       <c r="K203" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="X203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204" spans="11:24">
       <c r="K204" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="X204" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="205" spans="11:24">
       <c r="K205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="X205" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="206" spans="11:24">
       <c r="K206" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="X206" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="207" spans="11:24">
       <c r="K207" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="X207" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="208" spans="11:24">
       <c r="K208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="X208" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="209" spans="11:24">
       <c r="K209" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="X209" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="210" spans="11:24">
       <c r="K210" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="X210" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="211" spans="11:24">
       <c r="K211" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="X211" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="212" spans="11:24">
       <c r="K212" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="X212" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="213" spans="11:24">
       <c r="K213" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="X213" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="214" spans="11:24">
       <c r="K214" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="X214" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="215" spans="11:24">
       <c r="K215" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="X215" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="216" spans="11:24">
       <c r="K216" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="X216" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="217" spans="11:24">
       <c r="K217" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="X217" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="218" spans="11:24">
       <c r="K218" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="X218" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="219" spans="11:24">
       <c r="K219" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="X219" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="220" spans="11:24">
       <c r="K220" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="X220" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="221" spans="11:24">
       <c r="K221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="X221" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="222" spans="11:24">
       <c r="K222" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="X222" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="223" spans="11:24">
       <c r="K223" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="X223" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="224" spans="11:24">
       <c r="K224" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="X224" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="225" spans="11:24">
       <c r="K225" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="X225" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="226" spans="11:24">
       <c r="K226" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="X226" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="227" spans="11:24">
       <c r="K227" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="X227" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="228" spans="11:24">
       <c r="K228" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="X228" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="229" spans="11:24">
       <c r="K229" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="X229" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="230" spans="11:24">
       <c r="K230" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="X230" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="231" spans="11:24">
       <c r="K231" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="X231" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="232" spans="11:24">
       <c r="K232" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="X232" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="233" spans="11:24">
       <c r="K233" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="X233" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="234" spans="11:24">
       <c r="K234" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="X234" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="235" spans="11:24">
       <c r="K235" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="X235" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="236" spans="11:24">
       <c r="K236" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="X236" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="237" spans="11:24">
       <c r="K237" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="X237" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="238" spans="11:24">
       <c r="K238" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="X238" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="239" spans="11:24">
       <c r="K239" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="X239" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="240" spans="11:24">
       <c r="K240" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="X240" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="241" spans="11:24">
       <c r="K241" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="X241" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="242" spans="11:24">
       <c r="K242" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="X242" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="243" spans="11:24">
       <c r="K243" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="X243" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="244" spans="11:24">
       <c r="K244" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="X244" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="245" spans="11:24">
       <c r="K245" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="X245" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="246" spans="11:24">
       <c r="K246" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="X246" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="247" spans="11:24">
       <c r="K247" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="X247" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="248" spans="11:24">
       <c r="K248" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="X248" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="249" spans="11:24">
       <c r="K249" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="X249" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="250" spans="11:24">
       <c r="K250" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="X250" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="251" spans="11:24">
       <c r="K251" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="X251" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="252" spans="11:24">
       <c r="K252" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="X252" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="253" spans="11:24">
       <c r="K253" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="X253" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="254" spans="11:24">
       <c r="K254" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="X254" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="255" spans="11:24">
       <c r="K255" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="X255" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="256" spans="11:24">
       <c r="K256" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="X256" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="257" spans="11:24">
       <c r="K257" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="X257" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="258" spans="11:24">
       <c r="K258" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="X258" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="259" spans="11:24">
       <c r="K259" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="X259" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="260" spans="11:24">
       <c r="K260" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="X260" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="261" spans="11:24">
       <c r="K261" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="X261" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="262" spans="11:24">
       <c r="K262" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="X262" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="263" spans="11:24">
       <c r="K263" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="X263" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="264" spans="11:24">
       <c r="K264" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="X264" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="265" spans="11:24">
       <c r="K265" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="X265" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="266" spans="11:24">
       <c r="K266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="X266" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="267" spans="11:24">
       <c r="K267" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="X267" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="268" spans="11:24">
       <c r="K268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="X268" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="269" spans="11:24">
       <c r="K269" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="X269" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="270" spans="11:24">
       <c r="K270" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="X270" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="271" spans="11:24">
       <c r="K271" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="X271" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="272" spans="11:24">
       <c r="K272" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="X272" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="273" spans="11:24">
       <c r="K273" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="X273" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="274" spans="11:24">
       <c r="X274" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="275" spans="11:24">
       <c r="X275" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="276" spans="11:24">
       <c r="X276" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="277" spans="11:24">
       <c r="X277" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="278" spans="11:24">
       <c r="X278" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="279" spans="11:24">
       <c r="X279" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="280" spans="11:24">
       <c r="X280" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="281" spans="11:24">
       <c r="X281" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="282" spans="11:24">
       <c r="X282" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="283" spans="11:24">
       <c r="X283" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="284" spans="11:24">
       <c r="X284" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="285" spans="11:24">
       <c r="X285" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="286" spans="11:24">
       <c r="X286" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="287" spans="11:24">
       <c r="X287" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="288" spans="11:24">
       <c r="X288" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="289" spans="24:24">
       <c r="X289" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="290" spans="24:24">
       <c r="X290" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="291" spans="24:24">
       <c r="X291" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="292" spans="24:24">
       <c r="X292" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="293" spans="24:24">
       <c r="X293" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="294" spans="24:24">
       <c r="X294" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
